--- a/research/traditional_assets/database/data/ireland/ireland_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_healthcare_products.xlsx
@@ -650,10 +650,10 @@
         <v>0.08332685581033812</v>
       </c>
       <c r="X2">
-        <v>0.1125258915145677</v>
+        <v>0.1124947298653836</v>
       </c>
       <c r="Y2">
-        <v>-0.02919903570422956</v>
+        <v>-0.02916787405504546</v>
       </c>
       <c r="Z2">
         <v>0.9340441870693288</v>
@@ -662,10 +662,10 @@
         <v>0.1553167498828909</v>
       </c>
       <c r="AB2">
-        <v>0.09924040195719262</v>
+        <v>0.09921616116575546</v>
       </c>
       <c r="AC2">
-        <v>0.05607634792569825</v>
+        <v>0.05610058871713541</v>
       </c>
       <c r="AD2">
         <v>28326</v>
@@ -787,10 +787,10 @@
         <v>0.08332685581033812</v>
       </c>
       <c r="X3">
-        <v>0.1125258915145677</v>
+        <v>0.1124947298653836</v>
       </c>
       <c r="Y3">
-        <v>-0.02919903570422956</v>
+        <v>-0.02916787405504546</v>
       </c>
       <c r="Z3">
         <v>0.9340441870693288</v>
@@ -799,10 +799,10 @@
         <v>0.1553167498828909</v>
       </c>
       <c r="AB3">
-        <v>0.09924040195719262</v>
+        <v>0.09921616116575546</v>
       </c>
       <c r="AC3">
-        <v>0.05607634792569825</v>
+        <v>0.05610058871713541</v>
       </c>
       <c r="AD3">
         <v>28326</v>
@@ -1139,7 +1139,7 @@
         <v>10.0522193211488</v>
       </c>
       <c r="F2">
-        <v>9.22365369650187</v>
+        <v>9.453274821339299</v>
       </c>
       <c r="G2">
         <v>3.12268573127144</v>
@@ -1157,13 +1157,13 @@
         <v>102429</v>
       </c>
       <c r="L2">
-        <v>117866.300055793</v>
+        <v>118200.394114519</v>
       </c>
       <c r="M2">
         <v>130278.951873357</v>
       </c>
       <c r="N2">
-        <v>130956.324761862</v>
+        <v>131290.418820588</v>
       </c>
       <c r="O2">
         <v>29243.951873357</v>
@@ -1172,16 +1172,16 @@
         <v>14484.0247060693</v>
       </c>
       <c r="Q2">
-        <v>0.09924040195719259</v>
+        <v>0.0992161611657555</v>
       </c>
       <c r="R2">
-        <v>0.0989639809481084</v>
+        <v>0.09880464079776149</v>
       </c>
       <c r="S2">
         <v>0.0527070395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.112525891514568</v>
+        <v>0.112494729865384</v>
       </c>
       <c r="X2">
-        <v>0.104962310780157</v>
+        <v>0.104934681397745</v>
       </c>
       <c r="Y2">
         <v>1.30000442391174</v>
@@ -1236,7 +1236,7 @@
         <v>102429</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09918854914508439</v>
+        <v>0.09916361616627895</v>
       </c>
       <c r="C2">
-        <v>131799.4833135501</v>
+        <v>131801.232300168</v>
       </c>
       <c r="D2">
-        <v>130405.4833135501</v>
+        <v>130407.232300168</v>
       </c>
       <c r="E2">
         <v>-29243.95187335703</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09918854914508439</v>
+        <v>0.09916361616627895</v>
       </c>
       <c r="T2">
         <v>1.040156204727314</v>
       </c>
       <c r="U2">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09916813385445021</v>
+        <v>0.09913098204186825</v>
       </c>
       <c r="C3">
-        <v>130532.6387289496</v>
+        <v>130564.3011590379</v>
       </c>
       <c r="D3">
-        <v>130455.3682476832</v>
+        <v>130487.0306777714</v>
       </c>
       <c r="E3">
         <v>-27927.22235462346</v>
@@ -1539,37 +1539,37 @@
         <v>7700</v>
       </c>
       <c r="M3">
-        <v>75.89183451948979</v>
+        <v>74.04841319326279</v>
       </c>
       <c r="N3">
-        <v>7624.10816548051</v>
+        <v>7625.951586806737</v>
       </c>
       <c r="O3">
-        <v>953.0135206850638</v>
+        <v>953.2439483508422</v>
       </c>
       <c r="P3">
-        <v>6671.094644795447</v>
+        <v>6672.707638455895</v>
       </c>
       <c r="Q3">
-        <v>8336.094644795447</v>
+        <v>8337.707638455895</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09966041763500307</v>
+        <v>0.09963526428896069</v>
       </c>
       <c r="T3">
         <v>1.049349504516571</v>
       </c>
       <c r="U3">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>101.4601906615205</v>
+        <v>103.9860230347323</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09914771856381602</v>
+        <v>0.09909834791745757</v>
       </c>
       <c r="C4">
-        <v>129265.8323246297</v>
+        <v>129327.4677376414</v>
       </c>
       <c r="D4">
-        <v>130505.2913620969</v>
+        <v>130566.9267751085</v>
       </c>
       <c r="E4">
         <v>-26610.49283588989</v>
@@ -1621,37 +1621,37 @@
         <v>7700</v>
       </c>
       <c r="M4">
-        <v>151.7836690389796</v>
+        <v>148.0968263865256</v>
       </c>
       <c r="N4">
-        <v>7548.216330961021</v>
+        <v>7551.903173613475</v>
       </c>
       <c r="O4">
-        <v>943.5270413701276</v>
+        <v>943.9878967016843</v>
       </c>
       <c r="P4">
-        <v>6604.689289590893</v>
+        <v>6607.91527691179</v>
       </c>
       <c r="Q4">
-        <v>8269.689289590893</v>
+        <v>8272.91527691179</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1001419160941038</v>
+        <v>0.1001165378835339</v>
       </c>
       <c r="T4">
         <v>1.058730422668873</v>
       </c>
       <c r="U4">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>50.73009533076027</v>
+        <v>51.99301151736616</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.09912730327318184</v>
+        <v>0.09906571379304691</v>
       </c>
       <c r="C5">
-        <v>127999.0641444399</v>
+        <v>128090.7322155874</v>
       </c>
       <c r="D5">
-        <v>130555.2527006406</v>
+        <v>130646.9207717881</v>
       </c>
       <c r="E5">
         <v>-25293.76331715632</v>
@@ -1703,37 +1703,37 @@
         <v>7700</v>
       </c>
       <c r="M5">
-        <v>227.6755035584693</v>
+        <v>222.1452395797884</v>
       </c>
       <c r="N5">
-        <v>7472.324496441531</v>
+        <v>7477.854760420211</v>
       </c>
       <c r="O5">
-        <v>934.0405620551913</v>
+        <v>934.7318450525264</v>
       </c>
       <c r="P5">
-        <v>6538.28393438634</v>
+        <v>6543.122915367685</v>
       </c>
       <c r="Q5">
-        <v>8203.28393438634</v>
+        <v>8208.122915367685</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1006333423564849</v>
+        <v>0.1006077346450056</v>
       </c>
       <c r="T5">
         <v>1.068304761814007</v>
       </c>
       <c r="U5">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>33.82006355384019</v>
+        <v>34.6620076782441</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09910688798254765</v>
+        <v>0.09903307966863623</v>
       </c>
       <c r="C6">
-        <v>126732.334232297</v>
+        <v>126854.0947729253</v>
       </c>
       <c r="D6">
-        <v>130605.2523072313</v>
+        <v>130727.0128478595</v>
       </c>
       <c r="E6">
         <v>-23977.03379842275</v>
@@ -1785,37 +1785,37 @@
         <v>7700</v>
       </c>
       <c r="M6">
-        <v>303.5673380779592</v>
+        <v>296.1936527730512</v>
       </c>
       <c r="N6">
-        <v>7396.432661922041</v>
+        <v>7403.806347226949</v>
       </c>
       <c r="O6">
-        <v>924.5540827402551</v>
+        <v>925.4757934033686</v>
       </c>
       <c r="P6">
-        <v>6471.878579181786</v>
+        <v>6478.33055382358</v>
       </c>
       <c r="Q6">
-        <v>8136.878579181786</v>
+        <v>8143.33055382358</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1011350066659989</v>
+        <v>0.1011091646723412</v>
       </c>
       <c r="T6">
         <v>1.078078566357997</v>
       </c>
       <c r="U6">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.36504766538014</v>
+        <v>25.99650575868307</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09908647269191347</v>
+        <v>0.09900044554422556</v>
       </c>
       <c r="C7">
-        <v>125465.6426321853</v>
+        <v>125617.555590146</v>
       </c>
       <c r="D7">
-        <v>130655.2902258532</v>
+        <v>130807.2031838139</v>
       </c>
       <c r="E7">
         <v>-22660.30427968918</v>
@@ -1867,37 +1867,37 @@
         <v>7700</v>
       </c>
       <c r="M7">
-        <v>379.4591725974489</v>
+        <v>370.2420659663139</v>
       </c>
       <c r="N7">
-        <v>7320.540827402551</v>
+        <v>7329.757934033686</v>
       </c>
       <c r="O7">
-        <v>915.0676034253189</v>
+        <v>916.2197417542108</v>
       </c>
       <c r="P7">
-        <v>6405.473223977232</v>
+        <v>6413.538192279475</v>
       </c>
       <c r="Q7">
-        <v>8070.473223977232</v>
+        <v>8078.538192279475</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1016472323293975</v>
+        <v>0.1016211511213049</v>
       </c>
       <c r="T7">
         <v>1.088058135208178</v>
       </c>
       <c r="U7">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.29203813230411</v>
+        <v>20.79720460694646</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0990660574012793</v>
+        <v>0.09896781141981488</v>
       </c>
       <c r="C8">
-        <v>124198.9893881562</v>
+        <v>124381.1148481839</v>
       </c>
       <c r="D8">
-        <v>130705.3665005577</v>
+        <v>130887.4919605854</v>
       </c>
       <c r="E8">
         <v>-21343.57476095561</v>
@@ -1949,37 +1949,37 @@
         <v>7700</v>
       </c>
       <c r="M8">
-        <v>455.3510071169387</v>
+        <v>444.2904791595767</v>
       </c>
       <c r="N8">
-        <v>7244.648992883062</v>
+        <v>7255.709520840423</v>
       </c>
       <c r="O8">
-        <v>905.5811241103827</v>
+        <v>906.9636901050529</v>
       </c>
       <c r="P8">
-        <v>6339.067868772679</v>
+        <v>6348.745830735371</v>
       </c>
       <c r="Q8">
-        <v>8004.067868772679</v>
+        <v>8013.745830735371</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1021703564111662</v>
+        <v>0.1021440308989701</v>
       </c>
       <c r="T8">
         <v>1.098250035310489</v>
       </c>
       <c r="U8">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>16.91003177692009</v>
+        <v>17.33100383912205</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09904564211064511</v>
+        <v>0.09893517729540421</v>
       </c>
       <c r="C9">
-        <v>122932.3745443291</v>
+        <v>123144.7727284177</v>
       </c>
       <c r="D9">
-        <v>130755.481175464</v>
+        <v>130967.8793595526</v>
       </c>
       <c r="E9">
         <v>-20026.84524222204</v>
@@ -2031,37 +2031,37 @@
         <v>7700</v>
       </c>
       <c r="M9">
-        <v>531.2428416364286</v>
+        <v>518.3388923528396</v>
       </c>
       <c r="N9">
-        <v>7168.757158363572</v>
+        <v>7181.66110764716</v>
       </c>
       <c r="O9">
-        <v>896.0946447954465</v>
+        <v>897.707638455895</v>
       </c>
       <c r="P9">
-        <v>6272.662513568125</v>
+        <v>6283.953469191265</v>
       </c>
       <c r="Q9">
-        <v>7937.662513568125</v>
+        <v>7948.953469191265</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1027047304731881</v>
+        <v>0.1026781554030366</v>
       </c>
       <c r="T9">
         <v>1.108661116060162</v>
       </c>
       <c r="U9">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.49431295164579</v>
+        <v>14.8551461478189</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09902522682001093</v>
+        <v>0.09890254317099353</v>
       </c>
       <c r="C10">
-        <v>121665.7981448905</v>
+        <v>121908.5294126717</v>
       </c>
       <c r="D10">
-        <v>130805.6342947591</v>
+        <v>131048.3655625403</v>
       </c>
       <c r="E10">
         <v>-18710.11572348847</v>
@@ -2113,37 +2113,37 @@
         <v>7700</v>
       </c>
       <c r="M10">
-        <v>607.1346761559183</v>
+        <v>592.3873055461023</v>
       </c>
       <c r="N10">
-        <v>7092.865323844082</v>
+        <v>7107.612694453897</v>
       </c>
       <c r="O10">
-        <v>886.6081654805103</v>
+        <v>888.4515868067372</v>
       </c>
       <c r="P10">
-        <v>6206.257158363572</v>
+        <v>6219.16110764716</v>
       </c>
       <c r="Q10">
-        <v>7871.257158363572</v>
+        <v>7884.16110764716</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1032507213626452</v>
+        <v>0.1032238913093654</v>
       </c>
       <c r="T10">
         <v>1.119298524652219</v>
       </c>
       <c r="U10">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.68252383269007</v>
+        <v>12.99825287934154</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09900481152937675</v>
+        <v>0.09886990904658285</v>
       </c>
       <c r="C11">
-        <v>120399.2602340953</v>
+        <v>120672.385083218</v>
       </c>
       <c r="D11">
-        <v>130855.8259026974</v>
+        <v>131128.9507518202</v>
       </c>
       <c r="E11">
         <v>-17393.3862047549</v>
@@ -2195,37 +2195,37 @@
         <v>7700</v>
       </c>
       <c r="M11">
-        <v>683.0265106754081</v>
+        <v>666.435718739365</v>
       </c>
       <c r="N11">
-        <v>7016.973489324592</v>
+        <v>7033.564281260635</v>
       </c>
       <c r="O11">
-        <v>877.121686165574</v>
+        <v>879.1955351575793</v>
       </c>
       <c r="P11">
-        <v>6139.851803159018</v>
+        <v>6154.368746103055</v>
       </c>
       <c r="Q11">
-        <v>7804.851803159018</v>
+        <v>7819.368746103055</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1038087120518705</v>
+        <v>0.1037816214114377</v>
       </c>
       <c r="T11">
         <v>1.130169722444101</v>
       </c>
       <c r="U11">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.27335451794673</v>
+        <v>11.5540025594147</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09898439623874258</v>
+        <v>0.09883727492217219</v>
       </c>
       <c r="C12">
-        <v>119132.7608562659</v>
+        <v>119436.3399227769</v>
       </c>
       <c r="D12">
-        <v>130906.0560436016</v>
+        <v>131209.6351101126</v>
       </c>
       <c r="E12">
         <v>-16076.65668602133</v>
@@ -2277,37 +2277,37 @@
         <v>7700</v>
       </c>
       <c r="M12">
-        <v>758.9183451948978</v>
+        <v>740.4841319326279</v>
       </c>
       <c r="N12">
-        <v>6941.081654805103</v>
+        <v>6959.515868067372</v>
       </c>
       <c r="O12">
-        <v>867.6352068506378</v>
+        <v>869.9394835084215</v>
       </c>
       <c r="P12">
-        <v>6073.446447954465</v>
+        <v>6089.576384558951</v>
       </c>
       <c r="Q12">
-        <v>7738.446447954465</v>
+        <v>7754.576384558951</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1043791025341898</v>
+        <v>0.1043517455157783</v>
       </c>
       <c r="T12">
         <v>1.141282502409137</v>
       </c>
       <c r="U12">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.14601906615206</v>
+        <v>10.39860230347323</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09896398094810839</v>
+        <v>0.09880464079776152</v>
       </c>
       <c r="C13">
-        <v>117866.3000557932</v>
+        <v>118200.3941145188</v>
       </c>
       <c r="D13">
-        <v>130956.3247618625</v>
+        <v>131290.418820588</v>
       </c>
       <c r="E13">
         <v>-14759.92716728776</v>
@@ -2359,37 +2359,37 @@
         <v>7700</v>
       </c>
       <c r="M13">
-        <v>834.8101797143876</v>
+        <v>814.5325451258906</v>
       </c>
       <c r="N13">
-        <v>6865.189820285613</v>
+        <v>6885.46745487411</v>
       </c>
       <c r="O13">
-        <v>858.1487275357016</v>
+        <v>860.6834318592637</v>
       </c>
       <c r="P13">
-        <v>6007.041092749912</v>
+        <v>6024.784023014846</v>
       </c>
       <c r="Q13">
-        <v>7672.041092749912</v>
+        <v>7689.784023014846</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1049623107801567</v>
+        <v>0.1049346813977445</v>
       </c>
       <c r="T13">
         <v>1.152645007766645</v>
       </c>
       <c r="U13">
-        <v>0.05763661666253408</v>
+        <v>0.05623661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971732</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>9.223653696501868</v>
+        <v>9.453274821339303</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0990590656574742</v>
+        <v>0.09892950667335085</v>
       </c>
       <c r="C14">
-        <v>116315.7710153091</v>
+        <v>116575.1036071934</v>
       </c>
       <c r="D14">
-        <v>130722.525240112</v>
+        <v>130981.8578319963</v>
       </c>
       <c r="E14">
         <v>-13443.19764855419</v>
@@ -2441,37 +2441,37 @@
         <v>7700</v>
       </c>
       <c r="M14">
-        <v>928.0828438811606</v>
+        <v>912.2820896563577</v>
       </c>
       <c r="N14">
-        <v>6771.91715611884</v>
+        <v>6787.717910343642</v>
       </c>
       <c r="O14">
-        <v>846.4896445148549</v>
+        <v>848.4647387929552</v>
       </c>
       <c r="P14">
-        <v>5925.427511603984</v>
+        <v>5939.253171550687</v>
       </c>
       <c r="Q14">
-        <v>7590.427511603984</v>
+        <v>7604.253171550687</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1055587737589865</v>
+        <v>0.1055308658224827</v>
       </c>
       <c r="T14">
         <v>1.164265751882278</v>
       </c>
       <c r="U14">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.296673137280806</v>
+        <v>8.440371774590542</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.09904827536684002</v>
+        <v>0.09890999754894017</v>
       </c>
       <c r="C15">
-        <v>115025.5312566674</v>
+        <v>115306.4882190928</v>
       </c>
       <c r="D15">
-        <v>130749.0150002039</v>
+        <v>131029.9719626292</v>
       </c>
       <c r="E15">
         <v>-12126.46812982062</v>
@@ -2523,37 +2523,37 @@
         <v>7700</v>
       </c>
       <c r="M15">
-        <v>1005.423080871257</v>
+        <v>988.3055971277208</v>
       </c>
       <c r="N15">
-        <v>6694.576919128743</v>
+        <v>6711.694402872279</v>
       </c>
       <c r="O15">
-        <v>836.8221148910928</v>
+        <v>838.9618003590349</v>
       </c>
       <c r="P15">
-        <v>5857.75480423765</v>
+        <v>5872.732602513244</v>
       </c>
       <c r="Q15">
-        <v>7522.75480423765</v>
+        <v>7537.732602513244</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1061689485304331</v>
+        <v>0.1061407556362953</v>
       </c>
       <c r="T15">
         <v>1.176153639540799</v>
       </c>
       <c r="U15">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.658467511336127</v>
+        <v>7.791112407314347</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09903748507620584</v>
+        <v>0.09889048842452949</v>
       </c>
       <c r="C16">
-        <v>113735.3022360315</v>
+        <v>114037.9081919236</v>
       </c>
       <c r="D16">
-        <v>130775.5154983015</v>
+        <v>131078.1214541936</v>
       </c>
       <c r="E16">
         <v>-10809.73861108704</v>
@@ -2605,37 +2605,37 @@
         <v>7700</v>
       </c>
       <c r="M16">
-        <v>1082.763317861354</v>
+        <v>1064.329104599084</v>
       </c>
       <c r="N16">
-        <v>6617.236682138646</v>
+        <v>6635.670895400915</v>
       </c>
       <c r="O16">
-        <v>827.1545852673307</v>
+        <v>829.4588619251144</v>
       </c>
       <c r="P16">
-        <v>5790.082096871315</v>
+        <v>5806.212033475801</v>
       </c>
       <c r="Q16">
-        <v>7455.082096871315</v>
+        <v>7471.212033475801</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1067933134128435</v>
+        <v>0.1067648289341501</v>
       </c>
       <c r="T16">
         <v>1.188317989703007</v>
       </c>
       <c r="U16">
-        <v>0.05873661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.11143411766926</v>
+        <v>7.234604378220464</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09931544478557164</v>
+        <v>0.09887097930011882</v>
       </c>
       <c r="C17">
-        <v>111739.3234944666</v>
+        <v>112769.3635646824</v>
       </c>
       <c r="D17">
-        <v>130096.2662754702</v>
+        <v>131126.306345686</v>
       </c>
       <c r="E17">
         <v>-9493.009092353477</v>
@@ -2687,45 +2687,45 @@
         <v>7700</v>
       </c>
       <c r="M17">
-        <v>1203.555628969659</v>
+        <v>1140.352612070447</v>
       </c>
       <c r="N17">
-        <v>6496.444371030341</v>
+        <v>6559.647387929553</v>
       </c>
       <c r="O17">
-        <v>812.0555463787927</v>
+        <v>819.9559234911941</v>
       </c>
       <c r="P17">
-        <v>5684.388824651549</v>
+        <v>5739.691464438359</v>
       </c>
       <c r="Q17">
-        <v>7349.388824651549</v>
+        <v>7404.691464438359</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1074323692336636</v>
+        <v>0.1074035863096014</v>
       </c>
       <c r="T17">
         <v>1.200768559869032</v>
       </c>
       <c r="U17">
-        <v>0.06093661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05331953957971733</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.397710097199101</v>
+        <v>6.752297419672434</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09932390449493747</v>
+        <v>0.09908947017570813</v>
       </c>
       <c r="C18">
-        <v>110402.0316379766</v>
+        <v>110915.0062295754</v>
       </c>
       <c r="D18">
-        <v>130075.7039377137</v>
+        <v>130588.6785293126</v>
       </c>
       <c r="E18">
         <v>-8176.279573619904</v>
@@ -2769,37 +2769,37 @@
         <v>7700</v>
       </c>
       <c r="M18">
-        <v>1283.792670900969</v>
+        <v>1252.191162451363</v>
       </c>
       <c r="N18">
-        <v>6416.207329099031</v>
+        <v>6447.808837548637</v>
       </c>
       <c r="O18">
-        <v>802.0259161373789</v>
+        <v>805.9761046935796</v>
       </c>
       <c r="P18">
-        <v>5614.181412961652</v>
+        <v>5641.832732855057</v>
       </c>
       <c r="Q18">
-        <v>7279.181412961652</v>
+        <v>7306.832732855057</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1080866406692651</v>
+        <v>0.1080575521939921</v>
       </c>
       <c r="T18">
         <v>1.213515572181867</v>
       </c>
       <c r="U18">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05331953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.997853216124158</v>
+        <v>6.149220846540735</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09933236420430329</v>
+        <v>0.09908483605129746</v>
       </c>
       <c r="C19">
-        <v>109064.7462804113</v>
+        <v>109609.6338666066</v>
       </c>
       <c r="D19">
-        <v>130055.148098882</v>
+        <v>130600.0356850773</v>
       </c>
       <c r="E19">
         <v>-6859.550054886331</v>
@@ -2851,37 +2851,37 @@
         <v>7700</v>
       </c>
       <c r="M19">
-        <v>1364.02971283228</v>
+        <v>1330.453110104574</v>
       </c>
       <c r="N19">
-        <v>6335.97028716772</v>
+        <v>6369.546889895426</v>
       </c>
       <c r="O19">
-        <v>791.996285895965</v>
+        <v>796.1933612369282</v>
       </c>
       <c r="P19">
-        <v>5543.974001271755</v>
+        <v>5573.353528658497</v>
       </c>
       <c r="Q19">
-        <v>7208.974001271755</v>
+        <v>7238.353528658497</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1087566776816281</v>
+        <v>0.1087272762924645</v>
       </c>
       <c r="T19">
         <v>1.226569741417902</v>
       </c>
       <c r="U19">
-        <v>0.06093661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05331953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.645038321058029</v>
+        <v>5.787501973214808</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.09957707391366913</v>
+        <v>0.09920620192688681</v>
       </c>
       <c r="C20">
-        <v>107156.2077401623</v>
+        <v>107996.1150778811</v>
       </c>
       <c r="D20">
-        <v>129463.3390773666</v>
+        <v>130303.2464150853</v>
       </c>
       <c r="E20">
         <v>-5542.820536152765</v>
@@ -2933,37 +2933,37 @@
         <v>7700</v>
       </c>
       <c r="M20">
-        <v>1479.818451769397</v>
+        <v>1427.675962827547</v>
       </c>
       <c r="N20">
-        <v>6220.181548230603</v>
+        <v>6272.324037172453</v>
       </c>
       <c r="O20">
-        <v>777.5226935288254</v>
+        <v>784.0405046465567</v>
       </c>
       <c r="P20">
-        <v>5442.658854701777</v>
+        <v>5488.283532525897</v>
       </c>
       <c r="Q20">
-        <v>7107.658854701777</v>
+        <v>7153.283532525897</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1094430570601463</v>
+        <v>0.1094133351250459</v>
       </c>
       <c r="T20">
         <v>1.239942305025548</v>
       </c>
       <c r="U20">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.203340984695268</v>
+        <v>5.393380711369519</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09959865862303495</v>
+        <v>0.09920856780247611</v>
       </c>
       <c r="C21">
-        <v>105787.535875299</v>
+        <v>106673.6134277726</v>
       </c>
       <c r="D21">
-        <v>129411.3967312368</v>
+        <v>130297.4742837105</v>
       </c>
       <c r="E21">
         <v>-4226.091017419192</v>
@@ -3015,37 +3015,37 @@
         <v>7700</v>
       </c>
       <c r="M21">
-        <v>1562.030587978808</v>
+        <v>1506.991294095744</v>
       </c>
       <c r="N21">
-        <v>6137.969412021193</v>
+        <v>6193.008705904255</v>
       </c>
       <c r="O21">
-        <v>767.2461765026491</v>
+        <v>774.1260882380319</v>
       </c>
       <c r="P21">
-        <v>5370.723235518543</v>
+        <v>5418.882617666223</v>
       </c>
       <c r="Q21">
-        <v>7035.723235518543</v>
+        <v>7083.882617666223</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1101463840776403</v>
+        <v>0.1101163336818887</v>
       </c>
       <c r="T21">
         <v>1.253645055388939</v>
       </c>
       <c r="U21">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.929480932869201</v>
+        <v>5.10951856866586</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09962024333240074</v>
+        <v>0.09921093367806544</v>
       </c>
       <c r="C22">
-        <v>104418.9056735861</v>
+        <v>105351.1122890255</v>
       </c>
       <c r="D22">
-        <v>129359.4960482575</v>
+        <v>130291.7026636969</v>
       </c>
       <c r="E22">
         <v>-2909.361498685623</v>
@@ -3097,37 +3097,37 @@
         <v>7700</v>
       </c>
       <c r="M22">
-        <v>1644.242724188219</v>
+        <v>1586.306625363942</v>
       </c>
       <c r="N22">
-        <v>6055.757275811781</v>
+        <v>6113.693374636058</v>
       </c>
       <c r="O22">
-        <v>756.9696594764727</v>
+        <v>764.2116718295073</v>
       </c>
       <c r="P22">
-        <v>5298.787616335308</v>
+        <v>5349.481702806551</v>
       </c>
       <c r="Q22">
-        <v>6963.787616335308</v>
+        <v>7014.481702806551</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1108672942705716</v>
+        <v>0.1108369072026525</v>
       </c>
       <c r="T22">
         <v>1.267690374511414</v>
       </c>
       <c r="U22">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.683006886225741</v>
+        <v>4.854042640232567</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09964182804176656</v>
+        <v>0.09921329955365477</v>
       </c>
       <c r="C23">
-        <v>103050.3170849164</v>
+        <v>104028.6116615719</v>
       </c>
       <c r="D23">
-        <v>129307.6369783213</v>
+        <v>130285.9315549768</v>
       </c>
       <c r="E23">
         <v>-1592.631979952053</v>
@@ -3179,37 +3179,37 @@
         <v>7700</v>
       </c>
       <c r="M23">
-        <v>1726.45486039763</v>
+        <v>1665.621956632139</v>
       </c>
       <c r="N23">
-        <v>5973.545139602371</v>
+        <v>6034.378043367861</v>
       </c>
       <c r="O23">
-        <v>746.6931424502964</v>
+        <v>754.2972554209827</v>
       </c>
       <c r="P23">
-        <v>5226.851997152075</v>
+        <v>5280.080787946878</v>
       </c>
       <c r="Q23">
-        <v>6891.851997152075</v>
+        <v>6945.080787946878</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1116064553544632</v>
+        <v>0.1115757230910305</v>
       </c>
       <c r="T23">
         <v>1.282091271333193</v>
       </c>
       <c r="U23">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.46000655831023</v>
+        <v>4.622897752602444</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09966341275113237</v>
+        <v>0.09921566542924408</v>
       </c>
       <c r="C24">
-        <v>101681.770059263</v>
+        <v>102706.1115453437</v>
       </c>
       <c r="D24">
-        <v>129255.8194714015</v>
+        <v>130280.1609574822</v>
       </c>
       <c r="E24">
         <v>-275.9024612184839</v>
@@ -3261,37 +3261,37 @@
         <v>7700</v>
       </c>
       <c r="M24">
-        <v>1808.66699660704</v>
+        <v>1744.937287900336</v>
       </c>
       <c r="N24">
-        <v>5891.33300339296</v>
+        <v>5955.062712099664</v>
       </c>
       <c r="O24">
-        <v>736.41662542412</v>
+        <v>744.382839012458</v>
       </c>
       <c r="P24">
-        <v>5154.91637796884</v>
+        <v>5210.679873087206</v>
       </c>
       <c r="Q24">
-        <v>6819.91637796884</v>
+        <v>6875.679873087206</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1123645692866597</v>
+        <v>0.1123334829765465</v>
       </c>
       <c r="T24">
         <v>1.296861421919632</v>
       </c>
       <c r="U24">
-        <v>0.06243661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05463203957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.257278987477947</v>
+        <v>4.412766036575061</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09996674746049819</v>
+        <v>0.09941928130483341</v>
       </c>
       <c r="C25">
-        <v>99641.20574757288</v>
+        <v>100894.6512432103</v>
       </c>
       <c r="D25">
-        <v>128531.984678445</v>
+        <v>129785.4301740824</v>
       </c>
       <c r="E25">
         <v>1040.827057515089</v>
@@ -3343,37 +3343,37 @@
         <v>7700</v>
       </c>
       <c r="M25">
-        <v>1933.277823319673</v>
+        <v>1854.537398099405</v>
       </c>
       <c r="N25">
-        <v>5766.722176680328</v>
+        <v>5845.462601900595</v>
       </c>
       <c r="O25">
-        <v>720.840272085041</v>
+        <v>730.6828252375744</v>
       </c>
       <c r="P25">
-        <v>5045.881904595287</v>
+        <v>5114.779776663021</v>
       </c>
       <c r="Q25">
-        <v>6710.881904595287</v>
+        <v>6779.779776663021</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1131423744898223</v>
+        <v>0.1131109249370109</v>
       </c>
       <c r="T25">
         <v>1.312015212781044</v>
       </c>
       <c r="U25">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.982872977241402</v>
+        <v>4.1519788211827</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.100000582169864</v>
+        <v>0.09943039718042274</v>
       </c>
       <c r="C26">
-        <v>98244.24014701678</v>
+        <v>99551.02133270323</v>
       </c>
       <c r="D26">
-        <v>128451.7485966225</v>
+        <v>129758.5297823089</v>
       </c>
       <c r="E26">
         <v>2357.556576248655</v>
@@ -3425,37 +3425,37 @@
         <v>7700</v>
       </c>
       <c r="M26">
-        <v>2017.33338085531</v>
+        <v>1935.169458886335</v>
       </c>
       <c r="N26">
-        <v>5682.666619144689</v>
+        <v>5764.830541113664</v>
       </c>
       <c r="O26">
-        <v>710.3333273930862</v>
+        <v>720.603817639208</v>
       </c>
       <c r="P26">
-        <v>4972.333291751604</v>
+        <v>5044.226723474456</v>
       </c>
       <c r="Q26">
-        <v>6637.333291751604</v>
+        <v>6709.226723474456</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.113940648250963</v>
+        <v>0.113908825896435</v>
       </c>
       <c r="T26">
         <v>1.327567787612493</v>
       </c>
       <c r="U26">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.81691993652301</v>
+        <v>3.978979703633422</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1000344168792298</v>
+        <v>0.09944151305601207</v>
       </c>
       <c r="C27">
-        <v>96847.37465870188</v>
+        <v>98207.40257107656</v>
       </c>
       <c r="D27">
-        <v>128371.6126270411</v>
+        <v>129731.6405394158</v>
       </c>
       <c r="E27">
         <v>3674.286094982228</v>
@@ -3507,37 +3507,37 @@
         <v>7700</v>
       </c>
       <c r="M27">
-        <v>2101.388938390948</v>
+        <v>2015.801519673266</v>
       </c>
       <c r="N27">
-        <v>5598.611061609052</v>
+        <v>5684.198480326734</v>
       </c>
       <c r="O27">
-        <v>699.8263827011315</v>
+        <v>710.5248100408418</v>
       </c>
       <c r="P27">
-        <v>4898.78467890792</v>
+        <v>4973.673670285893</v>
       </c>
       <c r="Q27">
-        <v>6563.78467890792</v>
+        <v>6638.673670285893</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1147602093124007</v>
+        <v>0.114728004214777</v>
       </c>
       <c r="T27">
         <v>1.343535097772781</v>
       </c>
       <c r="U27">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.66424313906209</v>
+        <v>3.819820515488085</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1000682515885957</v>
+        <v>0.09945262893160137</v>
       </c>
       <c r="C28">
-        <v>95450.6090953766</v>
+        <v>96863.79495140092</v>
       </c>
       <c r="D28">
-        <v>128291.5765824494</v>
+        <v>129704.7624384737</v>
       </c>
       <c r="E28">
         <v>4991.015613715797</v>
@@ -3589,37 +3589,37 @@
         <v>7700</v>
       </c>
       <c r="M28">
-        <v>2185.444495926586</v>
+        <v>2096.433580460197</v>
       </c>
       <c r="N28">
-        <v>5514.555504073414</v>
+        <v>5603.566419539803</v>
       </c>
       <c r="O28">
-        <v>689.3194380091768</v>
+        <v>700.4458024424754</v>
       </c>
       <c r="P28">
-        <v>4825.236066064237</v>
+        <v>4903.120617097327</v>
       </c>
       <c r="Q28">
-        <v>6490.236066064237</v>
+        <v>6568.120617097327</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1156019206727961</v>
+        <v>0.1155693224876687</v>
       </c>
       <c r="T28">
         <v>1.35993395685632</v>
       </c>
       <c r="U28">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.523310710636625</v>
+        <v>3.672904341815466</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1001020862979615</v>
+        <v>0.09946374480719072</v>
       </c>
       <c r="C29">
-        <v>94053.94327025634</v>
+        <v>95520.19846675222</v>
       </c>
       <c r="D29">
-        <v>128211.6402760627</v>
+        <v>129677.8954725586</v>
       </c>
       <c r="E29">
         <v>6307.745132449374</v>
@@ -3671,37 +3671,37 @@
         <v>7700</v>
       </c>
       <c r="M29">
-        <v>2269.500053462225</v>
+        <v>2177.065641247128</v>
       </c>
       <c r="N29">
-        <v>5430.499946537775</v>
+        <v>5522.934358752873</v>
       </c>
       <c r="O29">
-        <v>678.8124933172219</v>
+        <v>690.3667948441091</v>
       </c>
       <c r="P29">
-        <v>4751.687453220553</v>
+        <v>4832.567563908764</v>
       </c>
       <c r="Q29">
-        <v>6416.687453220553</v>
+        <v>6497.567563908764</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1164666926184079</v>
+        <v>0.1164336905762562</v>
       </c>
       <c r="T29">
         <v>1.376782099750367</v>
       </c>
       <c r="U29">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.392817721353786</v>
+        <v>3.536870847674153</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1001359210073273</v>
+        <v>0.09947486068278003</v>
       </c>
       <c r="C30">
-        <v>92657.37699702162</v>
+        <v>94176.61311021265</v>
       </c>
       <c r="D30">
-        <v>128131.8035215616</v>
+        <v>129651.0396347526</v>
       </c>
       <c r="E30">
         <v>7624.474651182943</v>
@@ -3753,37 +3753,37 @@
         <v>7700</v>
       </c>
       <c r="M30">
-        <v>2353.555610997862</v>
+        <v>2257.697702034058</v>
       </c>
       <c r="N30">
-        <v>5346.444389002138</v>
+        <v>5442.302297965942</v>
       </c>
       <c r="O30">
-        <v>668.3055486252672</v>
+        <v>680.2877872457427</v>
       </c>
       <c r="P30">
-        <v>4678.138840376871</v>
+        <v>4762.014510720199</v>
       </c>
       <c r="Q30">
-        <v>6343.138840376871</v>
+        <v>6427.014510720199</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1173554860069534</v>
+        <v>0.1173220688895266</v>
       </c>
       <c r="T30">
         <v>1.394098246613692</v>
       </c>
       <c r="U30">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.271645659876865</v>
+        <v>3.41055403168579</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1001697557166931</v>
+        <v>0.09948597655836935</v>
       </c>
       <c r="C31">
-        <v>91260.91008981681</v>
+        <v>92833.03887486973</v>
       </c>
       <c r="D31">
-        <v>128052.0661330904</v>
+        <v>129624.1949181433</v>
       </c>
       <c r="E31">
         <v>8941.204169916506</v>
@@ -3835,37 +3835,37 @@
         <v>7700</v>
       </c>
       <c r="M31">
-        <v>2437.6111685335</v>
+        <v>2338.329762820988</v>
       </c>
       <c r="N31">
-        <v>5262.3888314665</v>
+        <v>5361.670237179012</v>
       </c>
       <c r="O31">
-        <v>657.7986039333125</v>
+        <v>670.2087796473764</v>
       </c>
       <c r="P31">
-        <v>4604.590227533187</v>
+        <v>4691.461457531635</v>
       </c>
       <c r="Q31">
-        <v>6269.590227533187</v>
+        <v>6356.461457531635</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.118269315828979</v>
+        <v>0.118235471944016</v>
       </c>
       <c r="T31">
         <v>1.4119021722619</v>
       </c>
       <c r="U31">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.158830292294905</v>
+        <v>3.292948720248349</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1002035904260589</v>
+        <v>0.09949709243395867</v>
       </c>
       <c r="C32">
-        <v>89864.54236324853</v>
+        <v>91489.47575381686</v>
       </c>
       <c r="D32">
-        <v>127972.4279252556</v>
+        <v>129597.361315824</v>
       </c>
       <c r="E32">
         <v>10257.93368865008</v>
@@ -3917,37 +3917,37 @@
         <v>7700</v>
       </c>
       <c r="M32">
-        <v>2521.666726069138</v>
+        <v>2418.961823607919</v>
       </c>
       <c r="N32">
-        <v>5178.333273930863</v>
+        <v>5281.038176392081</v>
       </c>
       <c r="O32">
-        <v>647.2916592413578</v>
+        <v>660.1297720490102</v>
       </c>
       <c r="P32">
-        <v>4531.041614689505</v>
+        <v>4620.908404343071</v>
       </c>
       <c r="Q32">
-        <v>6196.041614689505</v>
+        <v>6285.908404343071</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.119209255074491</v>
+        <v>0.1191749722286335</v>
       </c>
       <c r="T32">
         <v>1.430214781500057</v>
       </c>
       <c r="U32">
-        <v>0.0638366166625341</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.053535949218408</v>
+        <v>3.183183762906738</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1009426751354247</v>
+        <v>0.099508208309548</v>
       </c>
       <c r="C33">
-        <v>86832.58113934848</v>
+        <v>90145.9237401531</v>
       </c>
       <c r="D33">
-        <v>126257.1962200892</v>
+        <v>129570.5388208938</v>
       </c>
       <c r="E33">
         <v>11574.66320738365</v>
@@ -3999,45 +3999,45 @@
         <v>7700</v>
       </c>
       <c r="M33">
-        <v>2711.850682814701</v>
+        <v>2499.59388439485</v>
       </c>
       <c r="N33">
-        <v>4988.149317185298</v>
+        <v>5200.40611560515</v>
       </c>
       <c r="O33">
-        <v>623.5186646481623</v>
+        <v>650.0507644506438</v>
       </c>
       <c r="P33">
-        <v>4364.630652537136</v>
+        <v>4550.355351154507</v>
       </c>
       <c r="Q33">
-        <v>6029.630652537136</v>
+        <v>6215.355351154507</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.120176438935815</v>
+        <v>0.1201417044055589</v>
       </c>
       <c r="T33">
         <v>1.449058191005987</v>
       </c>
       <c r="U33">
-        <v>0.06643661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.839389369332078</v>
+        <v>3.080500415716197</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1009992598447906</v>
+        <v>0.1002193241851373</v>
       </c>
       <c r="C34">
-        <v>85386.42548748293</v>
+        <v>87136.0517845393</v>
       </c>
       <c r="D34">
-        <v>126127.7700869572</v>
+        <v>127877.3963840136</v>
       </c>
       <c r="E34">
         <v>12891.39272611722</v>
@@ -4081,37 +4081,37 @@
         <v>7700</v>
       </c>
       <c r="M34">
-        <v>2799.329737099047</v>
+        <v>2685.564306680466</v>
       </c>
       <c r="N34">
-        <v>4900.670262900953</v>
+        <v>5014.435693319534</v>
       </c>
       <c r="O34">
-        <v>612.5837828626192</v>
+        <v>626.8044616649418</v>
       </c>
       <c r="P34">
-        <v>4288.086480038334</v>
+        <v>4387.631231654592</v>
       </c>
       <c r="Q34">
-        <v>5953.086480038334</v>
+        <v>6052.631231654592</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1211720693812956</v>
+        <v>0.1211368698818056</v>
       </c>
       <c r="T34">
         <v>1.468455818438561</v>
       </c>
       <c r="U34">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.75065845154045</v>
+        <v>2.867181389343719</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1010558445541564</v>
+        <v>0.1002523150607266</v>
       </c>
       <c r="C35">
-        <v>83940.53491310151</v>
+        <v>85741.84553648603</v>
       </c>
       <c r="D35">
-        <v>125998.6090313093</v>
+        <v>127799.9196546938</v>
       </c>
       <c r="E35">
         <v>14208.12224485079</v>
@@ -4163,37 +4163,37 @@
         <v>7700</v>
       </c>
       <c r="M35">
-        <v>2886.808791383392</v>
+        <v>2769.488191264231</v>
       </c>
       <c r="N35">
-        <v>4813.191208616608</v>
+        <v>4930.51180873577</v>
       </c>
       <c r="O35">
-        <v>601.6489010770761</v>
+        <v>616.3139760919712</v>
       </c>
       <c r="P35">
-        <v>4211.542307539532</v>
+        <v>4314.197832643798</v>
       </c>
       <c r="Q35">
-        <v>5876.542307539532</v>
+        <v>5979.197832643798</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1221974201385816</v>
+        <v>0.122161741790179</v>
       </c>
       <c r="T35">
         <v>1.48843247952584</v>
       </c>
       <c r="U35">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.667305165130134</v>
+        <v>2.780297104818152</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1011124292635222</v>
+        <v>0.100285305936316</v>
       </c>
       <c r="C36">
-        <v>82494.90860268005</v>
+        <v>84347.73311281687</v>
       </c>
       <c r="D36">
-        <v>125869.7122396214</v>
+        <v>127722.5367497583</v>
       </c>
       <c r="E36">
         <v>15524.85176358437</v>
@@ -4245,37 +4245,37 @@
         <v>7700</v>
       </c>
       <c r="M36">
-        <v>2974.287845667738</v>
+        <v>2853.412075847996</v>
       </c>
       <c r="N36">
-        <v>4725.712154332263</v>
+        <v>4846.587924152004</v>
       </c>
       <c r="O36">
-        <v>590.7140192915328</v>
+        <v>605.8234905190005</v>
       </c>
       <c r="P36">
-        <v>4134.99813504073</v>
+        <v>4240.764433633004</v>
       </c>
       <c r="Q36">
-        <v>5799.99813504073</v>
+        <v>5905.764433633004</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1232538421309368</v>
+        <v>0.1232176704230486</v>
       </c>
       <c r="T36">
         <v>1.509014493979399</v>
       </c>
       <c r="U36">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.588855013214541</v>
+        <v>2.698523660558794</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.101169013972888</v>
+        <v>0.1003182968119053</v>
       </c>
       <c r="C37">
-        <v>81049.54574601981</v>
+        <v>82953.71434320297</v>
       </c>
       <c r="D37">
-        <v>125741.0789016948</v>
+        <v>127645.2474988779</v>
       </c>
       <c r="E37">
         <v>16841.58128231794</v>
@@ -4327,37 +4327,37 @@
         <v>7700</v>
       </c>
       <c r="M37">
-        <v>3061.766899952082</v>
+        <v>2937.335960431761</v>
       </c>
       <c r="N37">
-        <v>4638.233100047917</v>
+        <v>4762.664039568239</v>
       </c>
       <c r="O37">
-        <v>579.7791375059896</v>
+        <v>595.3330049460299</v>
       </c>
       <c r="P37">
-        <v>4058.453962541927</v>
+        <v>4167.331034622209</v>
       </c>
       <c r="Q37">
-        <v>5723.453962541927</v>
+        <v>5832.331034622209</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1243427694153645</v>
+        <v>0.1243060891676988</v>
       </c>
       <c r="T37">
         <v>1.530229801185376</v>
       </c>
       <c r="U37">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.514887727122697</v>
+        <v>2.621422984542828</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1020760986822538</v>
+        <v>0.1003512876874946</v>
       </c>
       <c r="C38">
-        <v>77706.06219348439</v>
+        <v>81559.78905772729</v>
       </c>
       <c r="D38">
-        <v>123714.3248678929</v>
+        <v>127568.0517321358</v>
       </c>
       <c r="E38">
         <v>18158.3108010515</v>
@@ -4409,45 +4409,45 @@
         <v>7700</v>
       </c>
       <c r="M38">
-        <v>3277.232063457331</v>
+        <v>3021.259845015525</v>
       </c>
       <c r="N38">
-        <v>4422.767936542669</v>
+        <v>4678.740154984475</v>
       </c>
       <c r="O38">
-        <v>552.8459920678337</v>
+        <v>584.8425193730594</v>
       </c>
       <c r="P38">
-        <v>3869.921944474836</v>
+        <v>4093.897635611416</v>
       </c>
       <c r="Q38">
-        <v>5534.921944474836</v>
+        <v>5758.897635611416</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1254657256774306</v>
+        <v>0.1254285209981194</v>
       </c>
       <c r="T38">
         <v>1.552108086741539</v>
       </c>
       <c r="U38">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.349543715826108</v>
+        <v>2.548605679416639</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1021563083916197</v>
+        <v>0.1015174035630839</v>
       </c>
       <c r="C39">
-        <v>76213.2549591367</v>
+        <v>77573.17327671633</v>
       </c>
       <c r="D39">
-        <v>123538.2471522788</v>
+        <v>124898.1654698584</v>
       </c>
       <c r="E39">
         <v>19475.04031978507</v>
@@ -4491,37 +4491,37 @@
         <v>7700</v>
       </c>
       <c r="M39">
-        <v>3368.266287442256</v>
+        <v>3275.700202275286</v>
       </c>
       <c r="N39">
-        <v>4331.733712557743</v>
+        <v>4424.299797724714</v>
       </c>
       <c r="O39">
-        <v>541.4667140697179</v>
+        <v>553.0374747155893</v>
       </c>
       <c r="P39">
-        <v>3790.266998488025</v>
+        <v>3871.262323009125</v>
       </c>
       <c r="Q39">
-        <v>5455.266998488025</v>
+        <v>5536.262323009125</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1266243313446417</v>
+        <v>0.1265865855850612</v>
       </c>
       <c r="T39">
         <v>1.574680921045517</v>
       </c>
       <c r="U39">
-        <v>0.06913661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.286042534317295</v>
+        <v>2.350642465586935</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1037992681009855</v>
+        <v>0.1015810194386733</v>
       </c>
       <c r="C40">
-        <v>71397.02675218743</v>
+        <v>76114.00272273776</v>
       </c>
       <c r="D40">
-        <v>120038.7484640631</v>
+        <v>124755.7244346134</v>
       </c>
       <c r="E40">
         <v>20791.76983851864</v>
@@ -4573,45 +4573,45 @@
         <v>7700</v>
       </c>
       <c r="M40">
-        <v>3694.468403472998</v>
+        <v>3364.232640174618</v>
       </c>
       <c r="N40">
-        <v>4005.531596527002</v>
+        <v>4335.767359825382</v>
       </c>
       <c r="O40">
-        <v>500.6914495658752</v>
+        <v>541.9709199781728</v>
       </c>
       <c r="P40">
-        <v>3504.840146961127</v>
+        <v>3793.79643984721</v>
       </c>
       <c r="Q40">
-        <v>5169.840146961127</v>
+        <v>5458.79643984721</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1278203113882143</v>
+        <v>0.1277820070941624</v>
       </c>
       <c r="T40">
         <v>1.597981911294785</v>
       </c>
       <c r="U40">
-        <v>0.07383661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.084197009984329</v>
+        <v>2.288783453334648</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1039206028103513</v>
+        <v>0.1026001353142626</v>
       </c>
       <c r="C41">
-        <v>69829.69992452624</v>
+        <v>72558.88875934537</v>
       </c>
       <c r="D41">
-        <v>119788.1511551355</v>
+        <v>122517.3399899546</v>
       </c>
       <c r="E41">
         <v>22108.49935725221</v>
@@ -4655,37 +4655,37 @@
         <v>7700</v>
       </c>
       <c r="M41">
-        <v>3791.691256195972</v>
+        <v>3596.551941519657</v>
       </c>
       <c r="N41">
-        <v>3908.308743804028</v>
+        <v>4103.448058480343</v>
       </c>
       <c r="O41">
-        <v>488.5385929755035</v>
+        <v>512.9310073100429</v>
       </c>
       <c r="P41">
-        <v>3419.770150828525</v>
+        <v>3590.5170511703</v>
       </c>
       <c r="Q41">
-        <v>5084.770150828524</v>
+        <v>5255.5170511703</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.129055503892232</v>
+        <v>0.129016622751103</v>
       </c>
       <c r="T41">
         <v>1.622046868437472</v>
       </c>
       <c r="U41">
-        <v>0.07383661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.030756061010372</v>
+        <v>2.1409394679134</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1072969375197171</v>
+        <v>0.1026882511898519</v>
       </c>
       <c r="C42">
-        <v>61936.30319555689</v>
+        <v>71052.38855049055</v>
       </c>
       <c r="D42">
-        <v>113211.4839448997</v>
+        <v>122327.5692998334</v>
       </c>
       <c r="E42">
         <v>23425.22887598578</v>
@@ -4737,45 +4737,45 @@
         <v>7700</v>
       </c>
       <c r="M42">
-        <v>4378.737489887833</v>
+        <v>3688.771222071443</v>
       </c>
       <c r="N42">
-        <v>3321.262510112167</v>
+        <v>4011.228777928557</v>
       </c>
       <c r="O42">
-        <v>415.1578137640208</v>
+        <v>501.4035972410696</v>
       </c>
       <c r="P42">
-        <v>2906.104696348146</v>
+        <v>3509.825180687487</v>
       </c>
       <c r="Q42">
-        <v>4571.104696348146</v>
+        <v>5174.825180687487</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1303318694797169</v>
+        <v>0.130292392263275</v>
       </c>
       <c r="T42">
         <v>1.646913990818248</v>
       </c>
       <c r="U42">
-        <v>0.08313661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y42">
-        <v>1.758497744562724</v>
+        <v>2.087415981215565</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1091857722290829</v>
+        <v>0.1027763670654412</v>
       </c>
       <c r="C43">
-        <v>57245.98094687904</v>
+        <v>69546.47531519627</v>
       </c>
       <c r="D43">
-        <v>109837.8912149554</v>
+        <v>122138.3855832726</v>
       </c>
       <c r="E43">
         <v>24741.95839471935</v>
@@ -4819,45 +4819,45 @@
         <v>7700</v>
       </c>
       <c r="M43">
-        <v>4741.939705394988</v>
+        <v>3780.990502623229</v>
       </c>
       <c r="N43">
-        <v>2958.060294605012</v>
+        <v>3919.009497376771</v>
       </c>
       <c r="O43">
-        <v>369.7575368256265</v>
+        <v>489.8761871720964</v>
       </c>
       <c r="P43">
-        <v>2588.302757779386</v>
+        <v>3429.133310204675</v>
       </c>
       <c r="Q43">
-        <v>4253.302757779386</v>
+        <v>5094.133310204676</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1316515016972861</v>
+        <v>0.1316114081995884</v>
       </c>
       <c r="T43">
         <v>1.672624066500067</v>
       </c>
       <c r="U43">
-        <v>0.08783661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.07685703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>1.623808078208918</v>
+        <v>2.036503396307868</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1094296069384487</v>
+        <v>0.1057309829410306</v>
       </c>
       <c r="C44">
-        <v>55508.34217582741</v>
+        <v>62208.28585447789</v>
       </c>
       <c r="D44">
-        <v>109416.9819626374</v>
+        <v>116116.9256412878</v>
       </c>
       <c r="E44">
         <v>26058.68791345292</v>
@@ -4901,45 +4901,45 @@
         <v>7700</v>
       </c>
       <c r="M44">
-        <v>4857.596771380232</v>
+        <v>4304.570373512131</v>
       </c>
       <c r="N44">
-        <v>2842.403228619768</v>
+        <v>3395.429626487869</v>
       </c>
       <c r="O44">
-        <v>355.300403577471</v>
+        <v>424.4287033109836</v>
       </c>
       <c r="P44">
-        <v>2487.102825042297</v>
+        <v>2971.000923176885</v>
       </c>
       <c r="Q44">
-        <v>4152.102825042297</v>
+        <v>4636.000923176885</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1330166384740818</v>
+        <v>0.1329759074440505</v>
       </c>
       <c r="T44">
         <v>1.699220696515742</v>
       </c>
       <c r="U44">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.585145981108706</v>
+        <v>1.788796402860876</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1096734416478146</v>
+        <v>0.1073547238166199</v>
       </c>
       <c r="C45">
-        <v>53773.91701852704</v>
+        <v>57828.52905170965</v>
       </c>
       <c r="D45">
-        <v>108999.2863240706</v>
+        <v>113053.8983572532</v>
       </c>
       <c r="E45">
         <v>27375.41743218649</v>
@@ -4983,37 +4983,37 @@
         <v>7700</v>
       </c>
       <c r="M45">
-        <v>4973.253837365475</v>
+        <v>4627.87568460166</v>
       </c>
       <c r="N45">
-        <v>2726.746162634525</v>
+        <v>3072.12431539834</v>
       </c>
       <c r="O45">
-        <v>340.8432703293156</v>
+        <v>384.0155394247925</v>
       </c>
       <c r="P45">
-        <v>2385.902892305209</v>
+        <v>2688.108775973547</v>
       </c>
       <c r="Q45">
-        <v>4050.902892305209</v>
+        <v>4353.108775973547</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1344296747869055</v>
+        <v>0.134388283854985</v>
       </c>
       <c r="T45">
         <v>1.726750541619686</v>
       </c>
       <c r="U45">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.548282121082922</v>
+        <v>1.663830345663827</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1099172763571804</v>
+        <v>0.1075452146922092</v>
       </c>
       <c r="C46">
-        <v>52042.66881135366</v>
+        <v>56163.0156443102</v>
       </c>
       <c r="D46">
-        <v>108584.7676356307</v>
+        <v>112705.1144685873</v>
       </c>
       <c r="E46">
         <v>28692.14695092006</v>
@@ -5065,37 +5065,37 @@
         <v>7700</v>
       </c>
       <c r="M46">
-        <v>5088.910903350718</v>
+        <v>4735.500700522629</v>
       </c>
       <c r="N46">
-        <v>2611.089096649282</v>
+        <v>2964.499299477371</v>
       </c>
       <c r="O46">
-        <v>326.3861370811602</v>
+        <v>370.5624124346714</v>
       </c>
       <c r="P46">
-        <v>2284.702959568122</v>
+        <v>2593.9368870427</v>
       </c>
       <c r="Q46">
-        <v>3949.702959568122</v>
+        <v>4258.9368870427</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1358931766823299</v>
+        <v>0.1358511022805957</v>
       </c>
       <c r="T46">
         <v>1.755263595477343</v>
       </c>
       <c r="U46">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.51309389105831</v>
+        <v>1.626016019626013</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1299932461317502</v>
+        <v>0.1077357055677986</v>
       </c>
       <c r="C47">
-        <v>24833.78507373758</v>
+        <v>54499.64769235469</v>
       </c>
       <c r="D47">
-        <v>82692.61341674825</v>
+        <v>112358.4760353654</v>
       </c>
       <c r="E47">
         <v>30008.87646965364</v>
@@ -5147,45 +5147,45 @@
         <v>7700</v>
       </c>
       <c r="M47">
-        <v>8107.956558143485</v>
+        <v>4843.125716443598</v>
       </c>
       <c r="N47">
-        <v>-407.9565581434854</v>
+        <v>2856.874283556402</v>
       </c>
       <c r="O47">
-        <v>-50.99456976793567</v>
+        <v>357.1092854445502</v>
       </c>
       <c r="P47">
-        <v>-356.9619883755497</v>
+        <v>2499.764998111852</v>
       </c>
       <c r="Q47">
-        <v>1308.03801162445</v>
+        <v>4164.764998111852</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1376846295967126</v>
+        <v>0.1373671141035014</v>
       </c>
       <c r="T47">
-        <v>1.790166039806897</v>
+        <v>1.784813487657096</v>
       </c>
       <c r="U47">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V47">
-        <v>0.1187105521715311</v>
+        <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.1205926663412405</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.9496844173722488</v>
+        <v>1.58988233030099</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1309036122983755</v>
+        <v>0.1079261964433879</v>
       </c>
       <c r="C48">
-        <v>22632.48020677437</v>
+        <v>52838.40546070519</v>
       </c>
       <c r="D48">
-        <v>81808.03806851861</v>
+        <v>112013.9633224494</v>
       </c>
       <c r="E48">
         <v>31325.60598838721</v>
@@ -5229,45 +5229,45 @@
         <v>7700</v>
       </c>
       <c r="M48">
-        <v>8288.133370546673</v>
+        <v>4950.750732364567</v>
       </c>
       <c r="N48">
-        <v>-588.1333705466732</v>
+        <v>2749.249267635433</v>
       </c>
       <c r="O48">
-        <v>-73.51667131833415</v>
+        <v>343.6561584544291</v>
       </c>
       <c r="P48">
-        <v>-514.616699228339</v>
+        <v>2405.593109181004</v>
       </c>
       <c r="Q48">
-        <v>1150.383300771661</v>
+        <v>4070.593109181004</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1393861968114666</v>
+        <v>0.1389392745124406</v>
       </c>
       <c r="T48">
-        <v>1.823317262766285</v>
+        <v>1.815457820287951</v>
       </c>
       <c r="U48">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V48">
-        <v>0.1161298879938891</v>
+        <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.1209457956960513</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.9290391039511131</v>
+        <v>1.555319670946621</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.1318139784650009</v>
+        <v>0.1081166873189772</v>
       </c>
       <c r="C49">
-        <v>20449.8999118686</v>
+        <v>51179.26945553078</v>
       </c>
       <c r="D49">
-        <v>80942.18729234641</v>
+        <v>111671.5568360086</v>
       </c>
       <c r="E49">
         <v>32642.33550712078</v>
@@ -5311,45 +5311,45 @@
         <v>7700</v>
       </c>
       <c r="M49">
-        <v>8468.310182949861</v>
+        <v>5058.375748285535</v>
       </c>
       <c r="N49">
-        <v>-768.310182949861</v>
+        <v>2641.624251714465</v>
       </c>
       <c r="O49">
-        <v>-96.03877286873262</v>
+        <v>330.2030314643081</v>
       </c>
       <c r="P49">
-        <v>-672.2714100811284</v>
+        <v>2311.421220250157</v>
       </c>
       <c r="Q49">
-        <v>992.7285899188716</v>
+        <v>3976.421220250157</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1411519741097961</v>
+        <v>0.1405707617292642</v>
       </c>
       <c r="T49">
-        <v>1.857719475271309</v>
+        <v>1.847258542829405</v>
       </c>
       <c r="U49">
-        <v>0.1368366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V49">
-        <v>0.1136590393131681</v>
+        <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.1212838982698062</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.9092723145053448</v>
+        <v>1.52222776305414</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1327243446316262</v>
+        <v>0.1142711781945665</v>
       </c>
       <c r="C50">
-        <v>18285.45587684069</v>
+        <v>39825.00888019554</v>
       </c>
       <c r="D50">
-        <v>80094.47277605206</v>
+        <v>101634.0257794069</v>
       </c>
       <c r="E50">
         <v>33959.06502585434</v>
@@ -5393,45 +5393,45 @@
         <v>7700</v>
       </c>
       <c r="M50">
-        <v>8648.486995353049</v>
+        <v>6063.483604175305</v>
       </c>
       <c r="N50">
-        <v>-948.4869953530488</v>
+        <v>1636.516395824695</v>
       </c>
       <c r="O50">
-        <v>-118.5608744191311</v>
+        <v>204.5645494780869</v>
       </c>
       <c r="P50">
-        <v>-829.9261209339177</v>
+        <v>1431.951846346608</v>
       </c>
       <c r="Q50">
-        <v>835.0738790660823</v>
+        <v>3096.951846346608</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1429856659195999</v>
+        <v>0.1422649984544273</v>
       </c>
       <c r="T50">
-        <v>1.893444849795757</v>
+        <v>1.880282370083991</v>
       </c>
       <c r="U50">
-        <v>0.1368366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V50">
-        <v>0.1112911426608104</v>
+        <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.1216079132363214</v>
+        <v>0.08394453957971733</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.8903291412864835</v>
+        <v>1.26989705962061</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1336347107982515</v>
+        <v>0.1273025599873987</v>
       </c>
       <c r="C51">
-        <v>16138.58417984584</v>
+        <v>22258.092946719</v>
       </c>
       <c r="D51">
-        <v>79264.33059779079</v>
+        <v>85383.83936466395</v>
       </c>
       <c r="E51">
         <v>35275.79454458792</v>
@@ -5475,37 +5475,37 @@
         <v>7700</v>
       </c>
       <c r="M51">
-        <v>8828.663807756238</v>
+        <v>8035.070926815517</v>
       </c>
       <c r="N51">
-        <v>-1128.663807756238</v>
+        <v>-335.0709268155169</v>
       </c>
       <c r="O51">
-        <v>-141.0829759695298</v>
+        <v>-41.88386585193962</v>
       </c>
       <c r="P51">
-        <v>-987.5808317867086</v>
+        <v>-293.1870609635773</v>
       </c>
       <c r="Q51">
-        <v>677.4191682132914</v>
+        <v>1371.812939036423</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.144891267212141</v>
+        <v>0.1442929322889002</v>
       </c>
       <c r="T51">
-        <v>1.930571219399595</v>
+        <v>1.919810575109129</v>
       </c>
       <c r="U51">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1090198948514061</v>
+        <v>0.1197873682468489</v>
       </c>
       <c r="W51">
-        <v>0.1219187031021624</v>
+        <v>0.1096187031021625</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8721591588112491</v>
+        <v>0.9582989459747914</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1345450769648769</v>
+        <v>0.128089926154024</v>
       </c>
       <c r="C52">
-        <v>14008.74403836759</v>
+        <v>20124.3940924379</v>
       </c>
       <c r="D52">
-        <v>78451.2199750461</v>
+        <v>84566.87002911641</v>
       </c>
       <c r="E52">
         <v>36592.52406332149</v>
@@ -5557,37 +5557,37 @@
         <v>7700</v>
       </c>
       <c r="M52">
-        <v>9008.840620159426</v>
+        <v>8199.051966138282</v>
       </c>
       <c r="N52">
-        <v>-1308.840620159426</v>
+        <v>-499.0519661382823</v>
       </c>
       <c r="O52">
-        <v>-163.6050775199283</v>
+        <v>-62.38149576728529</v>
       </c>
       <c r="P52">
-        <v>-1145.235542639498</v>
+        <v>-436.670470370997</v>
       </c>
       <c r="Q52">
-        <v>519.7644573605021</v>
+        <v>1228.329529629003</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1468730925563839</v>
+        <v>0.1462627909346782</v>
       </c>
       <c r="T52">
-        <v>1.969182643787587</v>
+        <v>1.958206786611311</v>
       </c>
       <c r="U52">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V52">
-        <v>0.106839496954378</v>
+        <v>0.1173916208819119</v>
       </c>
       <c r="W52">
-        <v>0.1222170613733699</v>
+        <v>0.1099170613733699</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8547159756350242</v>
+        <v>0.9391329670552956</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1354554431315022</v>
+        <v>0.1288772923206494</v>
       </c>
       <c r="C53">
-        <v>11895.41663442799</v>
+        <v>18006.18091411017</v>
       </c>
       <c r="D53">
-        <v>77654.62208984008</v>
+        <v>83765.38636952225</v>
       </c>
       <c r="E53">
         <v>37909.25358205505</v>
@@ -5639,37 +5639,37 @@
         <v>7700</v>
       </c>
       <c r="M53">
-        <v>9189.017432562616</v>
+        <v>8363.033005461048</v>
       </c>
       <c r="N53">
-        <v>-1489.017432562616</v>
+        <v>-663.0330054610477</v>
       </c>
       <c r="O53">
-        <v>-186.127179070327</v>
+        <v>-82.87912568263096</v>
       </c>
       <c r="P53">
-        <v>-1302.890253492289</v>
+        <v>-580.1538797784167</v>
       </c>
       <c r="Q53">
-        <v>362.1097465077112</v>
+        <v>1084.846120221583</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.148935808731004</v>
+        <v>0.1483130519741614</v>
       </c>
       <c r="T53">
-        <v>2.009370044681211</v>
+        <v>1.998170190419705</v>
       </c>
       <c r="U53">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1047446048572333</v>
+        <v>0.1150898243940313</v>
       </c>
       <c r="W53">
-        <v>0.1225037193202162</v>
+        <v>0.1102037193202162</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8379568388578668</v>
+        <v>0.9207185951522506</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1363658092981276</v>
+        <v>0.1296646584872747</v>
       </c>
       <c r="C54">
-        <v>9798.104010651368</v>
+        <v>15903.01724836734</v>
       </c>
       <c r="D54">
-        <v>76874.03898479702</v>
+        <v>82978.95222251299</v>
       </c>
       <c r="E54">
         <v>39225.98310078862</v>
@@ -5721,37 +5721,37 @@
         <v>7700</v>
       </c>
       <c r="M54">
-        <v>9369.194244965804</v>
+        <v>8527.014044783813</v>
       </c>
       <c r="N54">
-        <v>-1669.194244965804</v>
+        <v>-827.014044783813</v>
       </c>
       <c r="O54">
-        <v>-208.6492806207254</v>
+        <v>-103.3767555979766</v>
       </c>
       <c r="P54">
-        <v>-1460.544964345078</v>
+        <v>-723.6372891858364</v>
       </c>
       <c r="Q54">
-        <v>204.4550356549219</v>
+        <v>941.3627108141636</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1510844714128999</v>
+        <v>0.1504487405569565</v>
       </c>
       <c r="T54">
-        <v>2.051231920612071</v>
+        <v>2.03979873605345</v>
       </c>
       <c r="U54">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1027302855330558</v>
+        <v>0.1128765585403</v>
       </c>
       <c r="W54">
-        <v>0.1227793519614147</v>
+        <v>0.1104793519614147</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8218422842644463</v>
+        <v>0.9030124683223997</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1372761754647529</v>
+        <v>0.1304520246539001</v>
       </c>
       <c r="C55">
-        <v>7716.328032246325</v>
+        <v>13814.48315922747</v>
       </c>
       <c r="D55">
-        <v>76108.99252512555</v>
+        <v>82207.14765210669</v>
       </c>
       <c r="E55">
         <v>40542.71261952219</v>
@@ -5803,37 +5803,37 @@
         <v>7700</v>
       </c>
       <c r="M55">
-        <v>9549.371057368993</v>
+        <v>8690.99508410658</v>
       </c>
       <c r="N55">
-        <v>-1849.371057368993</v>
+        <v>-990.9950841065802</v>
       </c>
       <c r="O55">
-        <v>-231.1713821711242</v>
+        <v>-123.8743855133225</v>
       </c>
       <c r="P55">
-        <v>-1618.199675197869</v>
+        <v>-867.1206985932577</v>
       </c>
       <c r="Q55">
-        <v>46.80032480213094</v>
+        <v>797.8793014067423</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1533245665493446</v>
+        <v>0.1526753095049768</v>
       </c>
       <c r="T55">
-        <v>2.094875152965519</v>
+        <v>2.08319870916097</v>
       </c>
       <c r="U55">
-        <v>0.1368366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.1007919782588472</v>
+        <v>0.1107468121527471</v>
       </c>
       <c r="W55">
-        <v>0.1230445833708698</v>
+        <v>0.1107445833708698</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8063358260707774</v>
+        <v>0.8859744972219769</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1851245355791694</v>
+        <v>0.1312393908205254</v>
       </c>
       <c r="C56">
-        <v>-19738.58645978865</v>
+        <v>11740.17419037806</v>
       </c>
       <c r="D56">
-        <v>49970.80755182416</v>
+        <v>81449.56820199087</v>
       </c>
       <c r="E56">
         <v>41859.44213825578</v>
@@ -5885,45 +5885,45 @@
         <v>7700</v>
       </c>
       <c r="M56">
-        <v>15766.22602135811</v>
+        <v>8854.976123429347</v>
       </c>
       <c r="N56">
-        <v>-8066.226021358112</v>
+        <v>-1154.976123429347</v>
       </c>
       <c r="O56">
-        <v>-1008.278252669764</v>
+        <v>-144.3720154286684</v>
       </c>
       <c r="P56">
-        <v>-7057.947768688348</v>
+        <v>-1010.604108000679</v>
       </c>
       <c r="Q56">
-        <v>-5392.947768688348</v>
+        <v>654.3958919993211</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1580359570130067</v>
+        <v>0.1549986857985633</v>
       </c>
       <c r="T56">
-        <v>2.186666035133038</v>
+        <v>2.128485637620991</v>
       </c>
       <c r="U56">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.06104821779772314</v>
+        <v>0.1086959452610295</v>
       </c>
       <c r="W56">
-        <v>0.2081999913947895</v>
+        <v>0.1109999913947895</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>0.4883857423817851</v>
+        <v>0.8695675620882364</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1868839017457948</v>
+        <v>0.1320267569871508</v>
       </c>
       <c r="C57">
-        <v>-21678.46962707978</v>
+        <v>9679.700658425398</v>
       </c>
       <c r="D57">
-        <v>49347.6539032666</v>
+        <v>80705.82418877177</v>
       </c>
       <c r="E57">
         <v>43176.17165698935</v>
@@ -5967,45 +5967,45 @@
         <v>7700</v>
       </c>
       <c r="M57">
-        <v>16058.19316990178</v>
+        <v>9018.957162752113</v>
       </c>
       <c r="N57">
-        <v>-8358.19316990178</v>
+        <v>-1318.957162752113</v>
       </c>
       <c r="O57">
-        <v>-1044.774146237723</v>
+        <v>-164.8696453440141</v>
       </c>
       <c r="P57">
-        <v>-7313.419023664058</v>
+        <v>-1154.087517408099</v>
       </c>
       <c r="Q57">
-        <v>-5648.419023664058</v>
+        <v>510.9124825919014</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1605300893910735</v>
+        <v>0.1574253232607536</v>
       </c>
       <c r="T57">
-        <v>2.23525861369155</v>
+        <v>2.175785318457013</v>
       </c>
       <c r="U57">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.0599382502014009</v>
+        <v>0.1067196553471927</v>
       </c>
       <c r="W57">
-        <v>0.208446111854203</v>
+        <v>0.111246111854203</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y57">
-        <v>0.4795060016112073</v>
+        <v>0.8537572427775413</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1886432679124201</v>
+        <v>0.1328141231537761</v>
       </c>
       <c r="C58">
-        <v>-23603.00232722035</v>
+        <v>7632.686984514527</v>
       </c>
       <c r="D58">
-        <v>48739.85072185959</v>
+        <v>79975.54003359447</v>
       </c>
       <c r="E58">
         <v>44492.90117572292</v>
@@ -6049,45 +6049,45 @@
         <v>7700</v>
       </c>
       <c r="M58">
-        <v>16350.16031844545</v>
+        <v>9182.938202074878</v>
       </c>
       <c r="N58">
-        <v>-8650.160318445449</v>
+        <v>-1482.938202074878</v>
       </c>
       <c r="O58">
-        <v>-1081.270039805681</v>
+        <v>-185.3672752593598</v>
       </c>
       <c r="P58">
-        <v>-7568.890278639768</v>
+        <v>-1297.570926815518</v>
       </c>
       <c r="Q58">
-        <v>-5903.890278639768</v>
+        <v>367.4290731844817</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1631375914226888</v>
+        <v>0.1599622624257707</v>
       </c>
       <c r="T58">
-        <v>2.286059945820903</v>
+        <v>2.225234984785581</v>
       </c>
       <c r="U58">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.05886792430494732</v>
+        <v>0.1048139472159928</v>
       </c>
       <c r="W58">
-        <v>0.2086834422972089</v>
+        <v>0.1114834422972089</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.4709433944395786</v>
+        <v>0.8385115777279424</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1904026340790454</v>
+        <v>0.1336014893204014</v>
       </c>
       <c r="C59">
-        <v>-25512.74486312713</v>
+        <v>5598.771061911917</v>
       </c>
       <c r="D59">
-        <v>48146.83770468638</v>
+        <v>79258.35362972543</v>
       </c>
       <c r="E59">
         <v>45809.63069445649</v>
@@ -6131,45 +6131,45 @@
         <v>7700</v>
       </c>
       <c r="M59">
-        <v>16642.12746698912</v>
+        <v>9346.919241397643</v>
       </c>
       <c r="N59">
-        <v>-8942.127466989117</v>
+        <v>-1646.919241397643</v>
       </c>
       <c r="O59">
-        <v>-1117.76593337364</v>
+        <v>-205.8649051747054</v>
       </c>
       <c r="P59">
-        <v>-7824.361533615478</v>
+        <v>-1441.054336222938</v>
       </c>
       <c r="Q59">
-        <v>-6159.361533615478</v>
+        <v>223.945663777062</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1658663726185653</v>
+        <v>0.1626171987612537</v>
       </c>
       <c r="T59">
-        <v>2.339224130607436</v>
+        <v>2.276984635594548</v>
       </c>
       <c r="U59">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.05783515370310614</v>
+        <v>0.1029751060367649</v>
       </c>
       <c r="W59">
-        <v>0.2089124453562497</v>
+        <v>0.1117124453562497</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y59">
-        <v>0.4626812296248491</v>
+        <v>0.8238008482941188</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1921620002456708</v>
+        <v>0.1343888554870268</v>
       </c>
       <c r="C60">
-        <v>-27408.23059689903</v>
+        <v>3577.603657313462</v>
       </c>
       <c r="D60">
-        <v>47568.08148964804</v>
+        <v>78553.91574386053</v>
       </c>
       <c r="E60">
         <v>47126.36021319004</v>
@@ -6213,45 +6213,45 @@
         <v>7700</v>
       </c>
       <c r="M60">
-        <v>16934.09461553278</v>
+        <v>9510.900280720407</v>
       </c>
       <c r="N60">
-        <v>-9234.094615532784</v>
+        <v>-1810.900280720407</v>
       </c>
       <c r="O60">
-        <v>-1154.261826941598</v>
+        <v>-226.3625350900509</v>
       </c>
       <c r="P60">
-        <v>-8079.832788591186</v>
+        <v>-1584.537745630356</v>
       </c>
       <c r="Q60">
-        <v>-6414.832788591186</v>
+        <v>80.46225436964392</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1687250957761502</v>
+        <v>0.1653985606365216</v>
       </c>
       <c r="T60">
-        <v>2.394919943240946</v>
+        <v>2.331198555489656</v>
       </c>
       <c r="U60">
-        <v>0.2217366166625341</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V60">
-        <v>0.0568379958806388</v>
+        <v>0.101199673174062</v>
       </c>
       <c r="W60">
-        <v>0.2091335517580822</v>
+        <v>0.1119335517580822</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.4547039670451104</v>
+        <v>0.8095973853924963</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1939213664122961</v>
+        <v>0.1849196156511418</v>
       </c>
       <c r="C61">
-        <v>-29289.96754981474</v>
+        <v>-26271.32858370775</v>
       </c>
       <c r="D61">
-        <v>47003.0740554659</v>
+        <v>50021.71302157289</v>
       </c>
       <c r="E61">
         <v>48443.08973192361</v>
@@ -6295,37 +6295,37 @@
         <v>7700</v>
       </c>
       <c r="M61">
-        <v>17226.06176407645</v>
+        <v>16060.75613999724</v>
       </c>
       <c r="N61">
-        <v>-9526.06176407645</v>
+        <v>-8360.75613999724</v>
       </c>
       <c r="O61">
-        <v>-1190.757720509556</v>
+        <v>-1045.094517499655</v>
       </c>
       <c r="P61">
-        <v>-8335.304043566894</v>
+        <v>-7315.661622497585</v>
       </c>
       <c r="Q61">
-        <v>-6670.304043566894</v>
+        <v>-5650.661622497585</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1717232688438611</v>
+        <v>0.1713531450361679</v>
       </c>
       <c r="T61">
-        <v>2.453332624783408</v>
+        <v>2.447264488700875</v>
       </c>
       <c r="U61">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.0558746400182551</v>
+        <v>0.05992868527547206</v>
       </c>
       <c r="W61">
-        <v>0.2093471630276492</v>
+        <v>0.1943471630276492</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4469971201460408</v>
+        <v>0.4794294822037765</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1956807325789214</v>
+        <v>0.1865289818177672</v>
       </c>
       <c r="C62">
-        <v>-31158.43988964126</v>
+        <v>-28160.10269122264</v>
       </c>
       <c r="D62">
-        <v>46451.33123437295</v>
+        <v>49449.66843279156</v>
       </c>
       <c r="E62">
         <v>49759.81925065718</v>
@@ -6377,37 +6377,37 @@
         <v>7700</v>
       </c>
       <c r="M62">
-        <v>17518.02891262012</v>
+        <v>16332.97234575991</v>
       </c>
       <c r="N62">
-        <v>-9818.028912620121</v>
+        <v>-8632.972345759907</v>
       </c>
       <c r="O62">
-        <v>-1227.253614077515</v>
+        <v>-1079.121543219988</v>
       </c>
       <c r="P62">
-        <v>-8590.775298542605</v>
+        <v>-7553.850802539919</v>
       </c>
       <c r="Q62">
-        <v>-6925.775298542605</v>
+        <v>-5888.850802539919</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1748713505649577</v>
+        <v>0.1744919736620721</v>
       </c>
       <c r="T62">
-        <v>2.514665940402993</v>
+        <v>2.508446100918397</v>
       </c>
       <c r="U62">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.05494339601795084</v>
+        <v>0.05892987385421418</v>
       </c>
       <c r="W62">
-        <v>0.2095536539215639</v>
+        <v>0.1945536539215639</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4395471681436067</v>
+        <v>0.4714389908337134</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1974400987455468</v>
+        <v>0.1881383479843925</v>
       </c>
       <c r="C63">
-        <v>-33014.10931440589</v>
+        <v>-30035.94101270349</v>
       </c>
       <c r="D63">
-        <v>45912.3913283419</v>
+        <v>48890.5596300443</v>
       </c>
       <c r="E63">
         <v>51076.54876939076</v>
@@ -6459,37 +6459,37 @@
         <v>7700</v>
       </c>
       <c r="M63">
-        <v>17809.99606116379</v>
+        <v>16605.18855152257</v>
       </c>
       <c r="N63">
-        <v>-10109.99606116379</v>
+        <v>-8905.188551522573</v>
       </c>
       <c r="O63">
-        <v>-1263.749507645474</v>
+        <v>-1113.148568940322</v>
       </c>
       <c r="P63">
-        <v>-8846.246553518316</v>
+        <v>-7792.039982582251</v>
       </c>
       <c r="Q63">
-        <v>-7181.246553518316</v>
+        <v>-6127.039982582251</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1781808723743156</v>
+        <v>0.1777917678585355</v>
       </c>
       <c r="T63">
-        <v>2.57914455425948</v>
+        <v>2.572765231711177</v>
       </c>
       <c r="U63">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.0540426846078205</v>
+        <v>0.05796381034840739</v>
       </c>
       <c r="W63">
-        <v>0.2097533746222356</v>
+        <v>0.1947533746222356</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.432341476862564</v>
+        <v>0.4637104827872591</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1991994649121721</v>
+        <v>0.1897477141510179</v>
       </c>
       <c r="C64">
-        <v>-34857.41634094364</v>
+        <v>-31899.27742269638</v>
       </c>
       <c r="D64">
-        <v>45385.81382053773</v>
+        <v>48343.95273878498</v>
       </c>
       <c r="E64">
         <v>52393.27828812433</v>
@@ -6541,37 +6541,37 @@
         <v>7700</v>
       </c>
       <c r="M64">
-        <v>18101.96320970746</v>
+        <v>16877.40475728524</v>
       </c>
       <c r="N64">
-        <v>-10401.96320970746</v>
+        <v>-9177.40475728524</v>
       </c>
       <c r="O64">
-        <v>-1300.245401213433</v>
+        <v>-1147.175594660655</v>
       </c>
       <c r="P64">
-        <v>-9101.717808494028</v>
+        <v>-8030.229162624584</v>
       </c>
       <c r="Q64">
-        <v>-7436.717808494028</v>
+        <v>-6365.229162624584</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1816645795420608</v>
+        <v>0.1812652354337601</v>
       </c>
       <c r="T64">
-        <v>2.647016779371572</v>
+        <v>2.640469579914103</v>
       </c>
       <c r="U64">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05317102840446854</v>
+        <v>0.05702891018149758</v>
       </c>
       <c r="W64">
-        <v>0.2099466527196598</v>
+        <v>0.1949466527196597</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4253682272357484</v>
+        <v>0.4562312814519807</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2009588310787975</v>
+        <v>0.1913570803176432</v>
       </c>
       <c r="C65">
-        <v>-36688.78150577885</v>
+        <v>-33750.52660704119</v>
       </c>
       <c r="D65">
-        <v>44871.17817443609</v>
+        <v>47809.43307317374</v>
       </c>
       <c r="E65">
         <v>53710.0078068579</v>
@@ -6623,37 +6623,37 @@
         <v>7700</v>
       </c>
       <c r="M65">
-        <v>18393.93035825113</v>
+        <v>17149.6209630479</v>
       </c>
       <c r="N65">
-        <v>-10693.93035825113</v>
+        <v>-9449.620963047902</v>
       </c>
       <c r="O65">
-        <v>-1336.741294781391</v>
+        <v>-1181.202620380988</v>
       </c>
       <c r="P65">
-        <v>-9357.189063469737</v>
+        <v>-8268.418342666915</v>
       </c>
       <c r="Q65">
-        <v>-7692.189063469737</v>
+        <v>-6603.418342666915</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1853365952053597</v>
+        <v>0.1849264580130509</v>
       </c>
       <c r="T65">
-        <v>2.718557773408642</v>
+        <v>2.711833622614484</v>
       </c>
       <c r="U65">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05232704382661985</v>
+        <v>0.05612368938496588</v>
       </c>
       <c r="W65">
-        <v>0.2101337950044673</v>
+        <v>0.1951337950044673</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4186163506129588</v>
+        <v>0.4489895150797271</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2027181972454228</v>
+        <v>0.1929664464842685</v>
       </c>
       <c r="C66">
-        <v>-38508.60648522083</v>
+        <v>-35590.08511207992</v>
       </c>
       <c r="D66">
-        <v>44368.08271372767</v>
+        <v>47286.60408686858</v>
       </c>
       <c r="E66">
         <v>55026.73732559147</v>
@@ -6705,37 +6705,37 @@
         <v>7700</v>
       </c>
       <c r="M66">
-        <v>18685.8975067948</v>
+        <v>17421.83716881057</v>
       </c>
       <c r="N66">
-        <v>-10985.8975067948</v>
+        <v>-9721.837168810569</v>
       </c>
       <c r="O66">
-        <v>-1373.23718834935</v>
+        <v>-1215.229646101321</v>
       </c>
       <c r="P66">
-        <v>-9612.660318445447</v>
+        <v>-8506.607522709248</v>
       </c>
       <c r="Q66">
-        <v>-7947.660318445447</v>
+        <v>-6841.607522709248</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1892126117388419</v>
+        <v>0.1887910818467468</v>
       </c>
       <c r="T66">
-        <v>2.794073267114437</v>
+        <v>2.787162334353775</v>
       </c>
       <c r="U66">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05150943376682891</v>
+        <v>0.05524675673832579</v>
       </c>
       <c r="W66">
-        <v>0.2103150890928746</v>
+        <v>0.1953150890928746</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4120754701346312</v>
+        <v>0.4419740539066063</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2044775634120481</v>
+        <v>0.1945758126508939</v>
       </c>
       <c r="C67">
-        <v>-40317.27514094421</v>
+        <v>-37418.33232576695</v>
       </c>
       <c r="D67">
-        <v>43876.14357673786</v>
+        <v>46775.08639191512</v>
       </c>
       <c r="E67">
         <v>56343.46684432504</v>
@@ -6787,37 +6787,37 @@
         <v>7700</v>
       </c>
       <c r="M67">
-        <v>18977.86465533846</v>
+        <v>17694.05337457323</v>
       </c>
       <c r="N67">
-        <v>-11277.86465533846</v>
+        <v>-9994.053374573232</v>
       </c>
       <c r="O67">
-        <v>-1409.733081917308</v>
+        <v>-1249.256671821654</v>
       </c>
       <c r="P67">
-        <v>-9868.131573421157</v>
+        <v>-8744.796702751577</v>
       </c>
       <c r="Q67">
-        <v>-8203.131573421157</v>
+        <v>-7079.796702751577</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1933101149313802</v>
+        <v>0.1928765413280824</v>
       </c>
       <c r="T67">
-        <v>2.873903931889136</v>
+        <v>2.86679554390674</v>
       </c>
       <c r="U67">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05071698093964692</v>
+        <v>0.05439680663465925</v>
       </c>
       <c r="W67">
-        <v>0.2104908049016386</v>
+        <v>0.1954908049016386</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4057358475171754</v>
+        <v>0.435174453077274</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2062369295786735</v>
+        <v>0.1961851788175192</v>
       </c>
       <c r="C68">
-        <v>-42115.15449677344</v>
+        <v>-39235.63139578238</v>
       </c>
       <c r="D68">
-        <v>43394.9937396422</v>
+        <v>46274.51684063326</v>
       </c>
       <c r="E68">
         <v>57660.19636305861</v>
@@ -6869,37 +6869,37 @@
         <v>7700</v>
       </c>
       <c r="M68">
-        <v>19269.83180388213</v>
+        <v>17966.2695803359</v>
       </c>
       <c r="N68">
-        <v>-11569.83180388213</v>
+        <v>-10266.2695803359</v>
       </c>
       <c r="O68">
-        <v>-1446.228975485267</v>
+        <v>-1283.283697541987</v>
       </c>
       <c r="P68">
-        <v>-10123.60282839687</v>
+        <v>-8982.985882793912</v>
       </c>
       <c r="Q68">
-        <v>-8458.602828396868</v>
+        <v>-7317.985882793912</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1976486477234796</v>
+        <v>0.1972023219553789</v>
       </c>
       <c r="T68">
-        <v>2.958430518121169</v>
+        <v>2.951113059903997</v>
       </c>
       <c r="U68">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.04994854183450076</v>
+        <v>0.05357261259474017</v>
       </c>
       <c r="W68">
-        <v>0.2106611959889249</v>
+        <v>0.1956611959889248</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3995883346760061</v>
+        <v>0.4285809007579213</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2079962957452988</v>
+        <v>0.1977945449841446</v>
       </c>
       <c r="C69">
-        <v>-43902.59565189564</v>
+        <v>-41042.33008931772</v>
       </c>
       <c r="D69">
-        <v>42924.28210325356</v>
+        <v>45784.54766583149</v>
       </c>
       <c r="E69">
         <v>58976.92588179218</v>
@@ -6951,37 +6951,37 @@
         <v>7700</v>
       </c>
       <c r="M69">
-        <v>19561.7989524258</v>
+        <v>18238.48578609856</v>
       </c>
       <c r="N69">
-        <v>-11861.7989524258</v>
+        <v>-10538.48578609856</v>
       </c>
       <c r="O69">
-        <v>-1482.724869053226</v>
+        <v>-1317.310723262321</v>
       </c>
       <c r="P69">
-        <v>-10379.07408337258</v>
+        <v>-9221.175062836244</v>
       </c>
       <c r="Q69">
-        <v>-8714.074083372579</v>
+        <v>-7556.175062836244</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2022501218969184</v>
+        <v>0.201790271105542</v>
       </c>
       <c r="T69">
-        <v>3.048079927761205</v>
+        <v>3.040540728385937</v>
       </c>
       <c r="U69">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.04920304121010522</v>
+        <v>0.05277302136198284</v>
       </c>
       <c r="W69">
-        <v>0.2108265007750982</v>
+        <v>0.1958265007750981</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3936243296808417</v>
+        <v>0.4221841708958627</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2097556619119242</v>
+        <v>0.1994039111507699</v>
       </c>
       <c r="C70">
-        <v>-45679.93463527655</v>
+        <v>-42838.76159881186</v>
       </c>
       <c r="D70">
-        <v>42463.67263860624</v>
+        <v>45304.84567507094</v>
       </c>
       <c r="E70">
         <v>60293.65540052576</v>
@@ -7033,37 +7033,37 @@
         <v>7700</v>
       </c>
       <c r="M70">
-        <v>19853.76610096947</v>
+        <v>18510.70199186123</v>
       </c>
       <c r="N70">
-        <v>-12153.76610096947</v>
+        <v>-10810.70199186123</v>
       </c>
       <c r="O70">
-        <v>-1519.220762621184</v>
+        <v>-1351.337748982654</v>
       </c>
       <c r="P70">
-        <v>-10634.54533834829</v>
+        <v>-9459.364242878577</v>
       </c>
       <c r="Q70">
-        <v>-8969.545338348291</v>
+        <v>-7794.364242878577</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2071391882061971</v>
+        <v>0.2066649670775901</v>
       </c>
       <c r="T70">
-        <v>3.143332425503742</v>
+        <v>3.135557626147997</v>
       </c>
       <c r="U70">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.0484794670746625</v>
+        <v>0.05199694751842427</v>
       </c>
       <c r="W70">
-        <v>0.2109869436557957</v>
+        <v>0.1959869436557957</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3878357365973</v>
+        <v>0.4159755801473941</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2115150280785495</v>
+        <v>0.2010132773173953</v>
       </c>
       <c r="C71">
-        <v>-47447.49320564932</v>
+        <v>-44625.24529756024</v>
       </c>
       <c r="D71">
-        <v>42012.84358696704</v>
+        <v>44835.09149505613</v>
       </c>
       <c r="E71">
         <v>61610.38491925933</v>
@@ -7115,37 +7115,37 @@
         <v>7700</v>
       </c>
       <c r="M71">
-        <v>20145.73324951314</v>
+        <v>18782.9181976239</v>
       </c>
       <c r="N71">
-        <v>-12445.73324951314</v>
+        <v>-11082.9181976239</v>
       </c>
       <c r="O71">
-        <v>-1555.716656189143</v>
+        <v>-1385.364774702987</v>
       </c>
       <c r="P71">
-        <v>-10890.016593324</v>
+        <v>-9697.553422920912</v>
       </c>
       <c r="Q71">
-        <v>-9225.016593323999</v>
+        <v>-8032.553422920912</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.2123436781483325</v>
+        <v>0.211854159563964</v>
       </c>
       <c r="T71">
-        <v>3.244730245681282</v>
+        <v>3.23670464634632</v>
       </c>
       <c r="U71">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.04777686610256594</v>
+        <v>0.05124336856888188</v>
       </c>
       <c r="W71">
-        <v>0.2111427360182122</v>
+        <v>0.1961427360182122</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3822149288205275</v>
+        <v>0.4099469485510551</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2132743942451749</v>
+        <v>0.2026226434840206</v>
       </c>
       <c r="C72">
-        <v>-49205.57960107907</v>
+        <v>-46402.08744879797</v>
       </c>
       <c r="D72">
-        <v>41571.48671027087</v>
+        <v>44374.97886255196</v>
       </c>
       <c r="E72">
         <v>62927.1144379929</v>
@@ -7197,37 +7197,37 @@
         <v>7700</v>
       </c>
       <c r="M72">
-        <v>20437.70039805681</v>
+        <v>19055.13440338656</v>
       </c>
       <c r="N72">
-        <v>-12737.70039805681</v>
+        <v>-11355.13440338656</v>
       </c>
       <c r="O72">
-        <v>-1592.212549757101</v>
+        <v>-1419.39180042332</v>
       </c>
       <c r="P72">
-        <v>-11145.48784829971</v>
+        <v>-9935.742602963241</v>
       </c>
       <c r="Q72">
-        <v>-9480.48784829971</v>
+        <v>-8270.742602963241</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.2178951340866103</v>
+        <v>0.2173892982160961</v>
       </c>
       <c r="T72">
-        <v>3.352887920537325</v>
+        <v>3.34459480122453</v>
       </c>
       <c r="U72">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.04709433944395786</v>
+        <v>0.05051132044646929</v>
       </c>
       <c r="W72">
-        <v>0.211294077170274</v>
+        <v>0.1962940771702739</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3767547155516628</v>
+        <v>0.4040905635717543</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2150337604118002</v>
+        <v>0.204232009650646</v>
       </c>
       <c r="C73">
-        <v>-50954.48924177168</v>
+        <v>-48169.58187156564</v>
       </c>
       <c r="D73">
-        <v>41139.30658831181</v>
+        <v>43924.21395851784</v>
       </c>
       <c r="E73">
         <v>64243.84395672646</v>
@@ -7279,37 +7279,37 @@
         <v>7700</v>
       </c>
       <c r="M73">
-        <v>20729.66754660048</v>
+        <v>19327.35060914922</v>
       </c>
       <c r="N73">
-        <v>-13029.66754660048</v>
+        <v>-11627.35060914922</v>
       </c>
       <c r="O73">
-        <v>-1628.70844332506</v>
+        <v>-1453.418826143653</v>
       </c>
       <c r="P73">
-        <v>-11400.95910327542</v>
+        <v>-10173.93178300557</v>
       </c>
       <c r="Q73">
-        <v>-9735.959103275418</v>
+        <v>-8508.93178300557</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.223829449055114</v>
+        <v>0.2233061705683753</v>
       </c>
       <c r="T73">
-        <v>3.468504745383439</v>
+        <v>3.459925656439169</v>
       </c>
       <c r="U73">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04643103888840915</v>
+        <v>0.04979989339792747</v>
       </c>
       <c r="W73">
-        <v>0.2114411551912917</v>
+        <v>0.1964411551912917</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3714483111072733</v>
+        <v>0.3983991471834198</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2167931265784255</v>
+        <v>0.2058413758172713</v>
       </c>
       <c r="C74">
-        <v>-52694.50538949561</v>
+        <v>-49928.01056639953</v>
       </c>
       <c r="D74">
-        <v>40716.01995932145</v>
+        <v>43482.51478241752</v>
       </c>
       <c r="E74">
         <v>65560.57347546003</v>
@@ -7361,37 +7361,37 @@
         <v>7700</v>
       </c>
       <c r="M74">
-        <v>21021.63469514414</v>
+        <v>19599.56681491189</v>
       </c>
       <c r="N74">
-        <v>-13321.63469514414</v>
+        <v>-11899.56681491189</v>
       </c>
       <c r="O74">
-        <v>-1665.204336893018</v>
+        <v>-1487.445851863986</v>
       </c>
       <c r="P74">
-        <v>-11656.43035825113</v>
+        <v>-10412.1209630479</v>
       </c>
       <c r="Q74">
-        <v>-9991.430358251127</v>
+        <v>-8747.120963047901</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2301876436642252</v>
+        <v>0.2296456766601029</v>
       </c>
       <c r="T74">
-        <v>3.592379914861419</v>
+        <v>3.583494429883425</v>
       </c>
       <c r="U74">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04578616334829236</v>
+        <v>0.04910822821184516</v>
       </c>
       <c r="W74">
-        <v>0.2115841477117257</v>
+        <v>0.1965841477117256</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.366289306786339</v>
+        <v>0.3928658256947613</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2185524927450509</v>
+        <v>0.2074507419838966</v>
       </c>
       <c r="C75">
-        <v>-54425.89976670848</v>
+        <v>-51677.64430364623</v>
       </c>
       <c r="D75">
-        <v>40301.35510084215</v>
+        <v>43049.6105639044</v>
       </c>
       <c r="E75">
         <v>66877.3029941936</v>
@@ -7443,37 +7443,37 @@
         <v>7700</v>
       </c>
       <c r="M75">
-        <v>21313.60184368781</v>
+        <v>19871.78302067455</v>
       </c>
       <c r="N75">
-        <v>-13613.60184368781</v>
+        <v>-12171.78302067455</v>
       </c>
       <c r="O75">
-        <v>-1701.700230460977</v>
+        <v>-1521.472877584319</v>
       </c>
       <c r="P75">
-        <v>-11911.90161322684</v>
+        <v>-10650.31014309023</v>
       </c>
       <c r="Q75">
-        <v>-10246.90161322684</v>
+        <v>-8985.310143090233</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2370168156517891</v>
+        <v>0.2364547757956623</v>
       </c>
       <c r="T75">
-        <v>3.725431022819249</v>
+        <v>3.716216445805033</v>
       </c>
       <c r="U75">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04515895563119247</v>
+        <v>0.04843551275688837</v>
       </c>
       <c r="W75">
-        <v>0.21172322262886</v>
+        <v>0.19672322262886</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3612716450495398</v>
+        <v>0.387484102055107</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2203118589116762</v>
+        <v>0.209060108150522</v>
       </c>
       <c r="C76">
-        <v>-56148.93313823328</v>
+        <v>-53418.74317698092</v>
       </c>
       <c r="D76">
-        <v>39895.05124805091</v>
+        <v>42625.24120930328</v>
       </c>
       <c r="E76">
         <v>68194.03251292717</v>
@@ -7525,37 +7525,37 @@
         <v>7700</v>
       </c>
       <c r="M76">
-        <v>21605.56899223148</v>
+        <v>20143.99922643722</v>
       </c>
       <c r="N76">
-        <v>-13905.56899223148</v>
+        <v>-12443.99922643722</v>
       </c>
       <c r="O76">
-        <v>-1738.196124028935</v>
+        <v>-1555.499903304652</v>
       </c>
       <c r="P76">
-        <v>-12167.37286820255</v>
+        <v>-10888.49932313257</v>
       </c>
       <c r="Q76">
-        <v>-10502.37286820255</v>
+        <v>-9223.499323132568</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.2443713085614733</v>
+        <v>0.2437876517878032</v>
       </c>
       <c r="T76">
-        <v>3.86871683138922</v>
+        <v>3.859147847566765</v>
       </c>
       <c r="U76">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.04454869947401419</v>
+        <v>0.0477809788007142</v>
       </c>
       <c r="W76">
-        <v>0.2118585387644502</v>
+        <v>0.1968585387644502</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3563895957921136</v>
+        <v>0.3822478304057136</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2220712250783016</v>
+        <v>0.2106694743171473</v>
       </c>
       <c r="C77">
-        <v>-57863.8558581001</v>
+        <v>-55151.55712450654</v>
       </c>
       <c r="D77">
-        <v>39496.85804691767</v>
+        <v>42209.15678051122</v>
       </c>
       <c r="E77">
         <v>69510.76203166074</v>
@@ -7607,37 +7607,37 @@
         <v>7700</v>
       </c>
       <c r="M77">
-        <v>21897.53614077515</v>
+        <v>20416.21543219988</v>
       </c>
       <c r="N77">
-        <v>-14197.53614077515</v>
+        <v>-12716.21543219988</v>
       </c>
       <c r="O77">
-        <v>-1774.692017596894</v>
+        <v>-1589.526929024985</v>
       </c>
       <c r="P77">
-        <v>-12422.84412317826</v>
+        <v>-11126.6885031749</v>
       </c>
       <c r="Q77">
-        <v>-10757.84412317826</v>
+        <v>-9461.688503174897</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2523141609039323</v>
+        <v>0.2517071578593153</v>
       </c>
       <c r="T77">
-        <v>4.023465504644789</v>
+        <v>4.013513761469437</v>
       </c>
       <c r="U77">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04395471681436067</v>
+        <v>0.04714389908337135</v>
       </c>
       <c r="W77">
-        <v>0.211990246469758</v>
+        <v>0.196990246469758</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3516377345148853</v>
+        <v>0.3771511926669708</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2238305912449269</v>
+        <v>0.2122788404837727</v>
       </c>
       <c r="C78">
-        <v>-59570.90838396311</v>
+        <v>-56876.32641962817</v>
       </c>
       <c r="D78">
-        <v>39106.53503978824</v>
+        <v>41801.11700412317</v>
       </c>
       <c r="E78">
         <v>70827.49155039432</v>
@@ -7689,37 +7689,37 @@
         <v>7700</v>
       </c>
       <c r="M78">
-        <v>22189.50328931882</v>
+        <v>20688.43163796255</v>
       </c>
       <c r="N78">
-        <v>-14489.50328931882</v>
+        <v>-12988.43163796255</v>
       </c>
       <c r="O78">
-        <v>-1811.187911164853</v>
+        <v>-1623.553954745319</v>
       </c>
       <c r="P78">
-        <v>-12678.31537815397</v>
+        <v>-11364.87768321723</v>
       </c>
       <c r="Q78">
-        <v>-11013.31537815397</v>
+        <v>-9699.877683217233</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2609189176082628</v>
+        <v>0.2602866227701201</v>
       </c>
       <c r="T78">
-        <v>4.191109900671655</v>
+        <v>4.180743501530663</v>
       </c>
       <c r="U78">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.0433763652773296</v>
+        <v>0.04652358462174803</v>
       </c>
       <c r="W78">
-        <v>0.2121184881828208</v>
+        <v>0.1971184881828208</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3470109222186368</v>
+        <v>0.3721886769739843</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2255899574115522</v>
+        <v>0.213888206650398</v>
       </c>
       <c r="C79">
-        <v>-61270.3217613143</v>
+        <v>-58593.28213372774</v>
       </c>
       <c r="D79">
-        <v>38723.85118117062</v>
+        <v>41400.89080875718</v>
       </c>
       <c r="E79">
         <v>72144.22106912789</v>
@@ -7771,37 +7771,37 @@
         <v>7700</v>
       </c>
       <c r="M79">
-        <v>22481.47043786249</v>
+        <v>20960.64784372522</v>
       </c>
       <c r="N79">
-        <v>-14781.47043786249</v>
+        <v>-13260.64784372522</v>
       </c>
       <c r="O79">
-        <v>-1847.683804732811</v>
+        <v>-1657.580980465652</v>
       </c>
       <c r="P79">
-        <v>-12933.78663312968</v>
+        <v>-11603.06686325956</v>
       </c>
       <c r="Q79">
-        <v>-11268.78663312968</v>
+        <v>-9938.066863259563</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2702719140260134</v>
+        <v>0.2696121281079514</v>
       </c>
       <c r="T79">
-        <v>4.373332070266076</v>
+        <v>4.362514958118953</v>
       </c>
       <c r="U79">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04281303585814351</v>
+        <v>0.04591938222406299</v>
       </c>
       <c r="W79">
-        <v>0.2122433989422976</v>
+        <v>0.1972433989422976</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.342504286865148</v>
+        <v>0.367355057792504</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2273493235781776</v>
+        <v>0.2154975728170233</v>
       </c>
       <c r="C80">
-        <v>-62962.31807954243</v>
+        <v>-60302.64657251175</v>
       </c>
       <c r="D80">
-        <v>38348.58438167606</v>
+        <v>41008.25588870674</v>
       </c>
       <c r="E80">
         <v>73460.95058786146</v>
@@ -7853,37 +7853,37 @@
         <v>7700</v>
       </c>
       <c r="M80">
-        <v>22773.43758640616</v>
+        <v>21232.86404948788</v>
       </c>
       <c r="N80">
-        <v>-15073.43758640616</v>
+        <v>-13532.86404948788</v>
       </c>
       <c r="O80">
-        <v>-1884.17969830077</v>
+        <v>-1691.608006185985</v>
       </c>
       <c r="P80">
-        <v>-13189.25788810539</v>
+        <v>-11841.2560433019</v>
       </c>
       <c r="Q80">
-        <v>-11524.25788810539</v>
+        <v>-10176.2560433019</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2804751828453776</v>
+        <v>0.2797854066583129</v>
       </c>
       <c r="T80">
-        <v>4.572119891641806</v>
+        <v>4.560811092578906</v>
       </c>
       <c r="U80">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04226415078303911</v>
+        <v>0.04533067219554936</v>
       </c>
       <c r="W80">
-        <v>0.2123651068617878</v>
+        <v>0.1973651068617878</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3381132062643128</v>
+        <v>0.362645377564395</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2291086897448029</v>
+        <v>0.2171069389836487</v>
       </c>
       <c r="C81">
-        <v>-64647.11090172892</v>
+        <v>-62004.63368776274</v>
       </c>
       <c r="D81">
-        <v>37980.52107822314</v>
+        <v>40622.99829218932</v>
       </c>
       <c r="E81">
         <v>74777.68010659503</v>
@@ -7935,37 +7935,37 @@
         <v>7700</v>
       </c>
       <c r="M81">
-        <v>23065.40473494983</v>
+        <v>21505.08025525054</v>
       </c>
       <c r="N81">
-        <v>-15365.40473494983</v>
+        <v>-13805.08025525054</v>
       </c>
       <c r="O81">
-        <v>-1920.675591868729</v>
+        <v>-1725.635031906318</v>
       </c>
       <c r="P81">
-        <v>-13444.7291430811</v>
+        <v>-12079.44522334423</v>
       </c>
       <c r="Q81">
-        <v>-11779.7291430811</v>
+        <v>-10414.44522334423</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2916501915523004</v>
+        <v>0.2909275688801373</v>
       </c>
       <c r="T81">
-        <v>4.789839886481893</v>
+        <v>4.777992573177901</v>
       </c>
       <c r="U81">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04172916153262089</v>
+        <v>0.04475686621839051</v>
       </c>
       <c r="W81">
-        <v>0.2124837335681264</v>
+        <v>0.1974837335681264</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.333833292260967</v>
+        <v>0.3580549297471242</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2308680559114283</v>
+        <v>0.218716305150274</v>
       </c>
       <c r="C82">
-        <v>-66324.90566992838</v>
+        <v>-63699.44946609753</v>
       </c>
       <c r="D82">
-        <v>37619.45582875724</v>
+        <v>40244.9120325881</v>
       </c>
       <c r="E82">
         <v>76094.4096253286</v>
@@ -8017,37 +8017,37 @@
         <v>7700</v>
       </c>
       <c r="M82">
-        <v>23357.3718834935</v>
+        <v>21777.29646101321</v>
       </c>
       <c r="N82">
-        <v>-15657.3718834935</v>
+        <v>-14077.29646101321</v>
       </c>
       <c r="O82">
-        <v>-1957.171485436687</v>
+        <v>-1759.662057626651</v>
       </c>
       <c r="P82">
-        <v>-13700.20039805681</v>
+        <v>-12317.63440338656</v>
       </c>
       <c r="Q82">
-        <v>-12035.20039805681</v>
+        <v>-10652.63440338656</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.3039427011299154</v>
+        <v>0.3031839473241442</v>
       </c>
       <c r="T82">
-        <v>5.029331880805987</v>
+        <v>5.016892201836796</v>
       </c>
       <c r="U82">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04120754701346313</v>
+        <v>0.04419740539066063</v>
       </c>
       <c r="W82">
-        <v>0.2125993946068065</v>
+        <v>0.1975993946068065</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.329660376107705</v>
+        <v>0.3535792431252851</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2326274220780536</v>
+        <v>0.2203256713168993</v>
       </c>
       <c r="C83">
-        <v>-67995.90008754985</v>
+        <v>-65387.29229621583</v>
       </c>
       <c r="D83">
-        <v>37265.19092986934</v>
+        <v>39873.79872120336</v>
       </c>
       <c r="E83">
         <v>77411.13914406217</v>
@@ -8099,37 +8099,37 @@
         <v>7700</v>
       </c>
       <c r="M83">
-        <v>23649.33903203717</v>
+        <v>22049.51266677587</v>
       </c>
       <c r="N83">
-        <v>-15949.33903203717</v>
+        <v>-14349.51266677587</v>
       </c>
       <c r="O83">
-        <v>-1993.667379004646</v>
+        <v>-1793.689083346984</v>
       </c>
       <c r="P83">
-        <v>-13955.67165303252</v>
+        <v>-12555.82358342889</v>
       </c>
       <c r="Q83">
-        <v>-12290.67165303252</v>
+        <v>-10890.82358342889</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.3175291590841215</v>
+        <v>0.3167304708675202</v>
       </c>
       <c r="T83">
-        <v>5.294033558743146</v>
+        <v>5.280939159828207</v>
       </c>
       <c r="U83">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04069881186514877</v>
+        <v>0.04365175841052903</v>
       </c>
       <c r="W83">
-        <v>0.212712199817371</v>
+        <v>0.197712199817371</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3255904949211901</v>
+        <v>0.3492140672842322</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.234386788244679</v>
+        <v>0.2219350374835247</v>
       </c>
       <c r="C84">
-        <v>-69660.2844803342</v>
+        <v>-67068.35331601567</v>
       </c>
       <c r="D84">
-        <v>36917.53605581856</v>
+        <v>39509.4672201371</v>
       </c>
       <c r="E84">
         <v>78727.86866279574</v>
@@ -8181,37 +8181,37 @@
         <v>7700</v>
       </c>
       <c r="M84">
-        <v>23941.30618058083</v>
+        <v>22321.72887253854</v>
       </c>
       <c r="N84">
-        <v>-16241.30618058083</v>
+        <v>-14621.72887253854</v>
       </c>
       <c r="O84">
-        <v>-2030.163272572604</v>
+        <v>-1827.716109067318</v>
       </c>
       <c r="P84">
-        <v>-14211.14290800823</v>
+        <v>-12794.01276347122</v>
       </c>
       <c r="Q84">
-        <v>-12546.14290800823</v>
+        <v>-11129.01276347122</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3326252234776839</v>
+        <v>0.3317821636934936</v>
       </c>
       <c r="T84">
-        <v>5.588146534228876</v>
+        <v>5.574324668707551</v>
       </c>
       <c r="U84">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04020248489118354</v>
+        <v>0.04311941989332745</v>
       </c>
       <c r="W84">
-        <v>0.2128222536813364</v>
+        <v>0.1978222536813364</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3216198791294683</v>
+        <v>0.3449553591466196</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2361461544113043</v>
+        <v>0.22354440365015</v>
       </c>
       <c r="C85">
-        <v>-71318.24213731234</v>
+        <v>-68742.81674085092</v>
       </c>
       <c r="D85">
-        <v>36576.30791757401</v>
+        <v>39151.73331403542</v>
       </c>
       <c r="E85">
         <v>80044.59818152932</v>
@@ -8263,37 +8263,37 @@
         <v>7700</v>
       </c>
       <c r="M85">
-        <v>24233.27332912451</v>
+        <v>22593.94507830121</v>
       </c>
       <c r="N85">
-        <v>-16533.27332912451</v>
+        <v>-14893.94507830121</v>
       </c>
       <c r="O85">
-        <v>-2066.659166140563</v>
+        <v>-1861.743134787651</v>
       </c>
       <c r="P85">
-        <v>-14466.61416298394</v>
+        <v>-13032.20194351356</v>
       </c>
       <c r="Q85">
-        <v>-12801.61416298394</v>
+        <v>-11367.20194351356</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3494972954469593</v>
+        <v>0.3486046439107579</v>
       </c>
       <c r="T85">
-        <v>5.916861036242339</v>
+        <v>5.902226119807996</v>
       </c>
       <c r="U85">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.03971811760333795</v>
+        <v>0.0425999088102753</v>
       </c>
       <c r="W85">
-        <v>0.2129296556449653</v>
+        <v>0.1979296556449653</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3177449408267036</v>
+        <v>0.3407992704822025</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2379055205779296</v>
+        <v>0.2251537698167753</v>
       </c>
       <c r="C86">
-        <v>-72969.94963302781</v>
+        <v>-70410.86017411615</v>
       </c>
       <c r="D86">
-        <v>36241.32994059211</v>
+        <v>38800.41939950374</v>
       </c>
       <c r="E86">
         <v>81361.32770026287</v>
@@ -8345,37 +8345,37 @@
         <v>7700</v>
       </c>
       <c r="M86">
-        <v>24525.24047766817</v>
+        <v>22866.16128406387</v>
       </c>
       <c r="N86">
-        <v>-16825.24047766817</v>
+        <v>-15166.16128406387</v>
       </c>
       <c r="O86">
-        <v>-2103.155059708522</v>
+        <v>-1895.770160507984</v>
       </c>
       <c r="P86">
-        <v>-14722.08541795965</v>
+        <v>-13270.39112355589</v>
       </c>
       <c r="Q86">
-        <v>-13057.08541795965</v>
+        <v>-11605.39112355589</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3684783764123941</v>
+        <v>0.3675299341551801</v>
       </c>
       <c r="T86">
-        <v>6.286664851007482</v>
+        <v>6.271115252295992</v>
       </c>
       <c r="U86">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.03924528286996488</v>
+        <v>0.04209276703872442</v>
       </c>
       <c r="W86">
-        <v>0.213034500418984</v>
+        <v>0.198034500418984</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3139622629597191</v>
+        <v>0.3367421363097953</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.239664886744555</v>
+        <v>0.2267631359834007</v>
       </c>
       <c r="C87">
-        <v>-74615.57713221412</v>
+        <v>-72072.6549012586</v>
       </c>
       <c r="D87">
-        <v>35912.43196013936</v>
+        <v>38455.35419109487</v>
       </c>
       <c r="E87">
         <v>82678.05721899644</v>
@@ -8427,37 +8427,37 @@
         <v>7700</v>
       </c>
       <c r="M87">
-        <v>24817.20762621184</v>
+        <v>23138.37748982654</v>
       </c>
       <c r="N87">
-        <v>-17117.20762621184</v>
+        <v>-15438.37748982654</v>
       </c>
       <c r="O87">
-        <v>-2139.65095327648</v>
+        <v>-1929.797186228317</v>
       </c>
       <c r="P87">
-        <v>-14977.55667293536</v>
+        <v>-13508.58030359822</v>
       </c>
       <c r="Q87">
-        <v>-13312.55667293536</v>
+        <v>-11843.58030359822</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3899902681732204</v>
+        <v>0.3889785964321921</v>
       </c>
       <c r="T87">
-        <v>6.705775841074648</v>
+        <v>6.689189602449059</v>
       </c>
       <c r="U87">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.03878357365973</v>
+        <v>0.04159755801473942</v>
       </c>
       <c r="W87">
-        <v>0.2131368782571434</v>
+        <v>0.1981368782571434</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3102685892778401</v>
+        <v>0.3327804641179154</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2414242529111803</v>
+        <v>0.228372502150026</v>
       </c>
       <c r="C88">
-        <v>-76255.28867803095</v>
+        <v>-73728.36616823971</v>
       </c>
       <c r="D88">
-        <v>35589.44993305609</v>
+        <v>38116.37244284734</v>
       </c>
       <c r="E88">
         <v>83994.78673773001</v>
@@ -8509,37 +8509,37 @@
         <v>7700</v>
       </c>
       <c r="M88">
-        <v>25109.17477475551</v>
+        <v>23410.5936955892</v>
       </c>
       <c r="N88">
-        <v>-17409.17477475551</v>
+        <v>-15710.5936955892</v>
       </c>
       <c r="O88">
-        <v>-2176.146846844439</v>
+        <v>-1963.82421194865</v>
       </c>
       <c r="P88">
-        <v>-15233.02792791107</v>
+        <v>-13746.76948364055</v>
       </c>
       <c r="Q88">
-        <v>-13568.02792791107</v>
+        <v>-12081.76948364055</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.4145752873284504</v>
+        <v>0.4134913533202059</v>
       </c>
       <c r="T88">
-        <v>7.184759829722838</v>
+        <v>7.166988859766849</v>
       </c>
       <c r="U88">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.03833260187298895</v>
+        <v>0.04111386547968431</v>
       </c>
       <c r="W88">
-        <v>0.2132368752153456</v>
+        <v>0.1982368752153456</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3066608149839116</v>
+        <v>0.3289109238374746</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2431836190778056</v>
+        <v>0.2299818683166514</v>
       </c>
       <c r="C89">
-        <v>-77889.24246488549</v>
+        <v>-75378.15344539794</v>
       </c>
       <c r="D89">
-        <v>35272.22566493513</v>
+        <v>37783.31468442268</v>
       </c>
       <c r="E89">
         <v>85311.51625646358</v>
@@ -8591,37 +8591,37 @@
         <v>7700</v>
       </c>
       <c r="M89">
-        <v>25401.14192329918</v>
+        <v>23682.80990135187</v>
       </c>
       <c r="N89">
-        <v>-17701.14192329918</v>
+        <v>-15982.80990135187</v>
       </c>
       <c r="O89">
-        <v>-2212.642740412397</v>
+        <v>-1997.851237668983</v>
       </c>
       <c r="P89">
-        <v>-15488.49918288678</v>
+        <v>-13984.95866368288</v>
       </c>
       <c r="Q89">
-        <v>-13823.49918288678</v>
+        <v>-12319.95866368288</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.4429426171229466</v>
+        <v>0.4417753035756063</v>
       </c>
       <c r="T89">
-        <v>7.73743366277844</v>
+        <v>7.71829569513353</v>
       </c>
       <c r="U89">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.0378919972537592</v>
+        <v>0.04064129231325116</v>
       </c>
       <c r="W89">
-        <v>0.2133345733928995</v>
+        <v>0.1983345733928995</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3031359780300736</v>
+        <v>0.3251303385060093</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.244942985244431</v>
+        <v>0.2315912344832767</v>
       </c>
       <c r="C90">
-        <v>-79517.5910967919</v>
+        <v>-77022.17067759756</v>
       </c>
       <c r="D90">
-        <v>34960.60655176228</v>
+        <v>37456.02697095662</v>
       </c>
       <c r="E90">
         <v>86628.24577519715</v>
@@ -8673,37 +8673,37 @@
         <v>7700</v>
       </c>
       <c r="M90">
-        <v>25693.10907184285</v>
+        <v>23955.02610711453</v>
       </c>
       <c r="N90">
-        <v>-17993.10907184285</v>
+        <v>-16255.02610711453</v>
       </c>
       <c r="O90">
-        <v>-2249.138633980356</v>
+        <v>-2031.878263389316</v>
       </c>
       <c r="P90">
-        <v>-15743.97043786249</v>
+        <v>-14223.14784372521</v>
       </c>
       <c r="Q90">
-        <v>-14078.97043786249</v>
+        <v>-12558.14784372521</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.4760378352165256</v>
+        <v>0.4747732455402402</v>
       </c>
       <c r="T90">
-        <v>8.382219801343311</v>
+        <v>8.361487003061324</v>
       </c>
       <c r="U90">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.03746140637587557</v>
+        <v>0.04017945944605512</v>
       </c>
       <c r="W90">
-        <v>0.2134300511573272</v>
+        <v>0.1984300511573271</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2996912510070046</v>
+        <v>0.321435675568441</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2467023514110563</v>
+        <v>0.2332006006499021</v>
       </c>
       <c r="C91">
-        <v>-81140.48183215564</v>
+        <v>-78660.56652148812</v>
       </c>
       <c r="D91">
-        <v>34654.44533513211</v>
+        <v>37134.36064579964</v>
       </c>
       <c r="E91">
         <v>87944.97529393072</v>
@@ -8755,37 +8755,37 @@
         <v>7700</v>
       </c>
       <c r="M91">
-        <v>25985.07622038651</v>
+        <v>24227.2423128772</v>
       </c>
       <c r="N91">
-        <v>-18285.07622038651</v>
+        <v>-16527.2423128772</v>
       </c>
       <c r="O91">
-        <v>-2285.634527548314</v>
+        <v>-2065.905289109649</v>
       </c>
       <c r="P91">
-        <v>-15999.4416928382</v>
+        <v>-14461.33702376755</v>
       </c>
       <c r="Q91">
-        <v>-14334.4416928382</v>
+        <v>-12796.33702376755</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.5151503656907552</v>
+        <v>0.5137708133166258</v>
       </c>
       <c r="T91">
-        <v>9.144239783283613</v>
+        <v>9.121622185157811</v>
       </c>
       <c r="U91">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03704049169749495</v>
+        <v>0.03972800484553765</v>
       </c>
       <c r="W91">
-        <v>0.2135233833540149</v>
+        <v>0.1985233833540149</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2963239335799596</v>
+        <v>0.3178240387643012</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2484617175776817</v>
+        <v>0.2348099668165274</v>
       </c>
       <c r="C92">
-        <v>-82758.05681580755</v>
+        <v>-80293.48457064255</v>
       </c>
       <c r="D92">
-        <v>34353.59987021379</v>
+        <v>36818.17211537879</v>
       </c>
       <c r="E92">
         <v>89261.70481266431</v>
@@ -8837,37 +8837,37 @@
         <v>7700</v>
       </c>
       <c r="M92">
-        <v>26277.04336893019</v>
+        <v>24499.45851863986</v>
       </c>
       <c r="N92">
-        <v>-18577.04336893019</v>
+        <v>-16799.45851863986</v>
       </c>
       <c r="O92">
-        <v>-2322.130421116273</v>
+        <v>-2099.932314829983</v>
       </c>
       <c r="P92">
-        <v>-16254.91294781391</v>
+        <v>-14699.52620380988</v>
       </c>
       <c r="Q92">
-        <v>-14589.91294781391</v>
+        <v>-13034.52620380988</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5620854022598307</v>
+        <v>0.5605678946482883</v>
       </c>
       <c r="T92">
-        <v>10.05866376161197</v>
+        <v>10.03378440367359</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03662893067863388</v>
+        <v>0.03928658256947612</v>
       </c>
       <c r="W92">
-        <v>0.2136146415018873</v>
+        <v>0.1986146415018873</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2930314454290711</v>
+        <v>0.314292660555809</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.250221083744307</v>
+        <v>0.2364193329831527</v>
       </c>
       <c r="C93">
-        <v>-84370.45329905557</v>
+        <v>-81921.06356929071</v>
       </c>
       <c r="D93">
-        <v>34057.93290569934</v>
+        <v>36507.3226354642</v>
       </c>
       <c r="E93">
         <v>90578.43433139788</v>
@@ -8919,37 +8919,37 @@
         <v>7700</v>
       </c>
       <c r="M93">
-        <v>26569.01051747385</v>
+        <v>24771.67472440253</v>
       </c>
       <c r="N93">
-        <v>-18869.01051747385</v>
+        <v>-17071.67472440253</v>
       </c>
       <c r="O93">
-        <v>-2358.626314684232</v>
+        <v>-2133.959340550316</v>
       </c>
       <c r="P93">
-        <v>-16510.38420278962</v>
+        <v>-14937.71538385221</v>
       </c>
       <c r="Q93">
-        <v>-14845.38420278962</v>
+        <v>-13272.71538385221</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.6194504469553677</v>
+        <v>0.6177643273869871</v>
       </c>
       <c r="T93">
-        <v>11.17629306845775</v>
+        <v>11.1486493374151</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03622641495689066</v>
+        <v>0.03885486188189945</v>
       </c>
       <c r="W93">
-        <v>0.2137038939761802</v>
+        <v>0.1987038939761801</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2898113196551253</v>
+        <v>0.3108388950551957</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2519804499109323</v>
+        <v>0.2380286991497781</v>
       </c>
       <c r="C94">
-        <v>-85977.80384847059</v>
+        <v>-83543.4376153163</v>
       </c>
       <c r="D94">
-        <v>33767.31187501788</v>
+        <v>36201.67810817218</v>
       </c>
       <c r="E94">
         <v>91895.16385013144</v>
@@ -9001,37 +9001,37 @@
         <v>7700</v>
       </c>
       <c r="M94">
-        <v>26860.97766601752</v>
+        <v>25043.89093016519</v>
       </c>
       <c r="N94">
-        <v>-19160.97766601752</v>
+        <v>-17343.89093016519</v>
       </c>
       <c r="O94">
-        <v>-2395.12220825219</v>
+        <v>-2167.986366270649</v>
       </c>
       <c r="P94">
-        <v>-16765.85545776533</v>
+        <v>-15175.90456389455</v>
       </c>
       <c r="Q94">
-        <v>-15100.85545776533</v>
+        <v>-13510.90456389455</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6911567528247886</v>
+        <v>0.6892598683103608</v>
       </c>
       <c r="T94">
-        <v>12.57332970201497</v>
+        <v>12.542230504592</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03583264957692445</v>
+        <v>0.03843252642666142</v>
       </c>
       <c r="W94">
-        <v>0.2137912061792927</v>
+        <v>0.1987912061792927</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2866611966153957</v>
+        <v>0.3074602114132914</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2537398160775577</v>
+        <v>0.2396380653164034</v>
       </c>
       <c r="C95">
-        <v>-87580.2365440726</v>
+        <v>-85160.73635314133</v>
       </c>
       <c r="D95">
-        <v>33481.60869814945</v>
+        <v>35901.10888908072</v>
       </c>
       <c r="E95">
         <v>93211.89336886501</v>
@@ -9083,37 +9083,37 @@
         <v>7700</v>
       </c>
       <c r="M95">
-        <v>27152.94481456119</v>
+        <v>25316.10713592786</v>
       </c>
       <c r="N95">
-        <v>-19452.94481456119</v>
+        <v>-17616.10713592786</v>
       </c>
       <c r="O95">
-        <v>-2431.618101820149</v>
+        <v>-2202.013391990982</v>
       </c>
       <c r="P95">
-        <v>-17021.32671274104</v>
+        <v>-15414.09374393688</v>
       </c>
       <c r="Q95">
-        <v>-15356.32671274104</v>
+        <v>-13749.09374393688</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.7833505746569015</v>
+        <v>0.7811827066404122</v>
       </c>
       <c r="T95">
-        <v>14.36951965944569</v>
+        <v>14.33397771953371</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.0354473522696457</v>
+        <v>0.03801927345433172</v>
       </c>
       <c r="W95">
-        <v>0.2138766407006179</v>
+        <v>0.1988766407006179</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2835788181571656</v>
+        <v>0.3041541876346538</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2554991822441831</v>
+        <v>0.2412474314830288</v>
       </c>
       <c r="C96">
-        <v>-89177.87516754039</v>
+        <v>-86773.08515708119</v>
       </c>
       <c r="D96">
-        <v>33200.69959341522</v>
+        <v>35605.48960387441</v>
       </c>
       <c r="E96">
         <v>94528.62288759858</v>
@@ -9165,37 +9165,37 @@
         <v>7700</v>
       </c>
       <c r="M96">
-        <v>27444.91196310486</v>
+        <v>25588.32334169052</v>
       </c>
       <c r="N96">
-        <v>-19744.91196310486</v>
+        <v>-17888.32334169052</v>
       </c>
       <c r="O96">
-        <v>-2468.113995388107</v>
+        <v>-2236.040417711316</v>
       </c>
       <c r="P96">
-        <v>-17276.79796771675</v>
+        <v>-15652.28292397921</v>
       </c>
       <c r="Q96">
-        <v>-15611.79796771675</v>
+        <v>-13987.28292397921</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.9062756704330518</v>
+        <v>0.903746491080481</v>
       </c>
       <c r="T96">
-        <v>16.76443960268664</v>
+        <v>16.72297400612266</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03507025277741543</v>
+        <v>0.03761481309843458</v>
       </c>
       <c r="W96">
-        <v>0.2139602574661702</v>
+        <v>0.1989602574661702</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2805620222193234</v>
+        <v>0.3009185047874766</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2572585484108084</v>
+        <v>0.2428567976496541</v>
       </c>
       <c r="C97">
-        <v>-90770.8393810259</v>
+        <v>-88380.60530571469</v>
       </c>
       <c r="D97">
-        <v>32924.46489866328</v>
+        <v>35314.69897397449</v>
       </c>
       <c r="E97">
         <v>95845.35240633215</v>
@@ -9247,37 +9247,37 @@
         <v>7700</v>
       </c>
       <c r="M97">
-        <v>27736.87911164853</v>
+        <v>25860.53954745319</v>
       </c>
       <c r="N97">
-        <v>-20036.87911164853</v>
+        <v>-18160.53954745319</v>
       </c>
       <c r="O97">
-        <v>-2504.609888956066</v>
+        <v>-2270.067443431648</v>
       </c>
       <c r="P97">
-        <v>-17532.26922269246</v>
+        <v>-15890.47210402154</v>
       </c>
       <c r="Q97">
-        <v>-15867.26922269246</v>
+        <v>-14225.47210402154</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.078370804519663</v>
+        <v>1.075335789296578</v>
       </c>
       <c r="T97">
-        <v>20.11732752322397</v>
+        <v>20.06756880734721</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03470109222186368</v>
+        <v>0.03721886769739843</v>
       </c>
       <c r="W97">
-        <v>0.2140421138787635</v>
+        <v>0.1990421138787634</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2776087377749095</v>
+        <v>0.2977509415791875</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2590179145774337</v>
+        <v>0.2444661638162794</v>
       </c>
       <c r="C98">
-        <v>-92359.24489711526</v>
+        <v>-89983.41414777897</v>
       </c>
       <c r="D98">
-        <v>32652.78890130747</v>
+        <v>35028.61965064376</v>
       </c>
       <c r="E98">
         <v>97162.08192506571</v>
@@ -9329,37 +9329,37 @@
         <v>7700</v>
       </c>
       <c r="M98">
-        <v>28028.84626019219</v>
+        <v>26132.75575321585</v>
       </c>
       <c r="N98">
-        <v>-20328.84626019219</v>
+        <v>-18432.75575321585</v>
       </c>
       <c r="O98">
-        <v>-2541.105782524024</v>
+        <v>-2304.094469151981</v>
       </c>
       <c r="P98">
-        <v>-17787.74047766817</v>
+        <v>-16128.66128406387</v>
       </c>
       <c r="Q98">
-        <v>-16122.74047766817</v>
+        <v>-14463.66128406387</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.336513505649576</v>
+        <v>1.33271973662072</v>
       </c>
       <c r="T98">
-        <v>25.14665940402991</v>
+        <v>25.08446100918395</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03433962251121928</v>
+        <v>0.03683117115888387</v>
       </c>
       <c r="W98">
-        <v>0.2141222649494278</v>
+        <v>0.1991222649494277</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2747169800897542</v>
+        <v>0.2946493692710709</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.260777280744059</v>
+        <v>0.2460755299829048</v>
       </c>
       <c r="C99">
-        <v>-93943.20364044451</v>
+        <v>-91581.62526006592</v>
       </c>
       <c r="D99">
-        <v>32385.55967671181</v>
+        <v>34747.13805709039</v>
       </c>
       <c r="E99">
         <v>98478.81144379929</v>
@@ -9411,37 +9411,37 @@
         <v>7700</v>
       </c>
       <c r="M99">
-        <v>28320.81340873586</v>
+        <v>26404.97195897852</v>
       </c>
       <c r="N99">
-        <v>-20620.81340873586</v>
+        <v>-18704.97195897852</v>
       </c>
       <c r="O99">
-        <v>-2577.601676091983</v>
+        <v>-2338.121494872315</v>
       </c>
       <c r="P99">
-        <v>-18043.21173264388</v>
+        <v>-16366.8504641062</v>
       </c>
       <c r="Q99">
-        <v>-16378.21173264388</v>
+        <v>-14701.8504641062</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.766751340866101</v>
+        <v>1.761692982160959</v>
       </c>
       <c r="T99">
-        <v>33.52887920537322</v>
+        <v>33.44594801224527</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03398560578429949</v>
+        <v>0.03645146836343145</v>
       </c>
       <c r="W99">
-        <v>0.2142007634206969</v>
+        <v>0.1992007634206969</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2718848462743959</v>
+        <v>0.2916117469074516</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2625366469106844</v>
+        <v>0.2476848961495302</v>
       </c>
       <c r="C100">
-        <v>-95522.82390144333</v>
+        <v>-93175.34859776615</v>
       </c>
       <c r="D100">
-        <v>32122.66893444655</v>
+        <v>34470.14423812374</v>
       </c>
       <c r="E100">
         <v>99795.54096253286</v>
@@ -9493,37 +9493,37 @@
         <v>7700</v>
       </c>
       <c r="M100">
-        <v>28612.78055727953</v>
+        <v>26677.18816474118</v>
       </c>
       <c r="N100">
-        <v>-20912.78055727953</v>
+        <v>-18977.18816474118</v>
       </c>
       <c r="O100">
-        <v>-2614.097569659942</v>
+        <v>-2372.148520592648</v>
       </c>
       <c r="P100">
-        <v>-18298.68298761959</v>
+        <v>-16605.03964414854</v>
       </c>
       <c r="Q100">
-        <v>-16633.68298761959</v>
+        <v>-14940.03964414854</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.627227011299151</v>
+        <v>2.619639473241439</v>
       </c>
       <c r="T100">
-        <v>50.29331880805983</v>
+        <v>50.16892201836791</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03363881388854133</v>
+        <v>0.03607951460462092</v>
       </c>
       <c r="W100">
-        <v>0.2142776598823483</v>
+        <v>0.1992776598823483</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2691105111083306</v>
+        <v>0.2886361168369674</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2642960130773097</v>
+        <v>0.2492942623161555</v>
       </c>
       <c r="C101">
-        <v>-97098.21048265143</v>
+        <v>-94764.69063767901</v>
       </c>
       <c r="D101">
-        <v>31864.01187197203</v>
+        <v>34197.53171694444</v>
       </c>
       <c r="E101">
         <v>101112.2704812664</v>
@@ -9575,37 +9575,37 @@
         <v>7700</v>
       </c>
       <c r="M101">
-        <v>28904.7477058232</v>
+        <v>26949.40437050385</v>
       </c>
       <c r="N101">
-        <v>-21204.7477058232</v>
+        <v>-19249.40437050385</v>
       </c>
       <c r="O101">
-        <v>-2650.5934632279</v>
+        <v>-2406.175546312981</v>
       </c>
       <c r="P101">
-        <v>-18554.1542425953</v>
+        <v>-16843.22882419087</v>
       </c>
       <c r="Q101">
-        <v>-16889.1542425953</v>
+        <v>-15178.22882419087</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>5.208654022598302</v>
+        <v>5.193478946482879</v>
       </c>
       <c r="T101">
-        <v>100.5866376161196</v>
+        <v>100.3378440367358</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V101">
-        <v>0.03329902788966718</v>
+        <v>0.03571507506316011</v>
       </c>
       <c r="W101">
-        <v>0.2143530028801279</v>
+        <v>0.1993530028801279</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.2663922231173373</v>
+        <v>0.2857206005052808</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_healthcare_products.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_healthcare_products.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09916361616627895</v>
+        <v>0.09913098204186825</v>
       </c>
       <c r="C2">
-        <v>131801.232300168</v>
+        <v>130564.3011590379</v>
       </c>
       <c r="D2">
-        <v>130407.232300168</v>
+        <v>130487.0306777714</v>
       </c>
       <c r="E2">
-        <v>-29243.95187335703</v>
+        <v>-27927.22235462346</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1316.72951873357</v>
       </c>
       <c r="G2">
         <v>1394</v>
@@ -1457,28 +1457,28 @@
         <v>7700</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>74.04841319326279</v>
       </c>
       <c r="N2">
-        <v>7700</v>
+        <v>7625.951586806737</v>
       </c>
       <c r="O2">
-        <v>962.5</v>
+        <v>953.2439483508422</v>
       </c>
       <c r="P2">
-        <v>6737.5</v>
+        <v>6672.707638455895</v>
       </c>
       <c r="Q2">
-        <v>8402.5</v>
+        <v>8337.707638455895</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09916361616627895</v>
+        <v>0.09963526428896069</v>
       </c>
       <c r="T2">
-        <v>1.040156204727314</v>
+        <v>1.049349504516571</v>
       </c>
       <c r="U2">
         <v>0.05623661666253409</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>103.9860230347323</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09913098204186825</v>
+        <v>0.09909834791745757</v>
       </c>
       <c r="C3">
-        <v>130564.3011590379</v>
+        <v>129327.4677376414</v>
       </c>
       <c r="D3">
-        <v>130487.0306777714</v>
+        <v>130566.9267751085</v>
       </c>
       <c r="E3">
-        <v>-27927.22235462346</v>
+        <v>-26610.49283588989</v>
       </c>
       <c r="F3">
-        <v>1316.72951873357</v>
+        <v>2633.459037467141</v>
       </c>
       <c r="G3">
         <v>1394</v>
@@ -1539,28 +1539,28 @@
         <v>7700</v>
       </c>
       <c r="M3">
-        <v>74.04841319326279</v>
+        <v>148.0968263865256</v>
       </c>
       <c r="N3">
-        <v>7625.951586806737</v>
+        <v>7551.903173613475</v>
       </c>
       <c r="O3">
-        <v>953.2439483508422</v>
+        <v>943.9878967016843</v>
       </c>
       <c r="P3">
-        <v>6672.707638455895</v>
+        <v>6607.91527691179</v>
       </c>
       <c r="Q3">
-        <v>8337.707638455895</v>
+        <v>8272.91527691179</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09963526428896069</v>
+        <v>0.1001165378835339</v>
       </c>
       <c r="T3">
-        <v>1.049349504516571</v>
+        <v>1.058730422668873</v>
       </c>
       <c r="U3">
         <v>0.05623661666253409</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>103.9860230347323</v>
+        <v>51.99301151736616</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09909834791745757</v>
+        <v>0.09906571379304691</v>
       </c>
       <c r="C4">
-        <v>129327.4677376414</v>
+        <v>128090.7322155874</v>
       </c>
       <c r="D4">
-        <v>130566.9267751085</v>
+        <v>130646.9207717881</v>
       </c>
       <c r="E4">
-        <v>-26610.49283588989</v>
+        <v>-25293.76331715632</v>
       </c>
       <c r="F4">
-        <v>2633.459037467141</v>
+        <v>3950.188556200711</v>
       </c>
       <c r="G4">
         <v>1394</v>
@@ -1621,28 +1621,28 @@
         <v>7700</v>
       </c>
       <c r="M4">
-        <v>148.0968263865256</v>
+        <v>222.1452395797884</v>
       </c>
       <c r="N4">
-        <v>7551.903173613475</v>
+        <v>7477.854760420211</v>
       </c>
       <c r="O4">
-        <v>943.9878967016843</v>
+        <v>934.7318450525264</v>
       </c>
       <c r="P4">
-        <v>6607.91527691179</v>
+        <v>6543.122915367685</v>
       </c>
       <c r="Q4">
-        <v>8272.91527691179</v>
+        <v>8208.122915367685</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1001165378835339</v>
+        <v>0.1006077346450056</v>
       </c>
       <c r="T4">
-        <v>1.058730422668873</v>
+        <v>1.068304761814007</v>
       </c>
       <c r="U4">
         <v>0.05623661666253409</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>51.99301151736616</v>
+        <v>34.6620076782441</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09906571379304691</v>
+        <v>0.09903307966863623</v>
       </c>
       <c r="C5">
-        <v>128090.7322155874</v>
+        <v>126854.0947729253</v>
       </c>
       <c r="D5">
-        <v>130646.9207717881</v>
+        <v>130727.0128478595</v>
       </c>
       <c r="E5">
-        <v>-25293.76331715632</v>
+        <v>-23977.03379842275</v>
       </c>
       <c r="F5">
-        <v>3950.188556200711</v>
+        <v>5266.918074934281</v>
       </c>
       <c r="G5">
         <v>1394</v>
@@ -1703,28 +1703,28 @@
         <v>7700</v>
       </c>
       <c r="M5">
-        <v>222.1452395797884</v>
+        <v>296.1936527730512</v>
       </c>
       <c r="N5">
-        <v>7477.854760420211</v>
+        <v>7403.806347226949</v>
       </c>
       <c r="O5">
-        <v>934.7318450525264</v>
+        <v>925.4757934033686</v>
       </c>
       <c r="P5">
-        <v>6543.122915367685</v>
+        <v>6478.33055382358</v>
       </c>
       <c r="Q5">
-        <v>8208.122915367685</v>
+        <v>8143.33055382358</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1006077346450056</v>
+        <v>0.1011091646723412</v>
       </c>
       <c r="T5">
-        <v>1.068304761814007</v>
+        <v>1.078078566357997</v>
       </c>
       <c r="U5">
         <v>0.05623661666253409</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>34.6620076782441</v>
+        <v>25.99650575868307</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09903307966863623</v>
+        <v>0.09900044554422556</v>
       </c>
       <c r="C6">
-        <v>126854.0947729253</v>
+        <v>125617.555590146</v>
       </c>
       <c r="D6">
-        <v>130727.0128478595</v>
+        <v>130807.2031838139</v>
       </c>
       <c r="E6">
-        <v>-23977.03379842275</v>
+        <v>-22660.30427968918</v>
       </c>
       <c r="F6">
-        <v>5266.918074934281</v>
+        <v>6583.647593667852</v>
       </c>
       <c r="G6">
         <v>1394</v>
@@ -1785,28 +1785,28 @@
         <v>7700</v>
       </c>
       <c r="M6">
-        <v>296.1936527730512</v>
+        <v>370.2420659663139</v>
       </c>
       <c r="N6">
-        <v>7403.806347226949</v>
+        <v>7329.757934033686</v>
       </c>
       <c r="O6">
-        <v>925.4757934033686</v>
+        <v>916.2197417542108</v>
       </c>
       <c r="P6">
-        <v>6478.33055382358</v>
+        <v>6413.538192279475</v>
       </c>
       <c r="Q6">
-        <v>8143.33055382358</v>
+        <v>8078.538192279475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1011091646723412</v>
+        <v>0.1016211511213049</v>
       </c>
       <c r="T6">
-        <v>1.078078566357997</v>
+        <v>1.088058135208178</v>
       </c>
       <c r="U6">
         <v>0.05623661666253409</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>25.99650575868307</v>
+        <v>20.79720460694646</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09900044554422556</v>
+        <v>0.09896781141981488</v>
       </c>
       <c r="C7">
-        <v>125617.555590146</v>
+        <v>124381.1148481839</v>
       </c>
       <c r="D7">
-        <v>130807.2031838139</v>
+        <v>130887.4919605854</v>
       </c>
       <c r="E7">
-        <v>-22660.30427968918</v>
+        <v>-21343.57476095561</v>
       </c>
       <c r="F7">
-        <v>6583.647593667852</v>
+        <v>7900.377112401422</v>
       </c>
       <c r="G7">
         <v>1394</v>
@@ -1867,28 +1867,28 @@
         <v>7700</v>
       </c>
       <c r="M7">
-        <v>370.2420659663139</v>
+        <v>444.2904791595768</v>
       </c>
       <c r="N7">
-        <v>7329.757934033686</v>
+        <v>7255.709520840423</v>
       </c>
       <c r="O7">
-        <v>916.2197417542108</v>
+        <v>906.9636901050529</v>
       </c>
       <c r="P7">
-        <v>6413.538192279475</v>
+        <v>6348.745830735371</v>
       </c>
       <c r="Q7">
-        <v>8078.538192279475</v>
+        <v>8013.745830735371</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1016211511213049</v>
+        <v>0.1021440308989701</v>
       </c>
       <c r="T7">
-        <v>1.088058135208178</v>
+        <v>1.098250035310489</v>
       </c>
       <c r="U7">
         <v>0.05623661666253409</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>20.79720460694646</v>
+        <v>17.33100383912205</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09896781141981488</v>
+        <v>0.09893517729540421</v>
       </c>
       <c r="C8">
-        <v>124381.1148481839</v>
+        <v>123144.7727284177</v>
       </c>
       <c r="D8">
-        <v>130887.4919605854</v>
+        <v>130967.8793595526</v>
       </c>
       <c r="E8">
-        <v>-21343.57476095561</v>
+        <v>-20026.84524222204</v>
       </c>
       <c r="F8">
-        <v>7900.377112401421</v>
+        <v>9217.106631134991</v>
       </c>
       <c r="G8">
         <v>1394</v>
@@ -1949,28 +1949,28 @@
         <v>7700</v>
       </c>
       <c r="M8">
-        <v>444.2904791595767</v>
+        <v>518.3388923528395</v>
       </c>
       <c r="N8">
-        <v>7255.709520840423</v>
+        <v>7181.661107647161</v>
       </c>
       <c r="O8">
-        <v>906.9636901050529</v>
+        <v>897.7076384558951</v>
       </c>
       <c r="P8">
-        <v>6348.745830735371</v>
+        <v>6283.953469191266</v>
       </c>
       <c r="Q8">
-        <v>8013.745830735371</v>
+        <v>7948.953469191266</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1021440308989701</v>
+        <v>0.1026781554030366</v>
       </c>
       <c r="T8">
-        <v>1.098250035310489</v>
+        <v>1.108661116060162</v>
       </c>
       <c r="U8">
         <v>0.05623661666253409</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>17.33100383912205</v>
+        <v>14.8551461478189</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09893517729540421</v>
+        <v>0.09890254317099353</v>
       </c>
       <c r="C9">
-        <v>123144.7727284177</v>
+        <v>121908.5294126717</v>
       </c>
       <c r="D9">
-        <v>130967.8793595526</v>
+        <v>131048.3655625403</v>
       </c>
       <c r="E9">
-        <v>-20026.84524222204</v>
+        <v>-18710.11572348847</v>
       </c>
       <c r="F9">
-        <v>9217.106631134993</v>
+        <v>10533.83614986856</v>
       </c>
       <c r="G9">
         <v>1394</v>
@@ -2031,28 +2031,28 @@
         <v>7700</v>
       </c>
       <c r="M9">
-        <v>518.3388923528396</v>
+        <v>592.3873055461023</v>
       </c>
       <c r="N9">
-        <v>7181.66110764716</v>
+        <v>7107.612694453897</v>
       </c>
       <c r="O9">
-        <v>897.707638455895</v>
+        <v>888.4515868067372</v>
       </c>
       <c r="P9">
-        <v>6283.953469191265</v>
+        <v>6219.16110764716</v>
       </c>
       <c r="Q9">
-        <v>7948.953469191265</v>
+        <v>7884.16110764716</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1026781554030366</v>
+        <v>0.1032238913093654</v>
       </c>
       <c r="T9">
-        <v>1.108661116060162</v>
+        <v>1.119298524652219</v>
       </c>
       <c r="U9">
         <v>0.05623661666253409</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>14.8551461478189</v>
+        <v>12.99825287934154</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09890254317099353</v>
+        <v>0.09886990904658285</v>
       </c>
       <c r="C10">
-        <v>121908.5294126717</v>
+        <v>120672.385083218</v>
       </c>
       <c r="D10">
-        <v>131048.3655625403</v>
+        <v>131128.9507518202</v>
       </c>
       <c r="E10">
-        <v>-18710.11572348847</v>
+        <v>-17393.3862047549</v>
       </c>
       <c r="F10">
-        <v>10533.83614986856</v>
+        <v>11850.56566860213</v>
       </c>
       <c r="G10">
         <v>1394</v>
@@ -2113,28 +2113,28 @@
         <v>7700</v>
       </c>
       <c r="M10">
-        <v>592.3873055461023</v>
+        <v>666.435718739365</v>
       </c>
       <c r="N10">
-        <v>7107.612694453897</v>
+        <v>7033.564281260635</v>
       </c>
       <c r="O10">
-        <v>888.4515868067372</v>
+        <v>879.1955351575793</v>
       </c>
       <c r="P10">
-        <v>6219.16110764716</v>
+        <v>6154.368746103055</v>
       </c>
       <c r="Q10">
-        <v>7884.16110764716</v>
+        <v>7819.368746103055</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1032238913093654</v>
+        <v>0.1037816214114377</v>
       </c>
       <c r="T10">
-        <v>1.119298524652219</v>
+        <v>1.130169722444101</v>
       </c>
       <c r="U10">
         <v>0.05623661666253409</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>12.99825287934154</v>
+        <v>11.5540025594147</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09886990904658285</v>
+        <v>0.09883727492217219</v>
       </c>
       <c r="C11">
-        <v>120672.385083218</v>
+        <v>119436.3399227769</v>
       </c>
       <c r="D11">
-        <v>131128.9507518202</v>
+        <v>131209.6351101126</v>
       </c>
       <c r="E11">
-        <v>-17393.3862047549</v>
+        <v>-16076.65668602133</v>
       </c>
       <c r="F11">
-        <v>11850.56566860213</v>
+        <v>13167.2951873357</v>
       </c>
       <c r="G11">
         <v>1394</v>
@@ -2195,28 +2195,28 @@
         <v>7700</v>
       </c>
       <c r="M11">
-        <v>666.435718739365</v>
+        <v>740.4841319326277</v>
       </c>
       <c r="N11">
-        <v>7033.564281260635</v>
+        <v>6959.515868067372</v>
       </c>
       <c r="O11">
-        <v>879.1955351575793</v>
+        <v>869.9394835084215</v>
       </c>
       <c r="P11">
-        <v>6154.368746103055</v>
+        <v>6089.576384558951</v>
       </c>
       <c r="Q11">
-        <v>7819.368746103055</v>
+        <v>7754.576384558951</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1037816214114377</v>
+        <v>0.1043517455157783</v>
       </c>
       <c r="T11">
-        <v>1.130169722444101</v>
+        <v>1.141282502409137</v>
       </c>
       <c r="U11">
         <v>0.05623661666253409</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>11.5540025594147</v>
+        <v>10.39860230347323</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09883727492217219</v>
+        <v>0.09880464079776152</v>
       </c>
       <c r="C12">
-        <v>119436.3399227769</v>
+        <v>118200.3941145188</v>
       </c>
       <c r="D12">
-        <v>131209.6351101126</v>
+        <v>131290.418820588</v>
       </c>
       <c r="E12">
-        <v>-16076.65668602133</v>
+        <v>-14759.92716728776</v>
       </c>
       <c r="F12">
-        <v>13167.2951873357</v>
+        <v>14484.02470606927</v>
       </c>
       <c r="G12">
         <v>1394</v>
@@ -2277,28 +2277,28 @@
         <v>7700</v>
       </c>
       <c r="M12">
-        <v>740.4841319326279</v>
+        <v>814.5325451258906</v>
       </c>
       <c r="N12">
-        <v>6959.515868067372</v>
+        <v>6885.46745487411</v>
       </c>
       <c r="O12">
-        <v>869.9394835084215</v>
+        <v>860.6834318592637</v>
       </c>
       <c r="P12">
-        <v>6089.576384558951</v>
+        <v>6024.784023014846</v>
       </c>
       <c r="Q12">
-        <v>7754.576384558951</v>
+        <v>7689.784023014846</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1043517455157783</v>
+        <v>0.1049346813977445</v>
       </c>
       <c r="T12">
-        <v>1.141282502409137</v>
+        <v>1.152645007766645</v>
       </c>
       <c r="U12">
         <v>0.05623661666253409</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>10.39860230347323</v>
+        <v>9.453274821339303</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09880464079776152</v>
+        <v>0.09892950667335085</v>
       </c>
       <c r="C13">
-        <v>118200.3941145188</v>
+        <v>116575.1036071934</v>
       </c>
       <c r="D13">
-        <v>131290.418820588</v>
+        <v>130981.8578319963</v>
       </c>
       <c r="E13">
-        <v>-14759.92716728776</v>
+        <v>-13443.19764855419</v>
       </c>
       <c r="F13">
-        <v>14484.02470606927</v>
+        <v>15800.75422480284</v>
       </c>
       <c r="G13">
         <v>1394</v>
@@ -2359,45 +2359,45 @@
         <v>7700</v>
       </c>
       <c r="M13">
-        <v>814.5325451258906</v>
+        <v>912.2820896563577</v>
       </c>
       <c r="N13">
-        <v>6885.46745487411</v>
+        <v>6787.717910343642</v>
       </c>
       <c r="O13">
-        <v>860.6834318592637</v>
+        <v>848.4647387929552</v>
       </c>
       <c r="P13">
-        <v>6024.784023014846</v>
+        <v>5939.253171550687</v>
       </c>
       <c r="Q13">
-        <v>7689.784023014846</v>
+        <v>7604.253171550687</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1049346813977445</v>
+        <v>0.1055308658224827</v>
       </c>
       <c r="T13">
-        <v>1.152645007766645</v>
+        <v>1.164265751882278</v>
       </c>
       <c r="U13">
-        <v>0.05623661666253409</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.04920703957971732</v>
+        <v>0.05051953957971732</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>9.453274821339303</v>
+        <v>8.440371774590542</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09892950667335085</v>
+        <v>0.09890999754894017</v>
       </c>
       <c r="C14">
-        <v>116575.1036071934</v>
+        <v>115306.4882190928</v>
       </c>
       <c r="D14">
-        <v>130981.8578319963</v>
+        <v>131029.9719626292</v>
       </c>
       <c r="E14">
-        <v>-13443.19764855419</v>
+        <v>-12126.46812982062</v>
       </c>
       <c r="F14">
-        <v>15800.75422480284</v>
+        <v>17117.48374353641</v>
       </c>
       <c r="G14">
         <v>1394</v>
@@ -2441,28 +2441,28 @@
         <v>7700</v>
       </c>
       <c r="M14">
-        <v>912.2820896563577</v>
+        <v>988.3055971277208</v>
       </c>
       <c r="N14">
-        <v>6787.717910343642</v>
+        <v>6711.694402872279</v>
       </c>
       <c r="O14">
-        <v>848.4647387929552</v>
+        <v>838.9618003590349</v>
       </c>
       <c r="P14">
-        <v>5939.253171550687</v>
+        <v>5872.732602513244</v>
       </c>
       <c r="Q14">
-        <v>7604.253171550687</v>
+        <v>7537.732602513244</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1055308658224827</v>
+        <v>0.1061407556362953</v>
       </c>
       <c r="T14">
-        <v>1.164265751882278</v>
+        <v>1.176153639540799</v>
       </c>
       <c r="U14">
         <v>0.05773661666253409</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>8.440371774590542</v>
+        <v>7.791112407314347</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09890999754894017</v>
+        <v>0.09889048842452949</v>
       </c>
       <c r="C15">
-        <v>115306.4882190928</v>
+        <v>114037.9081919236</v>
       </c>
       <c r="D15">
-        <v>131029.9719626292</v>
+        <v>131078.1214541936</v>
       </c>
       <c r="E15">
-        <v>-12126.46812982062</v>
+        <v>-10809.73861108704</v>
       </c>
       <c r="F15">
-        <v>17117.48374353641</v>
+        <v>18434.21326226999</v>
       </c>
       <c r="G15">
         <v>1394</v>
@@ -2523,28 +2523,28 @@
         <v>7700</v>
       </c>
       <c r="M15">
-        <v>988.3055971277208</v>
+        <v>1064.329104599084</v>
       </c>
       <c r="N15">
-        <v>6711.694402872279</v>
+        <v>6635.670895400915</v>
       </c>
       <c r="O15">
-        <v>838.9618003590349</v>
+        <v>829.4588619251144</v>
       </c>
       <c r="P15">
-        <v>5872.732602513244</v>
+        <v>5806.212033475801</v>
       </c>
       <c r="Q15">
-        <v>7537.732602513244</v>
+        <v>7471.212033475801</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1061407556362953</v>
+        <v>0.1067648289341501</v>
       </c>
       <c r="T15">
-        <v>1.176153639540799</v>
+        <v>1.188317989703007</v>
       </c>
       <c r="U15">
         <v>0.05773661666253409</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>7.791112407314347</v>
+        <v>7.234604378220464</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09889048842452949</v>
+        <v>0.09887097930011882</v>
       </c>
       <c r="C16">
-        <v>114037.9081919236</v>
+        <v>112769.3635646824</v>
       </c>
       <c r="D16">
-        <v>131078.1214541936</v>
+        <v>131126.306345686</v>
       </c>
       <c r="E16">
-        <v>-10809.73861108704</v>
+        <v>-9493.009092353474</v>
       </c>
       <c r="F16">
-        <v>18434.21326226999</v>
+        <v>19750.94278100356</v>
       </c>
       <c r="G16">
         <v>1394</v>
@@ -2605,28 +2605,28 @@
         <v>7700</v>
       </c>
       <c r="M16">
-        <v>1064.329104599084</v>
+        <v>1140.352612070447</v>
       </c>
       <c r="N16">
-        <v>6635.670895400915</v>
+        <v>6559.647387929553</v>
       </c>
       <c r="O16">
-        <v>829.4588619251144</v>
+        <v>819.9559234911941</v>
       </c>
       <c r="P16">
-        <v>5806.212033475801</v>
+        <v>5739.691464438359</v>
       </c>
       <c r="Q16">
-        <v>7471.212033475801</v>
+        <v>7404.691464438359</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1067648289341501</v>
+        <v>0.1074035863096014</v>
       </c>
       <c r="T16">
-        <v>1.188317989703007</v>
+        <v>1.200768559869032</v>
       </c>
       <c r="U16">
         <v>0.05773661666253409</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>7.234604378220464</v>
+        <v>6.752297419672432</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09887097930011882</v>
+        <v>0.09908947017570813</v>
       </c>
       <c r="C17">
-        <v>112769.3635646824</v>
+        <v>110915.0062295754</v>
       </c>
       <c r="D17">
-        <v>131126.306345686</v>
+        <v>130588.6785293126</v>
       </c>
       <c r="E17">
-        <v>-9493.009092353477</v>
+        <v>-8176.279573619904</v>
       </c>
       <c r="F17">
-        <v>19750.94278100355</v>
+        <v>21067.67229973713</v>
       </c>
       <c r="G17">
         <v>1394</v>
@@ -2687,45 +2687,45 @@
         <v>7700</v>
       </c>
       <c r="M17">
-        <v>1140.352612070447</v>
+        <v>1252.191162451363</v>
       </c>
       <c r="N17">
-        <v>6559.647387929553</v>
+        <v>6447.808837548637</v>
       </c>
       <c r="O17">
-        <v>819.9559234911941</v>
+        <v>805.9761046935796</v>
       </c>
       <c r="P17">
-        <v>5739.691464438359</v>
+        <v>5641.832732855057</v>
       </c>
       <c r="Q17">
-        <v>7404.691464438359</v>
+        <v>7306.832732855057</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1074035863096014</v>
+        <v>0.1080575521939921</v>
       </c>
       <c r="T17">
-        <v>1.200768559869032</v>
+        <v>1.213515572181867</v>
       </c>
       <c r="U17">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05051953957971732</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>6.752297419672434</v>
+        <v>6.149220846540735</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09908947017570813</v>
+        <v>0.09908483605129746</v>
       </c>
       <c r="C18">
-        <v>110915.0062295754</v>
+        <v>109609.6338666066</v>
       </c>
       <c r="D18">
-        <v>130588.6785293126</v>
+        <v>130600.0356850773</v>
       </c>
       <c r="E18">
-        <v>-8176.279573619904</v>
+        <v>-6859.550054886331</v>
       </c>
       <c r="F18">
-        <v>21067.67229973713</v>
+        <v>22384.4018184707</v>
       </c>
       <c r="G18">
         <v>1394</v>
@@ -2769,28 +2769,28 @@
         <v>7700</v>
       </c>
       <c r="M18">
-        <v>1252.191162451363</v>
+        <v>1330.453110104574</v>
       </c>
       <c r="N18">
-        <v>6447.808837548637</v>
+        <v>6369.546889895426</v>
       </c>
       <c r="O18">
-        <v>805.9761046935796</v>
+        <v>796.1933612369282</v>
       </c>
       <c r="P18">
-        <v>5641.832732855057</v>
+        <v>5573.353528658497</v>
       </c>
       <c r="Q18">
-        <v>7306.832732855057</v>
+        <v>7238.353528658497</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1080575521939921</v>
+        <v>0.1087272762924645</v>
       </c>
       <c r="T18">
-        <v>1.213515572181867</v>
+        <v>1.226569741417902</v>
       </c>
       <c r="U18">
         <v>0.05943661666253409</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.149220846540735</v>
+        <v>5.787501973214808</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09908483605129746</v>
+        <v>0.0992062019268868</v>
       </c>
       <c r="C19">
-        <v>109609.6338666066</v>
+        <v>107996.1150778811</v>
       </c>
       <c r="D19">
-        <v>130600.0356850773</v>
+        <v>130303.2464150854</v>
       </c>
       <c r="E19">
-        <v>-6859.550054886331</v>
+        <v>-5542.820536152762</v>
       </c>
       <c r="F19">
-        <v>22384.4018184707</v>
+        <v>23701.13133720427</v>
       </c>
       <c r="G19">
         <v>1394</v>
@@ -2851,45 +2851,45 @@
         <v>7700</v>
       </c>
       <c r="M19">
-        <v>1330.453110104574</v>
+        <v>1427.675962827547</v>
       </c>
       <c r="N19">
-        <v>6369.546889895426</v>
+        <v>6272.324037172452</v>
       </c>
       <c r="O19">
-        <v>796.1933612369282</v>
+        <v>784.0405046465565</v>
       </c>
       <c r="P19">
-        <v>5573.353528658497</v>
+        <v>5488.283532525896</v>
       </c>
       <c r="Q19">
-        <v>7238.353528658497</v>
+        <v>7153.283532525896</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1087272762924645</v>
+        <v>0.1094133351250459</v>
       </c>
       <c r="T19">
-        <v>1.226569741417902</v>
+        <v>1.239942305025548</v>
       </c>
       <c r="U19">
-        <v>0.05943661666253409</v>
+        <v>0.06023661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>5.787501973214808</v>
+        <v>5.393380711369518</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09920620192688681</v>
+        <v>0.09920856780247611</v>
       </c>
       <c r="C20">
-        <v>107996.1150778811</v>
+        <v>106673.6134277726</v>
       </c>
       <c r="D20">
-        <v>130303.2464150853</v>
+        <v>130297.4742837105</v>
       </c>
       <c r="E20">
-        <v>-5542.820536152765</v>
+        <v>-4226.091017419192</v>
       </c>
       <c r="F20">
-        <v>23701.13133720426</v>
+        <v>25017.86085593784</v>
       </c>
       <c r="G20">
         <v>1394</v>
@@ -2933,28 +2933,28 @@
         <v>7700</v>
       </c>
       <c r="M20">
-        <v>1427.675962827547</v>
+        <v>1506.991294095744</v>
       </c>
       <c r="N20">
-        <v>6272.324037172453</v>
+        <v>6193.008705904255</v>
       </c>
       <c r="O20">
-        <v>784.0405046465567</v>
+        <v>774.1260882380319</v>
       </c>
       <c r="P20">
-        <v>5488.283532525897</v>
+        <v>5418.882617666223</v>
       </c>
       <c r="Q20">
-        <v>7153.283532525897</v>
+        <v>7083.882617666223</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1094133351250459</v>
+        <v>0.1101163336818887</v>
       </c>
       <c r="T20">
-        <v>1.239942305025548</v>
+        <v>1.253645055388939</v>
       </c>
       <c r="U20">
         <v>0.06023661666253409</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.393380711369519</v>
+        <v>5.10951856866586</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09920856780247611</v>
+        <v>0.09921093367806544</v>
       </c>
       <c r="C21">
-        <v>106673.6134277726</v>
+        <v>105351.1122890255</v>
       </c>
       <c r="D21">
-        <v>130297.4742837105</v>
+        <v>130291.7026636969</v>
       </c>
       <c r="E21">
-        <v>-4226.091017419192</v>
+        <v>-2909.361498685623</v>
       </c>
       <c r="F21">
-        <v>25017.86085593784</v>
+        <v>26334.59037467141</v>
       </c>
       <c r="G21">
         <v>1394</v>
@@ -3015,28 +3015,28 @@
         <v>7700</v>
       </c>
       <c r="M21">
-        <v>1506.991294095744</v>
+        <v>1586.306625363942</v>
       </c>
       <c r="N21">
-        <v>6193.008705904255</v>
+        <v>6113.693374636058</v>
       </c>
       <c r="O21">
-        <v>774.1260882380319</v>
+        <v>764.2116718295073</v>
       </c>
       <c r="P21">
-        <v>5418.882617666223</v>
+        <v>5349.481702806551</v>
       </c>
       <c r="Q21">
-        <v>7083.882617666223</v>
+        <v>7014.481702806551</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1101163336818887</v>
+        <v>0.1108369072026525</v>
       </c>
       <c r="T21">
-        <v>1.253645055388939</v>
+        <v>1.267690374511414</v>
       </c>
       <c r="U21">
         <v>0.06023661666253409</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.10951856866586</v>
+        <v>4.854042640232567</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09921093367806544</v>
+        <v>0.09921329955365477</v>
       </c>
       <c r="C22">
-        <v>105351.1122890255</v>
+        <v>104028.6116615719</v>
       </c>
       <c r="D22">
-        <v>130291.7026636969</v>
+        <v>130285.9315549768</v>
       </c>
       <c r="E22">
-        <v>-2909.361498685623</v>
+        <v>-1592.63197995205</v>
       </c>
       <c r="F22">
-        <v>26334.59037467141</v>
+        <v>27651.31989340498</v>
       </c>
       <c r="G22">
         <v>1394</v>
@@ -3097,28 +3097,28 @@
         <v>7700</v>
       </c>
       <c r="M22">
-        <v>1586.306625363942</v>
+        <v>1665.621956632139</v>
       </c>
       <c r="N22">
-        <v>6113.693374636058</v>
+        <v>6034.378043367861</v>
       </c>
       <c r="O22">
-        <v>764.2116718295073</v>
+        <v>754.2972554209827</v>
       </c>
       <c r="P22">
-        <v>5349.481702806551</v>
+        <v>5280.080787946878</v>
       </c>
       <c r="Q22">
-        <v>7014.481702806551</v>
+        <v>6945.080787946878</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1108369072026525</v>
+        <v>0.1115757230910305</v>
       </c>
       <c r="T22">
-        <v>1.267690374511414</v>
+        <v>1.282091271333193</v>
       </c>
       <c r="U22">
         <v>0.06023661666253409</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>4.854042640232567</v>
+        <v>4.622897752602444</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09921329955365477</v>
+        <v>0.09921566542924408</v>
       </c>
       <c r="C23">
-        <v>104028.6116615719</v>
+        <v>102706.1115453437</v>
       </c>
       <c r="D23">
-        <v>130285.9315549768</v>
+        <v>130280.1609574822</v>
       </c>
       <c r="E23">
-        <v>-1592.631979952053</v>
+        <v>-275.9024612184839</v>
       </c>
       <c r="F23">
-        <v>27651.31989340498</v>
+        <v>28968.04941213855</v>
       </c>
       <c r="G23">
         <v>1394</v>
@@ -3179,28 +3179,28 @@
         <v>7700</v>
       </c>
       <c r="M23">
-        <v>1665.621956632139</v>
+        <v>1744.937287900336</v>
       </c>
       <c r="N23">
-        <v>6034.378043367861</v>
+        <v>5955.062712099664</v>
       </c>
       <c r="O23">
-        <v>754.2972554209827</v>
+        <v>744.382839012458</v>
       </c>
       <c r="P23">
-        <v>5280.080787946878</v>
+        <v>5210.679873087206</v>
       </c>
       <c r="Q23">
-        <v>6945.080787946878</v>
+        <v>6875.679873087206</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1115757230910305</v>
+        <v>0.1123334829765465</v>
       </c>
       <c r="T23">
-        <v>1.282091271333193</v>
+        <v>1.296861421919632</v>
       </c>
       <c r="U23">
         <v>0.06023661666253409</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>4.622897752602444</v>
+        <v>4.412766036575061</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09921566542924408</v>
+        <v>0.09941928130483341</v>
       </c>
       <c r="C24">
-        <v>102706.1115453437</v>
+        <v>100894.6512432103</v>
       </c>
       <c r="D24">
-        <v>130280.1609574822</v>
+        <v>129785.4301740824</v>
       </c>
       <c r="E24">
-        <v>-275.9024612184839</v>
+        <v>1040.827057515089</v>
       </c>
       <c r="F24">
-        <v>28968.04941213855</v>
+        <v>30284.77893087212</v>
       </c>
       <c r="G24">
         <v>1394</v>
@@ -3261,45 +3261,45 @@
         <v>7700</v>
       </c>
       <c r="M24">
-        <v>1744.937287900336</v>
+        <v>1854.537398099405</v>
       </c>
       <c r="N24">
-        <v>5955.062712099664</v>
+        <v>5845.462601900595</v>
       </c>
       <c r="O24">
-        <v>744.382839012458</v>
+        <v>730.6828252375744</v>
       </c>
       <c r="P24">
-        <v>5210.679873087206</v>
+        <v>5114.779776663021</v>
       </c>
       <c r="Q24">
-        <v>6875.679873087206</v>
+        <v>6779.779776663021</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1123334829765465</v>
+        <v>0.1131109249370109</v>
       </c>
       <c r="T24">
-        <v>1.296861421919632</v>
+        <v>1.312015212781044</v>
       </c>
       <c r="U24">
-        <v>0.06023661666253409</v>
+        <v>0.06123661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.412766036575061</v>
+        <v>4.1519788211827</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09941928130483341</v>
+        <v>0.09943039718042274</v>
       </c>
       <c r="C25">
-        <v>100894.6512432103</v>
+        <v>99551.02133270321</v>
       </c>
       <c r="D25">
-        <v>129785.4301740824</v>
+        <v>129758.5297823089</v>
       </c>
       <c r="E25">
-        <v>1040.827057515089</v>
+        <v>2357.556576248659</v>
       </c>
       <c r="F25">
-        <v>30284.77893087212</v>
+        <v>31601.50844960569</v>
       </c>
       <c r="G25">
         <v>1394</v>
@@ -3343,28 +3343,28 @@
         <v>7700</v>
       </c>
       <c r="M25">
-        <v>1854.537398099405</v>
+        <v>1935.169458886336</v>
       </c>
       <c r="N25">
-        <v>5845.462601900595</v>
+        <v>5764.830541113664</v>
       </c>
       <c r="O25">
-        <v>730.6828252375744</v>
+        <v>720.603817639208</v>
       </c>
       <c r="P25">
-        <v>5114.779776663021</v>
+        <v>5044.226723474456</v>
       </c>
       <c r="Q25">
-        <v>6779.779776663021</v>
+        <v>6709.226723474456</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1131109249370109</v>
+        <v>0.113908825896435</v>
       </c>
       <c r="T25">
-        <v>1.312015212781044</v>
+        <v>1.327567787612493</v>
       </c>
       <c r="U25">
         <v>0.06123661666253409</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.1519788211827</v>
+        <v>3.978979703633421</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09943039718042274</v>
+        <v>0.09944151305601207</v>
       </c>
       <c r="C26">
-        <v>99551.02133270323</v>
+        <v>98207.40257107656</v>
       </c>
       <c r="D26">
-        <v>129758.5297823089</v>
+        <v>129731.6405394158</v>
       </c>
       <c r="E26">
-        <v>2357.556576248655</v>
+        <v>3674.286094982228</v>
       </c>
       <c r="F26">
-        <v>31601.50844960568</v>
+        <v>32918.23796833926</v>
       </c>
       <c r="G26">
         <v>1394</v>
@@ -3425,28 +3425,28 @@
         <v>7700</v>
       </c>
       <c r="M26">
-        <v>1935.169458886335</v>
+        <v>2015.801519673266</v>
       </c>
       <c r="N26">
-        <v>5764.830541113664</v>
+        <v>5684.198480326734</v>
       </c>
       <c r="O26">
-        <v>720.603817639208</v>
+        <v>710.5248100408418</v>
       </c>
       <c r="P26">
-        <v>5044.226723474456</v>
+        <v>4973.673670285893</v>
       </c>
       <c r="Q26">
-        <v>6709.226723474456</v>
+        <v>6638.673670285893</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.113908825896435</v>
+        <v>0.114728004214777</v>
       </c>
       <c r="T26">
-        <v>1.327567787612493</v>
+        <v>1.343535097772781</v>
       </c>
       <c r="U26">
         <v>0.06123661666253409</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>3.978979703633422</v>
+        <v>3.819820515488085</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09944151305601207</v>
+        <v>0.09945262893160137</v>
       </c>
       <c r="C27">
-        <v>98207.40257107656</v>
+        <v>96863.79495140092</v>
       </c>
       <c r="D27">
-        <v>129731.6405394158</v>
+        <v>129704.7624384737</v>
       </c>
       <c r="E27">
-        <v>3674.286094982228</v>
+        <v>4991.015613715797</v>
       </c>
       <c r="F27">
-        <v>32918.23796833926</v>
+        <v>34234.96748707283</v>
       </c>
       <c r="G27">
         <v>1394</v>
@@ -3507,28 +3507,28 @@
         <v>7700</v>
       </c>
       <c r="M27">
-        <v>2015.801519673266</v>
+        <v>2096.433580460197</v>
       </c>
       <c r="N27">
-        <v>5684.198480326734</v>
+        <v>5603.566419539803</v>
       </c>
       <c r="O27">
-        <v>710.5248100408418</v>
+        <v>700.4458024424754</v>
       </c>
       <c r="P27">
-        <v>4973.673670285893</v>
+        <v>4903.120617097327</v>
       </c>
       <c r="Q27">
-        <v>6638.673670285893</v>
+        <v>6568.120617097327</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.114728004214777</v>
+        <v>0.1155693224876687</v>
       </c>
       <c r="T27">
-        <v>1.343535097772781</v>
+        <v>1.35993395685632</v>
       </c>
       <c r="U27">
         <v>0.06123661666253409</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>3.819820515488085</v>
+        <v>3.672904341815466</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09945262893160137</v>
+        <v>0.09946374480719072</v>
       </c>
       <c r="C28">
-        <v>96863.79495140092</v>
+        <v>95520.19846675222</v>
       </c>
       <c r="D28">
-        <v>129704.7624384737</v>
+        <v>129677.8954725586</v>
       </c>
       <c r="E28">
-        <v>4991.015613715797</v>
+        <v>6307.745132449374</v>
       </c>
       <c r="F28">
-        <v>34234.96748707283</v>
+        <v>35551.6970058064</v>
       </c>
       <c r="G28">
         <v>1394</v>
@@ -3589,28 +3589,28 @@
         <v>7700</v>
       </c>
       <c r="M28">
-        <v>2096.433580460197</v>
+        <v>2177.065641247128</v>
       </c>
       <c r="N28">
-        <v>5603.566419539803</v>
+        <v>5522.934358752873</v>
       </c>
       <c r="O28">
-        <v>700.4458024424754</v>
+        <v>690.3667948441091</v>
       </c>
       <c r="P28">
-        <v>4903.120617097327</v>
+        <v>4832.567563908764</v>
       </c>
       <c r="Q28">
-        <v>6568.120617097327</v>
+        <v>6497.567563908764</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1155693224876687</v>
+        <v>0.1164336905762562</v>
       </c>
       <c r="T28">
-        <v>1.35993395685632</v>
+        <v>1.376782099750367</v>
       </c>
       <c r="U28">
         <v>0.06123661666253409</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.672904341815466</v>
+        <v>3.536870847674153</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09946374480719072</v>
+        <v>0.09947486068278003</v>
       </c>
       <c r="C29">
-        <v>95520.19846675222</v>
+        <v>94176.61311021265</v>
       </c>
       <c r="D29">
-        <v>129677.8954725586</v>
+        <v>129651.0396347526</v>
       </c>
       <c r="E29">
-        <v>6307.745132449374</v>
+        <v>7624.474651182943</v>
       </c>
       <c r="F29">
-        <v>35551.6970058064</v>
+        <v>36868.42652453997</v>
       </c>
       <c r="G29">
         <v>1394</v>
@@ -3671,28 +3671,28 @@
         <v>7700</v>
       </c>
       <c r="M29">
-        <v>2177.065641247128</v>
+        <v>2257.697702034058</v>
       </c>
       <c r="N29">
-        <v>5522.934358752873</v>
+        <v>5442.302297965942</v>
       </c>
       <c r="O29">
-        <v>690.3667948441091</v>
+        <v>680.2877872457427</v>
       </c>
       <c r="P29">
-        <v>4832.567563908764</v>
+        <v>4762.014510720199</v>
       </c>
       <c r="Q29">
-        <v>6497.567563908764</v>
+        <v>6427.014510720199</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1164336905762562</v>
+        <v>0.1173220688895266</v>
       </c>
       <c r="T29">
-        <v>1.376782099750367</v>
+        <v>1.394098246613692</v>
       </c>
       <c r="U29">
         <v>0.06123661666253409</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.536870847674153</v>
+        <v>3.41055403168579</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09947486068278003</v>
+        <v>0.09948597655836935</v>
       </c>
       <c r="C30">
-        <v>94176.61311021265</v>
+        <v>92833.03887486972</v>
       </c>
       <c r="D30">
-        <v>129651.0396347526</v>
+        <v>129624.1949181433</v>
       </c>
       <c r="E30">
-        <v>7624.474651182943</v>
+        <v>8941.204169916513</v>
       </c>
       <c r="F30">
-        <v>36868.42652453997</v>
+        <v>38185.15604327354</v>
       </c>
       <c r="G30">
         <v>1394</v>
@@ -3753,28 +3753,28 @@
         <v>7700</v>
       </c>
       <c r="M30">
-        <v>2257.697702034058</v>
+        <v>2338.329762820989</v>
       </c>
       <c r="N30">
-        <v>5442.302297965942</v>
+        <v>5361.670237179011</v>
       </c>
       <c r="O30">
-        <v>680.2877872457427</v>
+        <v>670.2087796473763</v>
       </c>
       <c r="P30">
-        <v>4762.014510720199</v>
+        <v>4691.461457531635</v>
       </c>
       <c r="Q30">
-        <v>6427.014510720199</v>
+        <v>6356.461457531635</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1173220688895266</v>
+        <v>0.118235471944016</v>
       </c>
       <c r="T30">
-        <v>1.394098246613692</v>
+        <v>1.4119021722619</v>
       </c>
       <c r="U30">
         <v>0.06123661666253409</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.41055403168579</v>
+        <v>3.292948720248349</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09948597655836935</v>
+        <v>0.09949709243395867</v>
       </c>
       <c r="C31">
-        <v>92833.03887486973</v>
+        <v>91489.47575381686</v>
       </c>
       <c r="D31">
-        <v>129624.1949181433</v>
+        <v>129597.361315824</v>
       </c>
       <c r="E31">
-        <v>8941.204169916506</v>
+        <v>10257.93368865008</v>
       </c>
       <c r="F31">
-        <v>38185.15604327354</v>
+        <v>39501.8855620071</v>
       </c>
       <c r="G31">
         <v>1394</v>
@@ -3835,28 +3835,28 @@
         <v>7700</v>
       </c>
       <c r="M31">
-        <v>2338.329762820988</v>
+        <v>2418.961823607919</v>
       </c>
       <c r="N31">
-        <v>5361.670237179012</v>
+        <v>5281.038176392081</v>
       </c>
       <c r="O31">
-        <v>670.2087796473764</v>
+        <v>660.1297720490102</v>
       </c>
       <c r="P31">
-        <v>4691.461457531635</v>
+        <v>4620.908404343071</v>
       </c>
       <c r="Q31">
-        <v>6356.461457531635</v>
+        <v>6285.908404343071</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.118235471944016</v>
+        <v>0.1191749722286335</v>
       </c>
       <c r="T31">
-        <v>1.4119021722619</v>
+        <v>1.430214781500057</v>
       </c>
       <c r="U31">
         <v>0.06123661666253409</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.292948720248349</v>
+        <v>3.183183762906738</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09949709243395867</v>
+        <v>0.099508208309548</v>
       </c>
       <c r="C32">
-        <v>91489.47575381686</v>
+        <v>90145.9237401531</v>
       </c>
       <c r="D32">
-        <v>129597.361315824</v>
+        <v>129570.5388208938</v>
       </c>
       <c r="E32">
-        <v>10257.93368865008</v>
+        <v>11574.66320738365</v>
       </c>
       <c r="F32">
-        <v>39501.8855620071</v>
+        <v>40818.61508074068</v>
       </c>
       <c r="G32">
         <v>1394</v>
@@ -3917,28 +3917,28 @@
         <v>7700</v>
       </c>
       <c r="M32">
-        <v>2418.961823607919</v>
+        <v>2499.59388439485</v>
       </c>
       <c r="N32">
-        <v>5281.038176392081</v>
+        <v>5200.40611560515</v>
       </c>
       <c r="O32">
-        <v>660.1297720490102</v>
+        <v>650.0507644506438</v>
       </c>
       <c r="P32">
-        <v>4620.908404343071</v>
+        <v>4550.355351154507</v>
       </c>
       <c r="Q32">
-        <v>6285.908404343071</v>
+        <v>6215.355351154507</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1191749722286335</v>
+        <v>0.1201417044055589</v>
       </c>
       <c r="T32">
-        <v>1.430214781500057</v>
+        <v>1.449058191005987</v>
       </c>
       <c r="U32">
         <v>0.06123661666253409</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.183183762906738</v>
+        <v>3.080500415716197</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.099508208309548</v>
+        <v>0.1002193241851373</v>
       </c>
       <c r="C33">
-        <v>90145.9237401531</v>
+        <v>87136.0517845393</v>
       </c>
       <c r="D33">
-        <v>129570.5388208938</v>
+        <v>127877.3963840136</v>
       </c>
       <c r="E33">
-        <v>11574.66320738365</v>
+        <v>12891.39272611722</v>
       </c>
       <c r="F33">
-        <v>40818.61508074068</v>
+        <v>42135.34459947425</v>
       </c>
       <c r="G33">
         <v>1394</v>
@@ -3999,45 +3999,45 @@
         <v>7700</v>
       </c>
       <c r="M33">
-        <v>2499.59388439485</v>
+        <v>2685.564306680466</v>
       </c>
       <c r="N33">
-        <v>5200.40611560515</v>
+        <v>5014.435693319534</v>
       </c>
       <c r="O33">
-        <v>650.0507644506438</v>
+        <v>626.8044616649418</v>
       </c>
       <c r="P33">
-        <v>4550.355351154507</v>
+        <v>4387.631231654592</v>
       </c>
       <c r="Q33">
-        <v>6215.355351154507</v>
+        <v>6052.631231654592</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1201417044055589</v>
+        <v>0.1211368698818056</v>
       </c>
       <c r="T33">
-        <v>1.449058191005987</v>
+        <v>1.468455818438561</v>
       </c>
       <c r="U33">
-        <v>0.06123661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.080500415716197</v>
+        <v>2.867181389343719</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1002193241851373</v>
+        <v>0.1002523150607266</v>
       </c>
       <c r="C34">
-        <v>87136.0517845393</v>
+        <v>85741.84553648603</v>
       </c>
       <c r="D34">
-        <v>127877.3963840136</v>
+        <v>127799.9196546938</v>
       </c>
       <c r="E34">
-        <v>12891.39272611722</v>
+        <v>14208.12224485079</v>
       </c>
       <c r="F34">
-        <v>42135.34459947425</v>
+        <v>43452.07411820782</v>
       </c>
       <c r="G34">
         <v>1394</v>
@@ -4081,28 +4081,28 @@
         <v>7700</v>
       </c>
       <c r="M34">
-        <v>2685.564306680466</v>
+        <v>2769.488191264231</v>
       </c>
       <c r="N34">
-        <v>5014.435693319534</v>
+        <v>4930.51180873577</v>
       </c>
       <c r="O34">
-        <v>626.8044616649418</v>
+        <v>616.3139760919712</v>
       </c>
       <c r="P34">
-        <v>4387.631231654592</v>
+        <v>4314.197832643798</v>
       </c>
       <c r="Q34">
-        <v>6052.631231654592</v>
+        <v>5979.197832643798</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1211368698818056</v>
+        <v>0.122161741790179</v>
       </c>
       <c r="T34">
-        <v>1.468455818438561</v>
+        <v>1.48843247952584</v>
       </c>
       <c r="U34">
         <v>0.06373661666253409</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.867181389343719</v>
+        <v>2.780297104818152</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1002523150607266</v>
+        <v>0.100285305936316</v>
       </c>
       <c r="C35">
-        <v>85741.84553648603</v>
+        <v>84347.73311281687</v>
       </c>
       <c r="D35">
-        <v>127799.9196546938</v>
+        <v>127722.5367497583</v>
       </c>
       <c r="E35">
-        <v>14208.12224485079</v>
+        <v>15524.85176358437</v>
       </c>
       <c r="F35">
-        <v>43452.07411820782</v>
+        <v>44768.8036369414</v>
       </c>
       <c r="G35">
         <v>1394</v>
@@ -4163,28 +4163,28 @@
         <v>7700</v>
       </c>
       <c r="M35">
-        <v>2769.488191264231</v>
+        <v>2853.412075847996</v>
       </c>
       <c r="N35">
-        <v>4930.51180873577</v>
+        <v>4846.587924152004</v>
       </c>
       <c r="O35">
-        <v>616.3139760919712</v>
+        <v>605.8234905190005</v>
       </c>
       <c r="P35">
-        <v>4314.197832643798</v>
+        <v>4240.764433633004</v>
       </c>
       <c r="Q35">
-        <v>5979.197832643798</v>
+        <v>5905.764433633004</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.122161741790179</v>
+        <v>0.1232176704230486</v>
       </c>
       <c r="T35">
-        <v>1.48843247952584</v>
+        <v>1.509014493979399</v>
       </c>
       <c r="U35">
         <v>0.06373661666253409</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.780297104818152</v>
+        <v>2.698523660558794</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.100285305936316</v>
+        <v>0.1003182968119053</v>
       </c>
       <c r="C36">
-        <v>84347.73311281687</v>
+        <v>82953.71434320297</v>
       </c>
       <c r="D36">
-        <v>127722.5367497583</v>
+        <v>127645.2474988779</v>
       </c>
       <c r="E36">
-        <v>15524.85176358437</v>
+        <v>16841.58128231794</v>
       </c>
       <c r="F36">
-        <v>44768.8036369414</v>
+        <v>46085.53315567497</v>
       </c>
       <c r="G36">
         <v>1394</v>
@@ -4245,28 +4245,28 @@
         <v>7700</v>
       </c>
       <c r="M36">
-        <v>2853.412075847996</v>
+        <v>2937.335960431761</v>
       </c>
       <c r="N36">
-        <v>4846.587924152004</v>
+        <v>4762.664039568239</v>
       </c>
       <c r="O36">
-        <v>605.8234905190005</v>
+        <v>595.3330049460299</v>
       </c>
       <c r="P36">
-        <v>4240.764433633004</v>
+        <v>4167.331034622209</v>
       </c>
       <c r="Q36">
-        <v>5905.764433633004</v>
+        <v>5832.331034622209</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1232176704230486</v>
+        <v>0.1243060891676988</v>
       </c>
       <c r="T36">
-        <v>1.509014493979399</v>
+        <v>1.530229801185376</v>
       </c>
       <c r="U36">
         <v>0.06373661666253409</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.698523660558794</v>
+        <v>2.621422984542828</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1003182968119053</v>
+        <v>0.1003512876874946</v>
       </c>
       <c r="C37">
-        <v>82953.71434320297</v>
+        <v>81559.78905772732</v>
       </c>
       <c r="D37">
-        <v>127645.2474988779</v>
+        <v>127568.0517321359</v>
       </c>
       <c r="E37">
-        <v>16841.58128231794</v>
+        <v>18158.31080105151</v>
       </c>
       <c r="F37">
-        <v>46085.53315567497</v>
+        <v>47402.26267440854</v>
       </c>
       <c r="G37">
         <v>1394</v>
@@ -4327,28 +4327,28 @@
         <v>7700</v>
       </c>
       <c r="M37">
-        <v>2937.335960431761</v>
+        <v>3021.259845015525</v>
       </c>
       <c r="N37">
-        <v>4762.664039568239</v>
+        <v>4678.740154984474</v>
       </c>
       <c r="O37">
-        <v>595.3330049460299</v>
+        <v>584.8425193730593</v>
       </c>
       <c r="P37">
-        <v>4167.331034622209</v>
+        <v>4093.897635611415</v>
       </c>
       <c r="Q37">
-        <v>5832.331034622209</v>
+        <v>5758.897635611415</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1243060891676988</v>
+        <v>0.1254285209981194</v>
       </c>
       <c r="T37">
-        <v>1.530229801185376</v>
+        <v>1.552108086741539</v>
       </c>
       <c r="U37">
         <v>0.06373661666253409</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.621422984542828</v>
+        <v>2.548605679416638</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1003512876874946</v>
+        <v>0.1015174035630839</v>
       </c>
       <c r="C38">
-        <v>81559.78905772729</v>
+        <v>77573.17327671633</v>
       </c>
       <c r="D38">
-        <v>127568.0517321358</v>
+        <v>124898.1654698584</v>
       </c>
       <c r="E38">
-        <v>18158.3108010515</v>
+        <v>19475.04031978507</v>
       </c>
       <c r="F38">
-        <v>47402.26267440853</v>
+        <v>48718.9921931421</v>
       </c>
       <c r="G38">
         <v>1394</v>
@@ -4409,45 +4409,45 @@
         <v>7700</v>
       </c>
       <c r="M38">
-        <v>3021.259845015525</v>
+        <v>3275.700202275286</v>
       </c>
       <c r="N38">
-        <v>4678.740154984475</v>
+        <v>4424.299797724714</v>
       </c>
       <c r="O38">
-        <v>584.8425193730594</v>
+        <v>553.0374747155893</v>
       </c>
       <c r="P38">
-        <v>4093.897635611416</v>
+        <v>3871.262323009125</v>
       </c>
       <c r="Q38">
-        <v>5758.897635611416</v>
+        <v>5536.262323009125</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1254285209981194</v>
+        <v>0.1265865855850612</v>
       </c>
       <c r="T38">
-        <v>1.552108086741539</v>
+        <v>1.574680921045517</v>
       </c>
       <c r="U38">
-        <v>0.06373661666253409</v>
+        <v>0.06723661666253408</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971732</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.548605679416639</v>
+        <v>2.350642465586935</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1015174035630839</v>
+        <v>0.1015810194386733</v>
       </c>
       <c r="C39">
-        <v>77573.17327671633</v>
+        <v>76114.00272273776</v>
       </c>
       <c r="D39">
-        <v>124898.1654698584</v>
+        <v>124755.7244346134</v>
       </c>
       <c r="E39">
-        <v>19475.04031978507</v>
+        <v>20791.76983851864</v>
       </c>
       <c r="F39">
-        <v>48718.9921931421</v>
+        <v>50035.72171187567</v>
       </c>
       <c r="G39">
         <v>1394</v>
@@ -4491,28 +4491,28 @@
         <v>7700</v>
       </c>
       <c r="M39">
-        <v>3275.700202275286</v>
+        <v>3364.232640174618</v>
       </c>
       <c r="N39">
-        <v>4424.299797724714</v>
+        <v>4335.767359825382</v>
       </c>
       <c r="O39">
-        <v>553.0374747155893</v>
+        <v>541.9709199781728</v>
       </c>
       <c r="P39">
-        <v>3871.262323009125</v>
+        <v>3793.79643984721</v>
       </c>
       <c r="Q39">
-        <v>5536.262323009125</v>
+        <v>5458.79643984721</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1265865855850612</v>
+        <v>0.1277820070941624</v>
       </c>
       <c r="T39">
-        <v>1.574680921045517</v>
+        <v>1.597981911294785</v>
       </c>
       <c r="U39">
         <v>0.06723661666253408</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.350642465586935</v>
+        <v>2.288783453334648</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1015810194386733</v>
+        <v>0.1026001353142626</v>
       </c>
       <c r="C40">
-        <v>76114.00272273776</v>
+        <v>72558.88875934537</v>
       </c>
       <c r="D40">
-        <v>124755.7244346134</v>
+        <v>122517.3399899546</v>
       </c>
       <c r="E40">
-        <v>20791.76983851864</v>
+        <v>22108.49935725221</v>
       </c>
       <c r="F40">
-        <v>50035.72171187567</v>
+        <v>51352.45123060924</v>
       </c>
       <c r="G40">
         <v>1394</v>
@@ -4573,45 +4573,45 @@
         <v>7700</v>
       </c>
       <c r="M40">
-        <v>3364.232640174618</v>
+        <v>3596.551941519657</v>
       </c>
       <c r="N40">
-        <v>4335.767359825382</v>
+        <v>4103.448058480343</v>
       </c>
       <c r="O40">
-        <v>541.9709199781728</v>
+        <v>512.9310073100429</v>
       </c>
       <c r="P40">
-        <v>3793.79643984721</v>
+        <v>3590.5170511703</v>
       </c>
       <c r="Q40">
-        <v>5458.79643984721</v>
+        <v>5255.5170511703</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1277820070941624</v>
+        <v>0.129016622751103</v>
       </c>
       <c r="T40">
-        <v>1.597981911294785</v>
+        <v>1.622046868437472</v>
       </c>
       <c r="U40">
-        <v>0.06723661666253408</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05883203957971732</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.288783453334648</v>
+        <v>2.1409394679134</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1026001353142626</v>
+        <v>0.1026882511898519</v>
       </c>
       <c r="C41">
-        <v>72558.88875934537</v>
+        <v>71052.38855049055</v>
       </c>
       <c r="D41">
-        <v>122517.3399899546</v>
+        <v>122327.5692998334</v>
       </c>
       <c r="E41">
-        <v>22108.49935725221</v>
+        <v>23425.22887598578</v>
       </c>
       <c r="F41">
-        <v>51352.45123060924</v>
+        <v>52669.18074934281</v>
       </c>
       <c r="G41">
         <v>1394</v>
@@ -4655,28 +4655,28 @@
         <v>7700</v>
       </c>
       <c r="M41">
-        <v>3596.551941519657</v>
+        <v>3688.771222071443</v>
       </c>
       <c r="N41">
-        <v>4103.448058480343</v>
+        <v>4011.228777928557</v>
       </c>
       <c r="O41">
-        <v>512.9310073100429</v>
+        <v>501.4035972410696</v>
       </c>
       <c r="P41">
-        <v>3590.5170511703</v>
+        <v>3509.825180687487</v>
       </c>
       <c r="Q41">
-        <v>5255.5170511703</v>
+        <v>5174.825180687487</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.129016622751103</v>
+        <v>0.130292392263275</v>
       </c>
       <c r="T41">
-        <v>1.622046868437472</v>
+        <v>1.646913990818248</v>
       </c>
       <c r="U41">
         <v>0.07003661666253409</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.1409394679134</v>
+        <v>2.087415981215565</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1026882511898519</v>
+        <v>0.1027763670654412</v>
       </c>
       <c r="C42">
-        <v>71052.38855049055</v>
+        <v>69546.47531519627</v>
       </c>
       <c r="D42">
-        <v>122327.5692998334</v>
+        <v>122138.3855832726</v>
       </c>
       <c r="E42">
-        <v>23425.22887598578</v>
+        <v>24741.95839471935</v>
       </c>
       <c r="F42">
-        <v>52669.18074934281</v>
+        <v>53985.91026807638</v>
       </c>
       <c r="G42">
         <v>1394</v>
@@ -4737,28 +4737,28 @@
         <v>7700</v>
       </c>
       <c r="M42">
-        <v>3688.771222071443</v>
+        <v>3780.990502623229</v>
       </c>
       <c r="N42">
-        <v>4011.228777928557</v>
+        <v>3919.009497376771</v>
       </c>
       <c r="O42">
-        <v>501.4035972410696</v>
+        <v>489.8761871720964</v>
       </c>
       <c r="P42">
-        <v>3509.825180687487</v>
+        <v>3429.133310204675</v>
       </c>
       <c r="Q42">
-        <v>5174.825180687487</v>
+        <v>5094.133310204676</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.130292392263275</v>
+        <v>0.1316114081995884</v>
       </c>
       <c r="T42">
-        <v>1.646913990818248</v>
+        <v>1.672624066500067</v>
       </c>
       <c r="U42">
         <v>0.07003661666253409</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.087415981215565</v>
+        <v>2.036503396307868</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1027763670654412</v>
+        <v>0.1057309829410306</v>
       </c>
       <c r="C43">
-        <v>69546.47531519627</v>
+        <v>62208.2858544779</v>
       </c>
       <c r="D43">
-        <v>122138.3855832726</v>
+        <v>116116.9256412879</v>
       </c>
       <c r="E43">
-        <v>24741.95839471935</v>
+        <v>26058.68791345293</v>
       </c>
       <c r="F43">
-        <v>53985.91026807638</v>
+        <v>55302.63978680996</v>
       </c>
       <c r="G43">
         <v>1394</v>
@@ -4819,45 +4819,45 @@
         <v>7700</v>
       </c>
       <c r="M43">
-        <v>3780.990502623229</v>
+        <v>4304.570373512132</v>
       </c>
       <c r="N43">
-        <v>3919.009497376771</v>
+        <v>3395.429626487868</v>
       </c>
       <c r="O43">
-        <v>489.8761871720964</v>
+        <v>424.4287033109835</v>
       </c>
       <c r="P43">
-        <v>3429.133310204675</v>
+        <v>2971.000923176884</v>
       </c>
       <c r="Q43">
-        <v>5094.133310204676</v>
+        <v>4636.000923176884</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1316114081995884</v>
+        <v>0.1329759074440505</v>
       </c>
       <c r="T43">
-        <v>1.672624066500067</v>
+        <v>1.699220696515742</v>
       </c>
       <c r="U43">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253408</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971732</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>2.036503396307868</v>
+        <v>1.788796402860876</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1057309829410306</v>
+        <v>0.1073547238166199</v>
       </c>
       <c r="C44">
-        <v>62208.28585447789</v>
+        <v>57828.52905170965</v>
       </c>
       <c r="D44">
-        <v>116116.9256412878</v>
+        <v>113053.8983572532</v>
       </c>
       <c r="E44">
-        <v>26058.68791345292</v>
+        <v>27375.41743218649</v>
       </c>
       <c r="F44">
-        <v>55302.63978680995</v>
+        <v>56619.36930554352</v>
       </c>
       <c r="G44">
         <v>1394</v>
@@ -4901,45 +4901,45 @@
         <v>7700</v>
       </c>
       <c r="M44">
-        <v>4304.570373512131</v>
+        <v>4627.87568460166</v>
       </c>
       <c r="N44">
-        <v>3395.429626487869</v>
+        <v>3072.12431539834</v>
       </c>
       <c r="O44">
-        <v>424.4287033109836</v>
+        <v>384.0155394247925</v>
       </c>
       <c r="P44">
-        <v>2971.000923176885</v>
+        <v>2688.108775973547</v>
       </c>
       <c r="Q44">
-        <v>4636.000923176885</v>
+        <v>4353.108775973547</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1329759074440505</v>
+        <v>0.134388283854985</v>
       </c>
       <c r="T44">
-        <v>1.699220696515742</v>
+        <v>1.726750541619686</v>
       </c>
       <c r="U44">
-        <v>0.07783661666253408</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.06810703957971732</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y44">
-        <v>1.788796402860876</v>
+        <v>1.663830345663827</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1073547238166199</v>
+        <v>0.1075452146922092</v>
       </c>
       <c r="C45">
-        <v>57828.52905170965</v>
+        <v>56163.0156443102</v>
       </c>
       <c r="D45">
-        <v>113053.8983572532</v>
+        <v>112705.1144685873</v>
       </c>
       <c r="E45">
-        <v>27375.41743218649</v>
+        <v>28692.14695092006</v>
       </c>
       <c r="F45">
-        <v>56619.36930554352</v>
+        <v>57936.09882427709</v>
       </c>
       <c r="G45">
         <v>1394</v>
@@ -4983,28 +4983,28 @@
         <v>7700</v>
       </c>
       <c r="M45">
-        <v>4627.87568460166</v>
+        <v>4735.500700522629</v>
       </c>
       <c r="N45">
-        <v>3072.12431539834</v>
+        <v>2964.499299477371</v>
       </c>
       <c r="O45">
-        <v>384.0155394247925</v>
+        <v>370.5624124346714</v>
       </c>
       <c r="P45">
-        <v>2688.108775973547</v>
+        <v>2593.9368870427</v>
       </c>
       <c r="Q45">
-        <v>4353.108775973547</v>
+        <v>4258.9368870427</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.134388283854985</v>
+        <v>0.1358511022805957</v>
       </c>
       <c r="T45">
-        <v>1.726750541619686</v>
+        <v>1.755263595477343</v>
       </c>
       <c r="U45">
         <v>0.0817366166625341</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.663830345663827</v>
+        <v>1.626016019626013</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1075452146922092</v>
+        <v>0.1077357055677986</v>
       </c>
       <c r="C46">
-        <v>56163.0156443102</v>
+        <v>54499.64769235469</v>
       </c>
       <c r="D46">
-        <v>112705.1144685873</v>
+        <v>112358.4760353654</v>
       </c>
       <c r="E46">
-        <v>28692.14695092006</v>
+        <v>30008.87646965364</v>
       </c>
       <c r="F46">
-        <v>57936.09882427709</v>
+        <v>59252.82834301067</v>
       </c>
       <c r="G46">
         <v>1394</v>
@@ -5065,28 +5065,28 @@
         <v>7700</v>
       </c>
       <c r="M46">
-        <v>4735.500700522629</v>
+        <v>4843.125716443598</v>
       </c>
       <c r="N46">
-        <v>2964.499299477371</v>
+        <v>2856.874283556402</v>
       </c>
       <c r="O46">
-        <v>370.5624124346714</v>
+        <v>357.1092854445502</v>
       </c>
       <c r="P46">
-        <v>2593.9368870427</v>
+        <v>2499.764998111852</v>
       </c>
       <c r="Q46">
-        <v>4258.9368870427</v>
+        <v>4164.764998111852</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1358511022805957</v>
+        <v>0.1373671141035014</v>
       </c>
       <c r="T46">
-        <v>1.755263595477343</v>
+        <v>1.784813487657096</v>
       </c>
       <c r="U46">
         <v>0.0817366166625341</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.626016019626013</v>
+        <v>1.58988233030099</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1077357055677986</v>
+        <v>0.1079261964433879</v>
       </c>
       <c r="C47">
-        <v>54499.64769235469</v>
+        <v>52838.40546070519</v>
       </c>
       <c r="D47">
-        <v>112358.4760353654</v>
+        <v>112013.9633224494</v>
       </c>
       <c r="E47">
-        <v>30008.87646965364</v>
+        <v>31325.60598838721</v>
       </c>
       <c r="F47">
-        <v>59252.82834301067</v>
+        <v>60569.55786174424</v>
       </c>
       <c r="G47">
         <v>1394</v>
@@ -5147,28 +5147,28 @@
         <v>7700</v>
       </c>
       <c r="M47">
-        <v>4843.125716443598</v>
+        <v>4950.750732364567</v>
       </c>
       <c r="N47">
-        <v>2856.874283556402</v>
+        <v>2749.249267635433</v>
       </c>
       <c r="O47">
-        <v>357.1092854445502</v>
+        <v>343.6561584544291</v>
       </c>
       <c r="P47">
-        <v>2499.764998111852</v>
+        <v>2405.593109181004</v>
       </c>
       <c r="Q47">
-        <v>4164.764998111852</v>
+        <v>4070.593109181004</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1373671141035014</v>
+        <v>0.1389392745124406</v>
       </c>
       <c r="T47">
-        <v>1.784813487657096</v>
+        <v>1.815457820287951</v>
       </c>
       <c r="U47">
         <v>0.0817366166625341</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.58988233030099</v>
+        <v>1.555319670946621</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1079261964433879</v>
+        <v>0.1081166873189772</v>
       </c>
       <c r="C48">
-        <v>52838.40546070519</v>
+        <v>51179.26945553078</v>
       </c>
       <c r="D48">
-        <v>112013.9633224494</v>
+        <v>111671.5568360086</v>
       </c>
       <c r="E48">
-        <v>31325.60598838721</v>
+        <v>32642.33550712078</v>
       </c>
       <c r="F48">
-        <v>60569.55786174424</v>
+        <v>61886.28738047781</v>
       </c>
       <c r="G48">
         <v>1394</v>
@@ -5229,28 +5229,28 @@
         <v>7700</v>
       </c>
       <c r="M48">
-        <v>4950.750732364567</v>
+        <v>5058.375748285535</v>
       </c>
       <c r="N48">
-        <v>2749.249267635433</v>
+        <v>2641.624251714465</v>
       </c>
       <c r="O48">
-        <v>343.6561584544291</v>
+        <v>330.2030314643081</v>
       </c>
       <c r="P48">
-        <v>2405.593109181004</v>
+        <v>2311.421220250157</v>
       </c>
       <c r="Q48">
-        <v>4070.593109181004</v>
+        <v>3976.421220250157</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1389392745124406</v>
+        <v>0.1405707617292642</v>
       </c>
       <c r="T48">
-        <v>1.815457820287951</v>
+        <v>1.847258542829405</v>
       </c>
       <c r="U48">
         <v>0.0817366166625341</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.555319670946621</v>
+        <v>1.52222776305414</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1081166873189772</v>
+        <v>0.1142711781945665</v>
       </c>
       <c r="C49">
-        <v>51179.26945553078</v>
+        <v>39825.00888019553</v>
       </c>
       <c r="D49">
-        <v>111671.5568360086</v>
+        <v>101634.0257794069</v>
       </c>
       <c r="E49">
-        <v>32642.33550712078</v>
+        <v>33959.06502585435</v>
       </c>
       <c r="F49">
-        <v>61886.28738047781</v>
+        <v>63203.01689921138</v>
       </c>
       <c r="G49">
         <v>1394</v>
@@ -5311,45 +5311,45 @@
         <v>7700</v>
       </c>
       <c r="M49">
-        <v>5058.375748285535</v>
+        <v>6063.483604175305</v>
       </c>
       <c r="N49">
-        <v>2641.624251714465</v>
+        <v>1636.516395824695</v>
       </c>
       <c r="O49">
-        <v>330.2030314643081</v>
+        <v>204.5645494780869</v>
       </c>
       <c r="P49">
-        <v>2311.421220250157</v>
+        <v>1431.951846346608</v>
       </c>
       <c r="Q49">
-        <v>3976.421220250157</v>
+        <v>3096.951846346608</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1405707617292642</v>
+        <v>0.1422649984544273</v>
       </c>
       <c r="T49">
-        <v>1.847258542829405</v>
+        <v>1.880282370083991</v>
       </c>
       <c r="U49">
-        <v>0.0817366166625341</v>
+        <v>0.09593661666253409</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y49">
-        <v>1.52222776305414</v>
+        <v>1.26989705962061</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1142711781945665</v>
+        <v>0.1273025599873987</v>
       </c>
       <c r="C50">
-        <v>39825.00888019554</v>
+        <v>22258.092946719</v>
       </c>
       <c r="D50">
-        <v>101634.0257794069</v>
+        <v>85383.83936466395</v>
       </c>
       <c r="E50">
-        <v>33959.06502585434</v>
+        <v>35275.79454458792</v>
       </c>
       <c r="F50">
-        <v>63203.01689921137</v>
+        <v>64519.74641794495</v>
       </c>
       <c r="G50">
         <v>1394</v>
@@ -5393,45 +5393,45 @@
         <v>7700</v>
       </c>
       <c r="M50">
-        <v>6063.483604175305</v>
+        <v>8035.070926815517</v>
       </c>
       <c r="N50">
-        <v>1636.516395824695</v>
+        <v>-335.0709268155169</v>
       </c>
       <c r="O50">
-        <v>204.5645494780869</v>
+        <v>-41.88386585193962</v>
       </c>
       <c r="P50">
-        <v>1431.951846346608</v>
+        <v>-293.1870609635773</v>
       </c>
       <c r="Q50">
-        <v>3096.951846346608</v>
+        <v>1371.812939036423</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1422649984544273</v>
+        <v>0.1442929322889002</v>
       </c>
       <c r="T50">
-        <v>1.880282370083991</v>
+        <v>1.919810575109129</v>
       </c>
       <c r="U50">
-        <v>0.09593661666253409</v>
+        <v>0.1245366166625341</v>
       </c>
       <c r="V50">
-        <v>0.125</v>
+        <v>0.1197873682468489</v>
       </c>
       <c r="W50">
-        <v>0.08394453957971733</v>
+        <v>0.1096187031021625</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.26989705962061</v>
+        <v>0.9582989459747914</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1273025599873987</v>
+        <v>0.128089926154024</v>
       </c>
       <c r="C51">
-        <v>22258.092946719</v>
+        <v>20124.3940924379</v>
       </c>
       <c r="D51">
-        <v>85383.83936466395</v>
+        <v>84566.87002911641</v>
       </c>
       <c r="E51">
-        <v>35275.79454458792</v>
+        <v>36592.52406332149</v>
       </c>
       <c r="F51">
-        <v>64519.74641794495</v>
+        <v>65836.47593667851</v>
       </c>
       <c r="G51">
         <v>1394</v>
@@ -5475,37 +5475,37 @@
         <v>7700</v>
       </c>
       <c r="M51">
-        <v>8035.070926815517</v>
+        <v>8199.051966138282</v>
       </c>
       <c r="N51">
-        <v>-335.0709268155169</v>
+        <v>-499.0519661382823</v>
       </c>
       <c r="O51">
-        <v>-41.88386585193962</v>
+        <v>-62.38149576728529</v>
       </c>
       <c r="P51">
-        <v>-293.1870609635773</v>
+        <v>-436.670470370997</v>
       </c>
       <c r="Q51">
-        <v>1371.812939036423</v>
+        <v>1228.329529629003</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1442929322889002</v>
+        <v>0.1462627909346782</v>
       </c>
       <c r="T51">
-        <v>1.919810575109129</v>
+        <v>1.958206786611311</v>
       </c>
       <c r="U51">
         <v>0.1245366166625341</v>
       </c>
       <c r="V51">
-        <v>0.1197873682468489</v>
+        <v>0.1173916208819119</v>
       </c>
       <c r="W51">
-        <v>0.1096187031021625</v>
+        <v>0.1099170613733699</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9582989459747914</v>
+        <v>0.9391329670552956</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.128089926154024</v>
+        <v>0.1288772923206494</v>
       </c>
       <c r="C52">
-        <v>20124.3940924379</v>
+        <v>18006.18091411017</v>
       </c>
       <c r="D52">
-        <v>84566.87002911641</v>
+        <v>83765.38636952225</v>
       </c>
       <c r="E52">
-        <v>36592.52406332149</v>
+        <v>37909.25358205505</v>
       </c>
       <c r="F52">
-        <v>65836.47593667851</v>
+        <v>67153.20545541208</v>
       </c>
       <c r="G52">
         <v>1394</v>
@@ -5557,37 +5557,37 @@
         <v>7700</v>
       </c>
       <c r="M52">
-        <v>8199.051966138282</v>
+        <v>8363.033005461048</v>
       </c>
       <c r="N52">
-        <v>-499.0519661382823</v>
+        <v>-663.0330054610477</v>
       </c>
       <c r="O52">
-        <v>-62.38149576728529</v>
+        <v>-82.87912568263096</v>
       </c>
       <c r="P52">
-        <v>-436.670470370997</v>
+        <v>-580.1538797784167</v>
       </c>
       <c r="Q52">
-        <v>1228.329529629003</v>
+        <v>1084.846120221583</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1462627909346782</v>
+        <v>0.1483130519741614</v>
       </c>
       <c r="T52">
-        <v>1.958206786611311</v>
+        <v>1.998170190419705</v>
       </c>
       <c r="U52">
         <v>0.1245366166625341</v>
       </c>
       <c r="V52">
-        <v>0.1173916208819119</v>
+        <v>0.1150898243940313</v>
       </c>
       <c r="W52">
-        <v>0.1099170613733699</v>
+        <v>0.1102037193202162</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9391329670552956</v>
+        <v>0.9207185951522506</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1288772923206494</v>
+        <v>0.1296646584872747</v>
       </c>
       <c r="C53">
-        <v>18006.18091411017</v>
+        <v>15903.01724836734</v>
       </c>
       <c r="D53">
-        <v>83765.38636952225</v>
+        <v>82978.95222251299</v>
       </c>
       <c r="E53">
-        <v>37909.25358205505</v>
+        <v>39225.98310078862</v>
       </c>
       <c r="F53">
-        <v>67153.20545541208</v>
+        <v>68469.93497414565</v>
       </c>
       <c r="G53">
         <v>1394</v>
@@ -5639,37 +5639,37 @@
         <v>7700</v>
       </c>
       <c r="M53">
-        <v>8363.033005461048</v>
+        <v>8527.014044783813</v>
       </c>
       <c r="N53">
-        <v>-663.0330054610477</v>
+        <v>-827.014044783813</v>
       </c>
       <c r="O53">
-        <v>-82.87912568263096</v>
+        <v>-103.3767555979766</v>
       </c>
       <c r="P53">
-        <v>-580.1538797784167</v>
+        <v>-723.6372891858364</v>
       </c>
       <c r="Q53">
-        <v>1084.846120221583</v>
+        <v>941.3627108141636</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1483130519741614</v>
+        <v>0.1504487405569565</v>
       </c>
       <c r="T53">
-        <v>1.998170190419705</v>
+        <v>2.03979873605345</v>
       </c>
       <c r="U53">
         <v>0.1245366166625341</v>
       </c>
       <c r="V53">
-        <v>0.1150898243940313</v>
+        <v>0.1128765585403</v>
       </c>
       <c r="W53">
-        <v>0.1102037193202162</v>
+        <v>0.1104793519614147</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.9207185951522506</v>
+        <v>0.9030124683223997</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1296646584872747</v>
+        <v>0.1304520246539001</v>
       </c>
       <c r="C54">
-        <v>15903.01724836734</v>
+        <v>13814.48315922747</v>
       </c>
       <c r="D54">
-        <v>82978.95222251299</v>
+        <v>82207.14765210669</v>
       </c>
       <c r="E54">
-        <v>39225.98310078862</v>
+        <v>40542.71261952219</v>
       </c>
       <c r="F54">
-        <v>68469.93497414565</v>
+        <v>69786.66449287922</v>
       </c>
       <c r="G54">
         <v>1394</v>
@@ -5721,37 +5721,37 @@
         <v>7700</v>
       </c>
       <c r="M54">
-        <v>8527.014044783813</v>
+        <v>8690.99508410658</v>
       </c>
       <c r="N54">
-        <v>-827.014044783813</v>
+        <v>-990.9950841065802</v>
       </c>
       <c r="O54">
-        <v>-103.3767555979766</v>
+        <v>-123.8743855133225</v>
       </c>
       <c r="P54">
-        <v>-723.6372891858364</v>
+        <v>-867.1206985932577</v>
       </c>
       <c r="Q54">
-        <v>941.3627108141636</v>
+        <v>797.8793014067423</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1504487405569565</v>
+        <v>0.1526753095049768</v>
       </c>
       <c r="T54">
-        <v>2.03979873605345</v>
+        <v>2.08319870916097</v>
       </c>
       <c r="U54">
         <v>0.1245366166625341</v>
       </c>
       <c r="V54">
-        <v>0.1128765585403</v>
+        <v>0.1107468121527471</v>
       </c>
       <c r="W54">
-        <v>0.1104793519614147</v>
+        <v>0.1107445833708698</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9030124683223997</v>
+        <v>0.8859744972219769</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1304520246539001</v>
+        <v>0.1312393908205254</v>
       </c>
       <c r="C55">
-        <v>13814.48315922747</v>
+        <v>11740.17419037806</v>
       </c>
       <c r="D55">
-        <v>82207.14765210669</v>
+        <v>81449.56820199087</v>
       </c>
       <c r="E55">
-        <v>40542.71261952219</v>
+        <v>41859.44213825578</v>
       </c>
       <c r="F55">
-        <v>69786.66449287922</v>
+        <v>71103.39401161281</v>
       </c>
       <c r="G55">
         <v>1394</v>
@@ -5803,37 +5803,37 @@
         <v>7700</v>
       </c>
       <c r="M55">
-        <v>8690.99508410658</v>
+        <v>8854.976123429347</v>
       </c>
       <c r="N55">
-        <v>-990.9950841065802</v>
+        <v>-1154.976123429347</v>
       </c>
       <c r="O55">
-        <v>-123.8743855133225</v>
+        <v>-144.3720154286684</v>
       </c>
       <c r="P55">
-        <v>-867.1206985932577</v>
+        <v>-1010.604108000679</v>
       </c>
       <c r="Q55">
-        <v>797.8793014067423</v>
+        <v>654.3958919993211</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1526753095049768</v>
+        <v>0.1549986857985633</v>
       </c>
       <c r="T55">
-        <v>2.08319870916097</v>
+        <v>2.128485637620991</v>
       </c>
       <c r="U55">
         <v>0.1245366166625341</v>
       </c>
       <c r="V55">
-        <v>0.1107468121527471</v>
+        <v>0.1086959452610295</v>
       </c>
       <c r="W55">
-        <v>0.1107445833708698</v>
+        <v>0.1109999913947895</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8859744972219769</v>
+        <v>0.8695675620882364</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1312393908205254</v>
+        <v>0.1320267569871508</v>
       </c>
       <c r="C56">
-        <v>11740.17419037806</v>
+        <v>9679.700658425398</v>
       </c>
       <c r="D56">
-        <v>81449.56820199087</v>
+        <v>80705.82418877177</v>
       </c>
       <c r="E56">
-        <v>41859.44213825578</v>
+        <v>43176.17165698935</v>
       </c>
       <c r="F56">
-        <v>71103.39401161281</v>
+        <v>72420.12353034638</v>
       </c>
       <c r="G56">
         <v>1394</v>
@@ -5885,37 +5885,37 @@
         <v>7700</v>
       </c>
       <c r="M56">
-        <v>8854.976123429347</v>
+        <v>9018.957162752113</v>
       </c>
       <c r="N56">
-        <v>-1154.976123429347</v>
+        <v>-1318.957162752113</v>
       </c>
       <c r="O56">
-        <v>-144.3720154286684</v>
+        <v>-164.8696453440141</v>
       </c>
       <c r="P56">
-        <v>-1010.604108000679</v>
+        <v>-1154.087517408099</v>
       </c>
       <c r="Q56">
-        <v>654.3958919993211</v>
+        <v>510.9124825919014</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1549986857985633</v>
+        <v>0.1574253232607536</v>
       </c>
       <c r="T56">
-        <v>2.128485637620991</v>
+        <v>2.175785318457013</v>
       </c>
       <c r="U56">
         <v>0.1245366166625341</v>
       </c>
       <c r="V56">
-        <v>0.1086959452610295</v>
+        <v>0.1067196553471927</v>
       </c>
       <c r="W56">
-        <v>0.1109999913947895</v>
+        <v>0.111246111854203</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8695675620882364</v>
+        <v>0.8537572427775413</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1320267569871508</v>
+        <v>0.1328141231537761</v>
       </c>
       <c r="C57">
-        <v>9679.700658425398</v>
+        <v>7632.686984514527</v>
       </c>
       <c r="D57">
-        <v>80705.82418877177</v>
+        <v>79975.54003359447</v>
       </c>
       <c r="E57">
-        <v>43176.17165698935</v>
+        <v>44492.90117572292</v>
       </c>
       <c r="F57">
-        <v>72420.12353034638</v>
+        <v>73736.85304907995</v>
       </c>
       <c r="G57">
         <v>1394</v>
@@ -5967,37 +5967,37 @@
         <v>7700</v>
       </c>
       <c r="M57">
-        <v>9018.957162752113</v>
+        <v>9182.938202074878</v>
       </c>
       <c r="N57">
-        <v>-1318.957162752113</v>
+        <v>-1482.938202074878</v>
       </c>
       <c r="O57">
-        <v>-164.8696453440141</v>
+        <v>-185.3672752593598</v>
       </c>
       <c r="P57">
-        <v>-1154.087517408099</v>
+        <v>-1297.570926815518</v>
       </c>
       <c r="Q57">
-        <v>510.9124825919014</v>
+        <v>367.4290731844817</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1574253232607536</v>
+        <v>0.1599622624257707</v>
       </c>
       <c r="T57">
-        <v>2.175785318457013</v>
+        <v>2.225234984785581</v>
       </c>
       <c r="U57">
         <v>0.1245366166625341</v>
       </c>
       <c r="V57">
-        <v>0.1067196553471927</v>
+        <v>0.1048139472159928</v>
       </c>
       <c r="W57">
-        <v>0.111246111854203</v>
+        <v>0.1114834422972089</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8537572427775413</v>
+        <v>0.8385115777279424</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1328141231537761</v>
+        <v>0.1336014893204014</v>
       </c>
       <c r="C58">
-        <v>7632.686984514527</v>
+        <v>5598.771061911917</v>
       </c>
       <c r="D58">
-        <v>79975.54003359447</v>
+        <v>79258.35362972543</v>
       </c>
       <c r="E58">
-        <v>44492.90117572292</v>
+        <v>45809.63069445649</v>
       </c>
       <c r="F58">
-        <v>73736.85304907995</v>
+        <v>75053.58256781352</v>
       </c>
       <c r="G58">
         <v>1394</v>
@@ -6049,37 +6049,37 @@
         <v>7700</v>
       </c>
       <c r="M58">
-        <v>9182.938202074878</v>
+        <v>9346.919241397643</v>
       </c>
       <c r="N58">
-        <v>-1482.938202074878</v>
+        <v>-1646.919241397643</v>
       </c>
       <c r="O58">
-        <v>-185.3672752593598</v>
+        <v>-205.8649051747054</v>
       </c>
       <c r="P58">
-        <v>-1297.570926815518</v>
+        <v>-1441.054336222938</v>
       </c>
       <c r="Q58">
-        <v>367.4290731844817</v>
+        <v>223.945663777062</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1599622624257707</v>
+        <v>0.1626171987612537</v>
       </c>
       <c r="T58">
-        <v>2.225234984785581</v>
+        <v>2.276984635594548</v>
       </c>
       <c r="U58">
         <v>0.1245366166625341</v>
       </c>
       <c r="V58">
-        <v>0.1048139472159928</v>
+        <v>0.1029751060367649</v>
       </c>
       <c r="W58">
-        <v>0.1114834422972089</v>
+        <v>0.1117124453562497</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8385115777279424</v>
+        <v>0.8238008482941188</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1336014893204014</v>
+        <v>0.1343888554870268</v>
       </c>
       <c r="C59">
-        <v>5598.771061911917</v>
+        <v>3577.603657313448</v>
       </c>
       <c r="D59">
-        <v>79258.35362972543</v>
+        <v>78553.91574386053</v>
       </c>
       <c r="E59">
-        <v>45809.63069445649</v>
+        <v>47126.36021319006</v>
       </c>
       <c r="F59">
-        <v>75053.58256781352</v>
+        <v>76370.31208654708</v>
       </c>
       <c r="G59">
         <v>1394</v>
@@ -6131,37 +6131,37 @@
         <v>7700</v>
       </c>
       <c r="M59">
-        <v>9346.919241397643</v>
+        <v>9510.900280720409</v>
       </c>
       <c r="N59">
-        <v>-1646.919241397643</v>
+        <v>-1810.900280720409</v>
       </c>
       <c r="O59">
-        <v>-205.8649051747054</v>
+        <v>-226.3625350900511</v>
       </c>
       <c r="P59">
-        <v>-1441.054336222938</v>
+        <v>-1584.537745630358</v>
       </c>
       <c r="Q59">
-        <v>223.945663777062</v>
+        <v>80.46225436964232</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1626171987612537</v>
+        <v>0.1653985606365217</v>
       </c>
       <c r="T59">
-        <v>2.276984635594548</v>
+        <v>2.331198555489657</v>
       </c>
       <c r="U59">
         <v>0.1245366166625341</v>
       </c>
       <c r="V59">
-        <v>0.1029751060367649</v>
+        <v>0.101199673174062</v>
       </c>
       <c r="W59">
-        <v>0.1117124453562497</v>
+        <v>0.1119335517580822</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8238008482941188</v>
+        <v>0.809597385392496</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1343888554870268</v>
+        <v>0.1849196156511418</v>
       </c>
       <c r="C60">
-        <v>3577.603657313462</v>
+        <v>-26271.32858370775</v>
       </c>
       <c r="D60">
-        <v>78553.91574386053</v>
+        <v>50021.71302157289</v>
       </c>
       <c r="E60">
-        <v>47126.36021319004</v>
+        <v>48443.08973192361</v>
       </c>
       <c r="F60">
-        <v>76370.31208654707</v>
+        <v>77687.04160528064</v>
       </c>
       <c r="G60">
         <v>1394</v>
@@ -6213,45 +6213,45 @@
         <v>7700</v>
       </c>
       <c r="M60">
-        <v>9510.900280720407</v>
+        <v>16060.75613999724</v>
       </c>
       <c r="N60">
-        <v>-1810.900280720407</v>
+        <v>-8360.75613999724</v>
       </c>
       <c r="O60">
-        <v>-226.3625350900509</v>
+        <v>-1045.094517499655</v>
       </c>
       <c r="P60">
-        <v>-1584.537745630356</v>
+        <v>-7315.661622497585</v>
       </c>
       <c r="Q60">
-        <v>80.46225436964392</v>
+        <v>-5650.661622497585</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1653985606365216</v>
+        <v>0.1713531450361679</v>
       </c>
       <c r="T60">
-        <v>2.331198555489656</v>
+        <v>2.447264488700875</v>
       </c>
       <c r="U60">
-        <v>0.1245366166625341</v>
+        <v>0.2067366166625341</v>
       </c>
       <c r="V60">
-        <v>0.101199673174062</v>
+        <v>0.05992868527547206</v>
       </c>
       <c r="W60">
-        <v>0.1119335517580822</v>
+        <v>0.1943471630276492</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y60">
-        <v>0.8095973853924963</v>
+        <v>0.4794294822037765</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1849196156511418</v>
+        <v>0.1865289818177672</v>
       </c>
       <c r="C61">
-        <v>-26271.32858370775</v>
+        <v>-28160.10269122264</v>
       </c>
       <c r="D61">
-        <v>50021.71302157289</v>
+        <v>49449.66843279156</v>
       </c>
       <c r="E61">
-        <v>48443.08973192361</v>
+        <v>49759.81925065718</v>
       </c>
       <c r="F61">
-        <v>77687.04160528064</v>
+        <v>79003.77112401421</v>
       </c>
       <c r="G61">
         <v>1394</v>
@@ -6295,37 +6295,37 @@
         <v>7700</v>
       </c>
       <c r="M61">
-        <v>16060.75613999724</v>
+        <v>16332.97234575991</v>
       </c>
       <c r="N61">
-        <v>-8360.75613999724</v>
+        <v>-8632.972345759907</v>
       </c>
       <c r="O61">
-        <v>-1045.094517499655</v>
+        <v>-1079.121543219988</v>
       </c>
       <c r="P61">
-        <v>-7315.661622497585</v>
+        <v>-7553.850802539919</v>
       </c>
       <c r="Q61">
-        <v>-5650.661622497585</v>
+        <v>-5888.850802539919</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1713531450361679</v>
+        <v>0.1744919736620721</v>
       </c>
       <c r="T61">
-        <v>2.447264488700875</v>
+        <v>2.508446100918397</v>
       </c>
       <c r="U61">
         <v>0.2067366166625341</v>
       </c>
       <c r="V61">
-        <v>0.05992868527547206</v>
+        <v>0.05892987385421418</v>
       </c>
       <c r="W61">
-        <v>0.1943471630276492</v>
+        <v>0.1945536539215639</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.4794294822037765</v>
+        <v>0.4714389908337134</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1865289818177672</v>
+        <v>0.1881383479843925</v>
       </c>
       <c r="C62">
-        <v>-28160.10269122264</v>
+        <v>-30035.94101270349</v>
       </c>
       <c r="D62">
-        <v>49449.66843279156</v>
+        <v>48890.5596300443</v>
       </c>
       <c r="E62">
-        <v>49759.81925065718</v>
+        <v>51076.54876939076</v>
       </c>
       <c r="F62">
-        <v>79003.77112401421</v>
+        <v>80320.50064274779</v>
       </c>
       <c r="G62">
         <v>1394</v>
@@ -6377,37 +6377,37 @@
         <v>7700</v>
       </c>
       <c r="M62">
-        <v>16332.97234575991</v>
+        <v>16605.18855152257</v>
       </c>
       <c r="N62">
-        <v>-8632.972345759907</v>
+        <v>-8905.188551522573</v>
       </c>
       <c r="O62">
-        <v>-1079.121543219988</v>
+        <v>-1113.148568940322</v>
       </c>
       <c r="P62">
-        <v>-7553.850802539919</v>
+        <v>-7792.039982582251</v>
       </c>
       <c r="Q62">
-        <v>-5888.850802539919</v>
+        <v>-6127.039982582251</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1744919736620721</v>
+        <v>0.1777917678585355</v>
       </c>
       <c r="T62">
-        <v>2.508446100918397</v>
+        <v>2.572765231711177</v>
       </c>
       <c r="U62">
         <v>0.2067366166625341</v>
       </c>
       <c r="V62">
-        <v>0.05892987385421418</v>
+        <v>0.05796381034840739</v>
       </c>
       <c r="W62">
-        <v>0.1945536539215639</v>
+        <v>0.1947533746222356</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4714389908337134</v>
+        <v>0.4637104827872591</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1881383479843925</v>
+        <v>0.1897477141510179</v>
       </c>
       <c r="C63">
-        <v>-30035.94101270349</v>
+        <v>-31899.27742269638</v>
       </c>
       <c r="D63">
-        <v>48890.5596300443</v>
+        <v>48343.95273878498</v>
       </c>
       <c r="E63">
-        <v>51076.54876939076</v>
+        <v>52393.27828812433</v>
       </c>
       <c r="F63">
-        <v>80320.50064274779</v>
+        <v>81637.23016148136</v>
       </c>
       <c r="G63">
         <v>1394</v>
@@ -6459,37 +6459,37 @@
         <v>7700</v>
       </c>
       <c r="M63">
-        <v>16605.18855152257</v>
+        <v>16877.40475728524</v>
       </c>
       <c r="N63">
-        <v>-8905.188551522573</v>
+        <v>-9177.40475728524</v>
       </c>
       <c r="O63">
-        <v>-1113.148568940322</v>
+        <v>-1147.175594660655</v>
       </c>
       <c r="P63">
-        <v>-7792.039982582251</v>
+        <v>-8030.229162624584</v>
       </c>
       <c r="Q63">
-        <v>-6127.039982582251</v>
+        <v>-6365.229162624584</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1777917678585355</v>
+        <v>0.1812652354337601</v>
       </c>
       <c r="T63">
-        <v>2.572765231711177</v>
+        <v>2.640469579914103</v>
       </c>
       <c r="U63">
         <v>0.2067366166625341</v>
       </c>
       <c r="V63">
-        <v>0.05796381034840739</v>
+        <v>0.05702891018149758</v>
       </c>
       <c r="W63">
-        <v>0.1947533746222356</v>
+        <v>0.1949466527196597</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4637104827872591</v>
+        <v>0.4562312814519807</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1897477141510179</v>
+        <v>0.1913570803176432</v>
       </c>
       <c r="C64">
-        <v>-31899.27742269638</v>
+        <v>-33750.52660704119</v>
       </c>
       <c r="D64">
-        <v>48343.95273878498</v>
+        <v>47809.43307317374</v>
       </c>
       <c r="E64">
-        <v>52393.27828812433</v>
+        <v>53710.0078068579</v>
       </c>
       <c r="F64">
-        <v>81637.23016148136</v>
+        <v>82953.95968021493</v>
       </c>
       <c r="G64">
         <v>1394</v>
@@ -6541,37 +6541,37 @@
         <v>7700</v>
       </c>
       <c r="M64">
-        <v>16877.40475728524</v>
+        <v>17149.6209630479</v>
       </c>
       <c r="N64">
-        <v>-9177.40475728524</v>
+        <v>-9449.620963047902</v>
       </c>
       <c r="O64">
-        <v>-1147.175594660655</v>
+        <v>-1181.202620380988</v>
       </c>
       <c r="P64">
-        <v>-8030.229162624584</v>
+        <v>-8268.418342666915</v>
       </c>
       <c r="Q64">
-        <v>-6365.229162624584</v>
+        <v>-6603.418342666915</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1812652354337601</v>
+        <v>0.1849264580130509</v>
       </c>
       <c r="T64">
-        <v>2.640469579914103</v>
+        <v>2.711833622614484</v>
       </c>
       <c r="U64">
         <v>0.2067366166625341</v>
       </c>
       <c r="V64">
-        <v>0.05702891018149758</v>
+        <v>0.05612368938496588</v>
       </c>
       <c r="W64">
-        <v>0.1949466527196597</v>
+        <v>0.1951337950044673</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4562312814519807</v>
+        <v>0.4489895150797271</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1913570803176432</v>
+        <v>0.1929664464842685</v>
       </c>
       <c r="C65">
-        <v>-33750.52660704119</v>
+        <v>-35590.08511207992</v>
       </c>
       <c r="D65">
-        <v>47809.43307317374</v>
+        <v>47286.60408686858</v>
       </c>
       <c r="E65">
-        <v>53710.0078068579</v>
+        <v>55026.73732559147</v>
       </c>
       <c r="F65">
-        <v>82953.95968021493</v>
+        <v>84270.6891989485</v>
       </c>
       <c r="G65">
         <v>1394</v>
@@ -6623,37 +6623,37 @@
         <v>7700</v>
       </c>
       <c r="M65">
-        <v>17149.6209630479</v>
+        <v>17421.83716881057</v>
       </c>
       <c r="N65">
-        <v>-9449.620963047902</v>
+        <v>-9721.837168810569</v>
       </c>
       <c r="O65">
-        <v>-1181.202620380988</v>
+        <v>-1215.229646101321</v>
       </c>
       <c r="P65">
-        <v>-8268.418342666915</v>
+        <v>-8506.607522709248</v>
       </c>
       <c r="Q65">
-        <v>-6603.418342666915</v>
+        <v>-6841.607522709248</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1849264580130509</v>
+        <v>0.1887910818467468</v>
       </c>
       <c r="T65">
-        <v>2.711833622614484</v>
+        <v>2.787162334353775</v>
       </c>
       <c r="U65">
         <v>0.2067366166625341</v>
       </c>
       <c r="V65">
-        <v>0.05612368938496588</v>
+        <v>0.05524675673832579</v>
       </c>
       <c r="W65">
-        <v>0.1951337950044673</v>
+        <v>0.1953150890928746</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4489895150797271</v>
+        <v>0.4419740539066063</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1929664464842685</v>
+        <v>0.1945758126508939</v>
       </c>
       <c r="C66">
-        <v>-35590.08511207992</v>
+        <v>-37418.33232576695</v>
       </c>
       <c r="D66">
-        <v>47286.60408686858</v>
+        <v>46775.08639191512</v>
       </c>
       <c r="E66">
-        <v>55026.73732559147</v>
+        <v>56343.46684432504</v>
       </c>
       <c r="F66">
-        <v>84270.6891989485</v>
+        <v>85587.41871768207</v>
       </c>
       <c r="G66">
         <v>1394</v>
@@ -6705,37 +6705,37 @@
         <v>7700</v>
       </c>
       <c r="M66">
-        <v>17421.83716881057</v>
+        <v>17694.05337457323</v>
       </c>
       <c r="N66">
-        <v>-9721.837168810569</v>
+        <v>-9994.053374573232</v>
       </c>
       <c r="O66">
-        <v>-1215.229646101321</v>
+        <v>-1249.256671821654</v>
       </c>
       <c r="P66">
-        <v>-8506.607522709248</v>
+        <v>-8744.796702751577</v>
       </c>
       <c r="Q66">
-        <v>-6841.607522709248</v>
+        <v>-7079.796702751577</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1887910818467468</v>
+        <v>0.1928765413280824</v>
       </c>
       <c r="T66">
-        <v>2.787162334353775</v>
+        <v>2.86679554390674</v>
       </c>
       <c r="U66">
         <v>0.2067366166625341</v>
       </c>
       <c r="V66">
-        <v>0.05524675673832579</v>
+        <v>0.05439680663465925</v>
       </c>
       <c r="W66">
-        <v>0.1953150890928746</v>
+        <v>0.1954908049016386</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4419740539066063</v>
+        <v>0.435174453077274</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1945758126508939</v>
+        <v>0.1961851788175192</v>
       </c>
       <c r="C67">
-        <v>-37418.33232576695</v>
+        <v>-39235.63139578238</v>
       </c>
       <c r="D67">
-        <v>46775.08639191512</v>
+        <v>46274.51684063326</v>
       </c>
       <c r="E67">
-        <v>56343.46684432504</v>
+        <v>57660.19636305861</v>
       </c>
       <c r="F67">
-        <v>85587.41871768207</v>
+        <v>86904.14823641564</v>
       </c>
       <c r="G67">
         <v>1394</v>
@@ -6787,37 +6787,37 @@
         <v>7700</v>
       </c>
       <c r="M67">
-        <v>17694.05337457323</v>
+        <v>17966.2695803359</v>
       </c>
       <c r="N67">
-        <v>-9994.053374573232</v>
+        <v>-10266.2695803359</v>
       </c>
       <c r="O67">
-        <v>-1249.256671821654</v>
+        <v>-1283.283697541987</v>
       </c>
       <c r="P67">
-        <v>-8744.796702751577</v>
+        <v>-8982.985882793912</v>
       </c>
       <c r="Q67">
-        <v>-7079.796702751577</v>
+        <v>-7317.985882793912</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1928765413280824</v>
+        <v>0.1972023219553789</v>
       </c>
       <c r="T67">
-        <v>2.86679554390674</v>
+        <v>2.951113059903997</v>
       </c>
       <c r="U67">
         <v>0.2067366166625341</v>
       </c>
       <c r="V67">
-        <v>0.05439680663465925</v>
+        <v>0.05357261259474017</v>
       </c>
       <c r="W67">
-        <v>0.1954908049016386</v>
+        <v>0.1956611959889248</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.435174453077274</v>
+        <v>0.4285809007579213</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1961851788175192</v>
+        <v>0.1977945449841446</v>
       </c>
       <c r="C68">
-        <v>-39235.63139578238</v>
+        <v>-41042.33008931772</v>
       </c>
       <c r="D68">
-        <v>46274.51684063326</v>
+        <v>45784.54766583149</v>
       </c>
       <c r="E68">
-        <v>57660.19636305861</v>
+        <v>58976.92588179218</v>
       </c>
       <c r="F68">
-        <v>86904.14823641564</v>
+        <v>88220.87775514921</v>
       </c>
       <c r="G68">
         <v>1394</v>
@@ -6869,37 +6869,37 @@
         <v>7700</v>
       </c>
       <c r="M68">
-        <v>17966.2695803359</v>
+        <v>18238.48578609856</v>
       </c>
       <c r="N68">
-        <v>-10266.2695803359</v>
+        <v>-10538.48578609856</v>
       </c>
       <c r="O68">
-        <v>-1283.283697541987</v>
+        <v>-1317.310723262321</v>
       </c>
       <c r="P68">
-        <v>-8982.985882793912</v>
+        <v>-9221.175062836244</v>
       </c>
       <c r="Q68">
-        <v>-7317.985882793912</v>
+        <v>-7556.175062836244</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1972023219553789</v>
+        <v>0.201790271105542</v>
       </c>
       <c r="T68">
-        <v>2.951113059903997</v>
+        <v>3.040540728385937</v>
       </c>
       <c r="U68">
         <v>0.2067366166625341</v>
       </c>
       <c r="V68">
-        <v>0.05357261259474017</v>
+        <v>0.05277302136198284</v>
       </c>
       <c r="W68">
-        <v>0.1956611959889248</v>
+        <v>0.1958265007750981</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4285809007579213</v>
+        <v>0.4221841708958627</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1977945449841446</v>
+        <v>0.1994039111507699</v>
       </c>
       <c r="C69">
-        <v>-41042.33008931772</v>
+        <v>-42838.76159881186</v>
       </c>
       <c r="D69">
-        <v>45784.54766583149</v>
+        <v>45304.84567507094</v>
       </c>
       <c r="E69">
-        <v>58976.92588179218</v>
+        <v>60293.65540052576</v>
       </c>
       <c r="F69">
-        <v>88220.87775514921</v>
+        <v>89537.60727388279</v>
       </c>
       <c r="G69">
         <v>1394</v>
@@ -6951,37 +6951,37 @@
         <v>7700</v>
       </c>
       <c r="M69">
-        <v>18238.48578609856</v>
+        <v>18510.70199186123</v>
       </c>
       <c r="N69">
-        <v>-10538.48578609856</v>
+        <v>-10810.70199186123</v>
       </c>
       <c r="O69">
-        <v>-1317.310723262321</v>
+        <v>-1351.337748982654</v>
       </c>
       <c r="P69">
-        <v>-9221.175062836244</v>
+        <v>-9459.364242878577</v>
       </c>
       <c r="Q69">
-        <v>-7556.175062836244</v>
+        <v>-7794.364242878577</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.201790271105542</v>
+        <v>0.2066649670775901</v>
       </c>
       <c r="T69">
-        <v>3.040540728385937</v>
+        <v>3.135557626147997</v>
       </c>
       <c r="U69">
         <v>0.2067366166625341</v>
       </c>
       <c r="V69">
-        <v>0.05277302136198284</v>
+        <v>0.05199694751842427</v>
       </c>
       <c r="W69">
-        <v>0.1958265007750981</v>
+        <v>0.1959869436557957</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4221841708958627</v>
+        <v>0.4159755801473941</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1994039111507699</v>
+        <v>0.2010132773173953</v>
       </c>
       <c r="C70">
-        <v>-42838.76159881186</v>
+        <v>-44625.24529756024</v>
       </c>
       <c r="D70">
-        <v>45304.84567507094</v>
+        <v>44835.09149505613</v>
       </c>
       <c r="E70">
-        <v>60293.65540052576</v>
+        <v>61610.38491925933</v>
       </c>
       <c r="F70">
-        <v>89537.60727388279</v>
+        <v>90854.33679261636</v>
       </c>
       <c r="G70">
         <v>1394</v>
@@ -7033,37 +7033,37 @@
         <v>7700</v>
       </c>
       <c r="M70">
-        <v>18510.70199186123</v>
+        <v>18782.9181976239</v>
       </c>
       <c r="N70">
-        <v>-10810.70199186123</v>
+        <v>-11082.9181976239</v>
       </c>
       <c r="O70">
-        <v>-1351.337748982654</v>
+        <v>-1385.364774702987</v>
       </c>
       <c r="P70">
-        <v>-9459.364242878577</v>
+        <v>-9697.553422920912</v>
       </c>
       <c r="Q70">
-        <v>-7794.364242878577</v>
+        <v>-8032.553422920912</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2066649670775901</v>
+        <v>0.211854159563964</v>
       </c>
       <c r="T70">
-        <v>3.135557626147997</v>
+        <v>3.23670464634632</v>
       </c>
       <c r="U70">
         <v>0.2067366166625341</v>
       </c>
       <c r="V70">
-        <v>0.05199694751842427</v>
+        <v>0.05124336856888188</v>
       </c>
       <c r="W70">
-        <v>0.1959869436557957</v>
+        <v>0.1961427360182122</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4159755801473941</v>
+        <v>0.4099469485510551</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2010132773173953</v>
+        <v>0.2026226434840206</v>
       </c>
       <c r="C71">
-        <v>-44625.24529756024</v>
+        <v>-46402.08744879797</v>
       </c>
       <c r="D71">
-        <v>44835.09149505613</v>
+        <v>44374.97886255196</v>
       </c>
       <c r="E71">
-        <v>61610.38491925933</v>
+        <v>62927.1144379929</v>
       </c>
       <c r="F71">
-        <v>90854.33679261636</v>
+        <v>92171.06631134993</v>
       </c>
       <c r="G71">
         <v>1394</v>
@@ -7115,37 +7115,37 @@
         <v>7700</v>
       </c>
       <c r="M71">
-        <v>18782.9181976239</v>
+        <v>19055.13440338656</v>
       </c>
       <c r="N71">
-        <v>-11082.9181976239</v>
+        <v>-11355.13440338656</v>
       </c>
       <c r="O71">
-        <v>-1385.364774702987</v>
+        <v>-1419.39180042332</v>
       </c>
       <c r="P71">
-        <v>-9697.553422920912</v>
+        <v>-9935.742602963241</v>
       </c>
       <c r="Q71">
-        <v>-8032.553422920912</v>
+        <v>-8270.742602963241</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.211854159563964</v>
+        <v>0.2173892982160961</v>
       </c>
       <c r="T71">
-        <v>3.23670464634632</v>
+        <v>3.34459480122453</v>
       </c>
       <c r="U71">
         <v>0.2067366166625341</v>
       </c>
       <c r="V71">
-        <v>0.05124336856888188</v>
+        <v>0.05051132044646929</v>
       </c>
       <c r="W71">
-        <v>0.1961427360182122</v>
+        <v>0.1962940771702739</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4099469485510551</v>
+        <v>0.4040905635717543</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2026226434840206</v>
+        <v>0.204232009650646</v>
       </c>
       <c r="C72">
-        <v>-46402.08744879797</v>
+        <v>-48169.58187156566</v>
       </c>
       <c r="D72">
-        <v>44374.97886255196</v>
+        <v>43924.21395851784</v>
       </c>
       <c r="E72">
-        <v>62927.1144379929</v>
+        <v>64243.84395672647</v>
       </c>
       <c r="F72">
-        <v>92171.06631134993</v>
+        <v>93487.7958300835</v>
       </c>
       <c r="G72">
         <v>1394</v>
@@ -7197,37 +7197,37 @@
         <v>7700</v>
       </c>
       <c r="M72">
-        <v>19055.13440338656</v>
+        <v>19327.35060914923</v>
       </c>
       <c r="N72">
-        <v>-11355.13440338656</v>
+        <v>-11627.35060914923</v>
       </c>
       <c r="O72">
-        <v>-1419.39180042332</v>
+        <v>-1453.418826143653</v>
       </c>
       <c r="P72">
-        <v>-9935.742602963241</v>
+        <v>-10173.93178300557</v>
       </c>
       <c r="Q72">
-        <v>-8270.742602963241</v>
+        <v>-8508.931783005573</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2173892982160961</v>
+        <v>0.2233061705683753</v>
       </c>
       <c r="T72">
-        <v>3.34459480122453</v>
+        <v>3.45992565643917</v>
       </c>
       <c r="U72">
         <v>0.2067366166625341</v>
       </c>
       <c r="V72">
-        <v>0.05051132044646929</v>
+        <v>0.04979989339792747</v>
       </c>
       <c r="W72">
-        <v>0.1962940771702739</v>
+        <v>0.1964411551912917</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4040905635717543</v>
+        <v>0.3983991471834197</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.204232009650646</v>
+        <v>0.2058413758172713</v>
       </c>
       <c r="C73">
-        <v>-48169.58187156564</v>
+        <v>-49928.01056639953</v>
       </c>
       <c r="D73">
-        <v>43924.21395851784</v>
+        <v>43482.51478241752</v>
       </c>
       <c r="E73">
-        <v>64243.84395672646</v>
+        <v>65560.57347546003</v>
       </c>
       <c r="F73">
-        <v>93487.79583008349</v>
+        <v>94804.52534881706</v>
       </c>
       <c r="G73">
         <v>1394</v>
@@ -7279,37 +7279,37 @@
         <v>7700</v>
       </c>
       <c r="M73">
-        <v>19327.35060914922</v>
+        <v>19599.56681491189</v>
       </c>
       <c r="N73">
-        <v>-11627.35060914922</v>
+        <v>-11899.56681491189</v>
       </c>
       <c r="O73">
-        <v>-1453.418826143653</v>
+        <v>-1487.445851863986</v>
       </c>
       <c r="P73">
-        <v>-10173.93178300557</v>
+        <v>-10412.1209630479</v>
       </c>
       <c r="Q73">
-        <v>-8508.93178300557</v>
+        <v>-8747.120963047901</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2233061705683753</v>
+        <v>0.2296456766601029</v>
       </c>
       <c r="T73">
-        <v>3.459925656439169</v>
+        <v>3.583494429883425</v>
       </c>
       <c r="U73">
         <v>0.2067366166625341</v>
       </c>
       <c r="V73">
-        <v>0.04979989339792747</v>
+        <v>0.04910822821184516</v>
       </c>
       <c r="W73">
-        <v>0.1964411551912917</v>
+        <v>0.1965841477117256</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3983991471834198</v>
+        <v>0.3928658256947613</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2058413758172713</v>
+        <v>0.2074507419838966</v>
       </c>
       <c r="C74">
-        <v>-49928.01056639953</v>
+        <v>-51677.64430364623</v>
       </c>
       <c r="D74">
-        <v>43482.51478241752</v>
+        <v>43049.6105639044</v>
       </c>
       <c r="E74">
-        <v>65560.57347546003</v>
+        <v>66877.3029941936</v>
       </c>
       <c r="F74">
-        <v>94804.52534881706</v>
+        <v>96121.25486755063</v>
       </c>
       <c r="G74">
         <v>1394</v>
@@ -7361,37 +7361,37 @@
         <v>7700</v>
       </c>
       <c r="M74">
-        <v>19599.56681491189</v>
+        <v>19871.78302067455</v>
       </c>
       <c r="N74">
-        <v>-11899.56681491189</v>
+        <v>-12171.78302067455</v>
       </c>
       <c r="O74">
-        <v>-1487.445851863986</v>
+        <v>-1521.472877584319</v>
       </c>
       <c r="P74">
-        <v>-10412.1209630479</v>
+        <v>-10650.31014309023</v>
       </c>
       <c r="Q74">
-        <v>-8747.120963047901</v>
+        <v>-8985.310143090233</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2296456766601029</v>
+        <v>0.2364547757956623</v>
       </c>
       <c r="T74">
-        <v>3.583494429883425</v>
+        <v>3.716216445805033</v>
       </c>
       <c r="U74">
         <v>0.2067366166625341</v>
       </c>
       <c r="V74">
-        <v>0.04910822821184516</v>
+        <v>0.04843551275688837</v>
       </c>
       <c r="W74">
-        <v>0.1965841477117256</v>
+        <v>0.19672322262886</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3928658256947613</v>
+        <v>0.387484102055107</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2074507419838966</v>
+        <v>0.209060108150522</v>
       </c>
       <c r="C75">
-        <v>-51677.64430364623</v>
+        <v>-53418.74317698092</v>
       </c>
       <c r="D75">
-        <v>43049.6105639044</v>
+        <v>42625.24120930328</v>
       </c>
       <c r="E75">
-        <v>66877.3029941936</v>
+        <v>68194.03251292717</v>
       </c>
       <c r="F75">
-        <v>96121.25486755063</v>
+        <v>97437.9843862842</v>
       </c>
       <c r="G75">
         <v>1394</v>
@@ -7443,37 +7443,37 @@
         <v>7700</v>
       </c>
       <c r="M75">
-        <v>19871.78302067455</v>
+        <v>20143.99922643722</v>
       </c>
       <c r="N75">
-        <v>-12171.78302067455</v>
+        <v>-12443.99922643722</v>
       </c>
       <c r="O75">
-        <v>-1521.472877584319</v>
+        <v>-1555.499903304652</v>
       </c>
       <c r="P75">
-        <v>-10650.31014309023</v>
+        <v>-10888.49932313257</v>
       </c>
       <c r="Q75">
-        <v>-8985.310143090233</v>
+        <v>-9223.499323132568</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2364547757956623</v>
+        <v>0.2437876517878032</v>
       </c>
       <c r="T75">
-        <v>3.716216445805033</v>
+        <v>3.859147847566765</v>
       </c>
       <c r="U75">
         <v>0.2067366166625341</v>
       </c>
       <c r="V75">
-        <v>0.04843551275688837</v>
+        <v>0.0477809788007142</v>
       </c>
       <c r="W75">
-        <v>0.19672322262886</v>
+        <v>0.1968585387644502</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.387484102055107</v>
+        <v>0.3822478304057136</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.209060108150522</v>
+        <v>0.2106694743171473</v>
       </c>
       <c r="C76">
-        <v>-53418.74317698092</v>
+        <v>-55151.55712450654</v>
       </c>
       <c r="D76">
-        <v>42625.24120930328</v>
+        <v>42209.15678051122</v>
       </c>
       <c r="E76">
-        <v>68194.03251292717</v>
+        <v>69510.76203166074</v>
       </c>
       <c r="F76">
-        <v>97437.9843862842</v>
+        <v>98754.71390501776</v>
       </c>
       <c r="G76">
         <v>1394</v>
@@ -7525,37 +7525,37 @@
         <v>7700</v>
       </c>
       <c r="M76">
-        <v>20143.99922643722</v>
+        <v>20416.21543219988</v>
       </c>
       <c r="N76">
-        <v>-12443.99922643722</v>
+        <v>-12716.21543219988</v>
       </c>
       <c r="O76">
-        <v>-1555.499903304652</v>
+        <v>-1589.526929024985</v>
       </c>
       <c r="P76">
-        <v>-10888.49932313257</v>
+        <v>-11126.6885031749</v>
       </c>
       <c r="Q76">
-        <v>-9223.499323132568</v>
+        <v>-9461.688503174897</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2437876517878032</v>
+        <v>0.2517071578593153</v>
       </c>
       <c r="T76">
-        <v>3.859147847566765</v>
+        <v>4.013513761469437</v>
       </c>
       <c r="U76">
         <v>0.2067366166625341</v>
       </c>
       <c r="V76">
-        <v>0.0477809788007142</v>
+        <v>0.04714389908337135</v>
       </c>
       <c r="W76">
-        <v>0.1968585387644502</v>
+        <v>0.196990246469758</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3822478304057136</v>
+        <v>0.3771511926669708</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2106694743171473</v>
+        <v>0.2122788404837727</v>
       </c>
       <c r="C77">
-        <v>-55151.55712450654</v>
+        <v>-56876.32641962817</v>
       </c>
       <c r="D77">
-        <v>42209.15678051122</v>
+        <v>41801.11700412317</v>
       </c>
       <c r="E77">
-        <v>69510.76203166074</v>
+        <v>70827.49155039432</v>
       </c>
       <c r="F77">
-        <v>98754.71390501776</v>
+        <v>100071.4434237513</v>
       </c>
       <c r="G77">
         <v>1394</v>
@@ -7607,37 +7607,37 @@
         <v>7700</v>
       </c>
       <c r="M77">
-        <v>20416.21543219988</v>
+        <v>20688.43163796255</v>
       </c>
       <c r="N77">
-        <v>-12716.21543219988</v>
+        <v>-12988.43163796255</v>
       </c>
       <c r="O77">
-        <v>-1589.526929024985</v>
+        <v>-1623.553954745319</v>
       </c>
       <c r="P77">
-        <v>-11126.6885031749</v>
+        <v>-11364.87768321723</v>
       </c>
       <c r="Q77">
-        <v>-9461.688503174897</v>
+        <v>-9699.877683217233</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2517071578593153</v>
+        <v>0.2602866227701201</v>
       </c>
       <c r="T77">
-        <v>4.013513761469437</v>
+        <v>4.180743501530663</v>
       </c>
       <c r="U77">
         <v>0.2067366166625341</v>
       </c>
       <c r="V77">
-        <v>0.04714389908337135</v>
+        <v>0.04652358462174803</v>
       </c>
       <c r="W77">
-        <v>0.196990246469758</v>
+        <v>0.1971184881828208</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3771511926669708</v>
+        <v>0.3721886769739843</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2122788404837727</v>
+        <v>0.213888206650398</v>
       </c>
       <c r="C78">
-        <v>-56876.32641962817</v>
+        <v>-58593.28213372774</v>
       </c>
       <c r="D78">
-        <v>41801.11700412317</v>
+        <v>41400.89080875718</v>
       </c>
       <c r="E78">
-        <v>70827.49155039432</v>
+        <v>72144.22106912789</v>
       </c>
       <c r="F78">
-        <v>100071.4434237513</v>
+        <v>101388.1729424849</v>
       </c>
       <c r="G78">
         <v>1394</v>
@@ -7689,37 +7689,37 @@
         <v>7700</v>
       </c>
       <c r="M78">
-        <v>20688.43163796255</v>
+        <v>20960.64784372522</v>
       </c>
       <c r="N78">
-        <v>-12988.43163796255</v>
+        <v>-13260.64784372522</v>
       </c>
       <c r="O78">
-        <v>-1623.553954745319</v>
+        <v>-1657.580980465652</v>
       </c>
       <c r="P78">
-        <v>-11364.87768321723</v>
+        <v>-11603.06686325956</v>
       </c>
       <c r="Q78">
-        <v>-9699.877683217233</v>
+        <v>-9938.066863259563</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2602866227701201</v>
+        <v>0.2696121281079514</v>
       </c>
       <c r="T78">
-        <v>4.180743501530663</v>
+        <v>4.362514958118953</v>
       </c>
       <c r="U78">
         <v>0.2067366166625341</v>
       </c>
       <c r="V78">
-        <v>0.04652358462174803</v>
+        <v>0.04591938222406299</v>
       </c>
       <c r="W78">
-        <v>0.1971184881828208</v>
+        <v>0.1972433989422976</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3721886769739843</v>
+        <v>0.367355057792504</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.213888206650398</v>
+        <v>0.2154975728170233</v>
       </c>
       <c r="C79">
-        <v>-58593.28213372774</v>
+        <v>-60302.64657251175</v>
       </c>
       <c r="D79">
-        <v>41400.89080875718</v>
+        <v>41008.25588870674</v>
       </c>
       <c r="E79">
-        <v>72144.22106912789</v>
+        <v>73460.95058786146</v>
       </c>
       <c r="F79">
-        <v>101388.1729424849</v>
+        <v>102704.9024612185</v>
       </c>
       <c r="G79">
         <v>1394</v>
@@ -7771,37 +7771,37 @@
         <v>7700</v>
       </c>
       <c r="M79">
-        <v>20960.64784372522</v>
+        <v>21232.86404948788</v>
       </c>
       <c r="N79">
-        <v>-13260.64784372522</v>
+        <v>-13532.86404948788</v>
       </c>
       <c r="O79">
-        <v>-1657.580980465652</v>
+        <v>-1691.608006185985</v>
       </c>
       <c r="P79">
-        <v>-11603.06686325956</v>
+        <v>-11841.2560433019</v>
       </c>
       <c r="Q79">
-        <v>-9938.066863259563</v>
+        <v>-10176.2560433019</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2696121281079514</v>
+        <v>0.2797854066583129</v>
       </c>
       <c r="T79">
-        <v>4.362514958118953</v>
+        <v>4.560811092578906</v>
       </c>
       <c r="U79">
         <v>0.2067366166625341</v>
       </c>
       <c r="V79">
-        <v>0.04591938222406299</v>
+        <v>0.04533067219554936</v>
       </c>
       <c r="W79">
-        <v>0.1972433989422976</v>
+        <v>0.1973651068617878</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.367355057792504</v>
+        <v>0.362645377564395</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2154975728170233</v>
+        <v>0.2171069389836487</v>
       </c>
       <c r="C80">
-        <v>-60302.64657251175</v>
+        <v>-62004.63368776274</v>
       </c>
       <c r="D80">
-        <v>41008.25588870674</v>
+        <v>40622.99829218932</v>
       </c>
       <c r="E80">
-        <v>73460.95058786146</v>
+        <v>74777.68010659503</v>
       </c>
       <c r="F80">
-        <v>102704.9024612185</v>
+        <v>104021.6319799521</v>
       </c>
       <c r="G80">
         <v>1394</v>
@@ -7853,37 +7853,37 @@
         <v>7700</v>
       </c>
       <c r="M80">
-        <v>21232.86404948788</v>
+        <v>21505.08025525054</v>
       </c>
       <c r="N80">
-        <v>-13532.86404948788</v>
+        <v>-13805.08025525054</v>
       </c>
       <c r="O80">
-        <v>-1691.608006185985</v>
+        <v>-1725.635031906318</v>
       </c>
       <c r="P80">
-        <v>-11841.2560433019</v>
+        <v>-12079.44522334423</v>
       </c>
       <c r="Q80">
-        <v>-10176.2560433019</v>
+        <v>-10414.44522334423</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2797854066583129</v>
+        <v>0.2909275688801373</v>
       </c>
       <c r="T80">
-        <v>4.560811092578906</v>
+        <v>4.777992573177901</v>
       </c>
       <c r="U80">
         <v>0.2067366166625341</v>
       </c>
       <c r="V80">
-        <v>0.04533067219554936</v>
+        <v>0.04475686621839051</v>
       </c>
       <c r="W80">
-        <v>0.1973651068617878</v>
+        <v>0.1974837335681264</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.362645377564395</v>
+        <v>0.3580549297471242</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2171069389836487</v>
+        <v>0.218716305150274</v>
       </c>
       <c r="C81">
-        <v>-62004.63368776274</v>
+        <v>-63699.44946609753</v>
       </c>
       <c r="D81">
-        <v>40622.99829218932</v>
+        <v>40244.9120325881</v>
       </c>
       <c r="E81">
-        <v>74777.68010659503</v>
+        <v>76094.4096253286</v>
       </c>
       <c r="F81">
-        <v>104021.6319799521</v>
+        <v>105338.3614986856</v>
       </c>
       <c r="G81">
         <v>1394</v>
@@ -7935,37 +7935,37 @@
         <v>7700</v>
       </c>
       <c r="M81">
-        <v>21505.08025525054</v>
+        <v>21777.29646101321</v>
       </c>
       <c r="N81">
-        <v>-13805.08025525054</v>
+        <v>-14077.29646101321</v>
       </c>
       <c r="O81">
-        <v>-1725.635031906318</v>
+        <v>-1759.662057626651</v>
       </c>
       <c r="P81">
-        <v>-12079.44522334423</v>
+        <v>-12317.63440338656</v>
       </c>
       <c r="Q81">
-        <v>-10414.44522334423</v>
+        <v>-10652.63440338656</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2909275688801373</v>
+        <v>0.3031839473241442</v>
       </c>
       <c r="T81">
-        <v>4.777992573177901</v>
+        <v>5.016892201836796</v>
       </c>
       <c r="U81">
         <v>0.2067366166625341</v>
       </c>
       <c r="V81">
-        <v>0.04475686621839051</v>
+        <v>0.04419740539066063</v>
       </c>
       <c r="W81">
-        <v>0.1974837335681264</v>
+        <v>0.1975993946068065</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3580549297471242</v>
+        <v>0.3535792431252851</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.218716305150274</v>
+        <v>0.2203256713168993</v>
       </c>
       <c r="C82">
-        <v>-63699.44946609753</v>
+        <v>-65387.29229621583</v>
       </c>
       <c r="D82">
-        <v>40244.9120325881</v>
+        <v>39873.79872120336</v>
       </c>
       <c r="E82">
-        <v>76094.4096253286</v>
+        <v>77411.13914406217</v>
       </c>
       <c r="F82">
-        <v>105338.3614986856</v>
+        <v>106655.0910174192</v>
       </c>
       <c r="G82">
         <v>1394</v>
@@ -8017,37 +8017,37 @@
         <v>7700</v>
       </c>
       <c r="M82">
-        <v>21777.29646101321</v>
+        <v>22049.51266677587</v>
       </c>
       <c r="N82">
-        <v>-14077.29646101321</v>
+        <v>-14349.51266677587</v>
       </c>
       <c r="O82">
-        <v>-1759.662057626651</v>
+        <v>-1793.689083346984</v>
       </c>
       <c r="P82">
-        <v>-12317.63440338656</v>
+        <v>-12555.82358342889</v>
       </c>
       <c r="Q82">
-        <v>-10652.63440338656</v>
+        <v>-10890.82358342889</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3031839473241442</v>
+        <v>0.3167304708675202</v>
       </c>
       <c r="T82">
-        <v>5.016892201836796</v>
+        <v>5.280939159828207</v>
       </c>
       <c r="U82">
         <v>0.2067366166625341</v>
       </c>
       <c r="V82">
-        <v>0.04419740539066063</v>
+        <v>0.04365175841052903</v>
       </c>
       <c r="W82">
-        <v>0.1975993946068065</v>
+        <v>0.197712199817371</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3535792431252851</v>
+        <v>0.3492140672842322</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2203256713168993</v>
+        <v>0.2219350374835247</v>
       </c>
       <c r="C83">
-        <v>-65387.29229621583</v>
+        <v>-67068.35331601567</v>
       </c>
       <c r="D83">
-        <v>39873.79872120336</v>
+        <v>39509.4672201371</v>
       </c>
       <c r="E83">
-        <v>77411.13914406217</v>
+        <v>78727.86866279574</v>
       </c>
       <c r="F83">
-        <v>106655.0910174192</v>
+        <v>107971.8205361528</v>
       </c>
       <c r="G83">
         <v>1394</v>
@@ -8099,37 +8099,37 @@
         <v>7700</v>
       </c>
       <c r="M83">
-        <v>22049.51266677587</v>
+        <v>22321.72887253854</v>
       </c>
       <c r="N83">
-        <v>-14349.51266677587</v>
+        <v>-14621.72887253854</v>
       </c>
       <c r="O83">
-        <v>-1793.689083346984</v>
+        <v>-1827.716109067318</v>
       </c>
       <c r="P83">
-        <v>-12555.82358342889</v>
+        <v>-12794.01276347122</v>
       </c>
       <c r="Q83">
-        <v>-10890.82358342889</v>
+        <v>-11129.01276347122</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3167304708675202</v>
+        <v>0.3317821636934936</v>
       </c>
       <c r="T83">
-        <v>5.280939159828207</v>
+        <v>5.574324668707551</v>
       </c>
       <c r="U83">
         <v>0.2067366166625341</v>
       </c>
       <c r="V83">
-        <v>0.04365175841052903</v>
+        <v>0.04311941989332745</v>
       </c>
       <c r="W83">
-        <v>0.197712199817371</v>
+        <v>0.1978222536813364</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3492140672842322</v>
+        <v>0.3449553591466196</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2219350374835247</v>
+        <v>0.22354440365015</v>
       </c>
       <c r="C84">
-        <v>-67068.35331601567</v>
+        <v>-68742.81674085092</v>
       </c>
       <c r="D84">
-        <v>39509.4672201371</v>
+        <v>39151.73331403542</v>
       </c>
       <c r="E84">
-        <v>78727.86866279574</v>
+        <v>80044.59818152932</v>
       </c>
       <c r="F84">
-        <v>107971.8205361528</v>
+        <v>109288.5500548863</v>
       </c>
       <c r="G84">
         <v>1394</v>
@@ -8181,37 +8181,37 @@
         <v>7700</v>
       </c>
       <c r="M84">
-        <v>22321.72887253854</v>
+        <v>22593.94507830121</v>
       </c>
       <c r="N84">
-        <v>-14621.72887253854</v>
+        <v>-14893.94507830121</v>
       </c>
       <c r="O84">
-        <v>-1827.716109067318</v>
+        <v>-1861.743134787651</v>
       </c>
       <c r="P84">
-        <v>-12794.01276347122</v>
+        <v>-13032.20194351356</v>
       </c>
       <c r="Q84">
-        <v>-11129.01276347122</v>
+        <v>-11367.20194351356</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3317821636934936</v>
+        <v>0.3486046439107579</v>
       </c>
       <c r="T84">
-        <v>5.574324668707551</v>
+        <v>5.902226119807996</v>
       </c>
       <c r="U84">
         <v>0.2067366166625341</v>
       </c>
       <c r="V84">
-        <v>0.04311941989332745</v>
+        <v>0.0425999088102753</v>
       </c>
       <c r="W84">
-        <v>0.1978222536813364</v>
+        <v>0.1979296556449653</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3449553591466196</v>
+        <v>0.3407992704822025</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.22354440365015</v>
+        <v>0.2251537698167754</v>
       </c>
       <c r="C85">
-        <v>-68742.81674085092</v>
+        <v>-70410.86017411618</v>
       </c>
       <c r="D85">
-        <v>39151.73331403542</v>
+        <v>38800.41939950373</v>
       </c>
       <c r="E85">
-        <v>80044.59818152932</v>
+        <v>81361.32770026289</v>
       </c>
       <c r="F85">
-        <v>109288.5500548863</v>
+        <v>110605.2795736199</v>
       </c>
       <c r="G85">
         <v>1394</v>
@@ -8263,37 +8263,37 @@
         <v>7700</v>
       </c>
       <c r="M85">
-        <v>22593.94507830121</v>
+        <v>22866.16128406387</v>
       </c>
       <c r="N85">
-        <v>-14893.94507830121</v>
+        <v>-15166.16128406387</v>
       </c>
       <c r="O85">
-        <v>-1861.743134787651</v>
+        <v>-1895.770160507984</v>
       </c>
       <c r="P85">
-        <v>-13032.20194351356</v>
+        <v>-13270.39112355589</v>
       </c>
       <c r="Q85">
-        <v>-11367.20194351356</v>
+        <v>-11605.39112355589</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3486046439107579</v>
+        <v>0.3675299341551804</v>
       </c>
       <c r="T85">
-        <v>5.902226119807996</v>
+        <v>6.271115252295997</v>
       </c>
       <c r="U85">
         <v>0.2067366166625341</v>
       </c>
       <c r="V85">
-        <v>0.0425999088102753</v>
+        <v>0.04209276703872441</v>
       </c>
       <c r="W85">
-        <v>0.1979296556449653</v>
+        <v>0.198034500418984</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3407992704822025</v>
+        <v>0.3367421363097952</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2251537698167753</v>
+        <v>0.2267631359834007</v>
       </c>
       <c r="C86">
-        <v>-70410.86017411615</v>
+        <v>-72072.6549012586</v>
       </c>
       <c r="D86">
-        <v>38800.41939950374</v>
+        <v>38455.35419109487</v>
       </c>
       <c r="E86">
-        <v>81361.32770026287</v>
+        <v>82678.05721899644</v>
       </c>
       <c r="F86">
-        <v>110605.2795736199</v>
+        <v>111922.0090923535</v>
       </c>
       <c r="G86">
         <v>1394</v>
@@ -8345,37 +8345,37 @@
         <v>7700</v>
       </c>
       <c r="M86">
-        <v>22866.16128406387</v>
+        <v>23138.37748982654</v>
       </c>
       <c r="N86">
-        <v>-15166.16128406387</v>
+        <v>-15438.37748982654</v>
       </c>
       <c r="O86">
-        <v>-1895.770160507984</v>
+        <v>-1929.797186228317</v>
       </c>
       <c r="P86">
-        <v>-13270.39112355589</v>
+        <v>-13508.58030359822</v>
       </c>
       <c r="Q86">
-        <v>-11605.39112355589</v>
+        <v>-11843.58030359822</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3675299341551801</v>
+        <v>0.3889785964321921</v>
       </c>
       <c r="T86">
-        <v>6.271115252295992</v>
+        <v>6.689189602449059</v>
       </c>
       <c r="U86">
         <v>0.2067366166625341</v>
       </c>
       <c r="V86">
-        <v>0.04209276703872442</v>
+        <v>0.04159755801473942</v>
       </c>
       <c r="W86">
-        <v>0.198034500418984</v>
+        <v>0.1981368782571434</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3367421363097953</v>
+        <v>0.3327804641179154</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2267631359834007</v>
+        <v>0.228372502150026</v>
       </c>
       <c r="C87">
-        <v>-72072.6549012586</v>
+        <v>-73728.36616823971</v>
       </c>
       <c r="D87">
-        <v>38455.35419109487</v>
+        <v>38116.37244284734</v>
       </c>
       <c r="E87">
-        <v>82678.05721899644</v>
+        <v>83994.78673773001</v>
       </c>
       <c r="F87">
-        <v>111922.0090923535</v>
+        <v>113238.738611087</v>
       </c>
       <c r="G87">
         <v>1394</v>
@@ -8427,37 +8427,37 @@
         <v>7700</v>
       </c>
       <c r="M87">
-        <v>23138.37748982654</v>
+        <v>23410.5936955892</v>
       </c>
       <c r="N87">
-        <v>-15438.37748982654</v>
+        <v>-15710.5936955892</v>
       </c>
       <c r="O87">
-        <v>-1929.797186228317</v>
+        <v>-1963.82421194865</v>
       </c>
       <c r="P87">
-        <v>-13508.58030359822</v>
+        <v>-13746.76948364055</v>
       </c>
       <c r="Q87">
-        <v>-11843.58030359822</v>
+        <v>-12081.76948364055</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3889785964321921</v>
+        <v>0.4134913533202059</v>
       </c>
       <c r="T87">
-        <v>6.689189602449059</v>
+        <v>7.166988859766849</v>
       </c>
       <c r="U87">
         <v>0.2067366166625341</v>
       </c>
       <c r="V87">
-        <v>0.04159755801473942</v>
+        <v>0.04111386547968431</v>
       </c>
       <c r="W87">
-        <v>0.1981368782571434</v>
+        <v>0.1982368752153456</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3327804641179154</v>
+        <v>0.3289109238374746</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.228372502150026</v>
+        <v>0.2299818683166514</v>
       </c>
       <c r="C88">
-        <v>-73728.36616823971</v>
+        <v>-75378.15344539794</v>
       </c>
       <c r="D88">
-        <v>38116.37244284734</v>
+        <v>37783.31468442268</v>
       </c>
       <c r="E88">
-        <v>83994.78673773001</v>
+        <v>85311.51625646358</v>
       </c>
       <c r="F88">
-        <v>113238.738611087</v>
+        <v>114555.4681298206</v>
       </c>
       <c r="G88">
         <v>1394</v>
@@ -8509,37 +8509,37 @@
         <v>7700</v>
       </c>
       <c r="M88">
-        <v>23410.5936955892</v>
+        <v>23682.80990135187</v>
       </c>
       <c r="N88">
-        <v>-15710.5936955892</v>
+        <v>-15982.80990135187</v>
       </c>
       <c r="O88">
-        <v>-1963.82421194865</v>
+        <v>-1997.851237668983</v>
       </c>
       <c r="P88">
-        <v>-13746.76948364055</v>
+        <v>-13984.95866368288</v>
       </c>
       <c r="Q88">
-        <v>-12081.76948364055</v>
+        <v>-12319.95866368288</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4134913533202059</v>
+        <v>0.4417753035756063</v>
       </c>
       <c r="T88">
-        <v>7.166988859766849</v>
+        <v>7.71829569513353</v>
       </c>
       <c r="U88">
         <v>0.2067366166625341</v>
       </c>
       <c r="V88">
-        <v>0.04111386547968431</v>
+        <v>0.04064129231325116</v>
       </c>
       <c r="W88">
-        <v>0.1982368752153456</v>
+        <v>0.1983345733928995</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3289109238374746</v>
+        <v>0.3251303385060093</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2299818683166514</v>
+        <v>0.2315912344832767</v>
       </c>
       <c r="C89">
-        <v>-75378.15344539794</v>
+        <v>-77022.17067759756</v>
       </c>
       <c r="D89">
-        <v>37783.31468442268</v>
+        <v>37456.02697095662</v>
       </c>
       <c r="E89">
-        <v>85311.51625646358</v>
+        <v>86628.24577519715</v>
       </c>
       <c r="F89">
-        <v>114555.4681298206</v>
+        <v>115872.1976485542</v>
       </c>
       <c r="G89">
         <v>1394</v>
@@ -8591,37 +8591,37 @@
         <v>7700</v>
       </c>
       <c r="M89">
-        <v>23682.80990135187</v>
+        <v>23955.02610711453</v>
       </c>
       <c r="N89">
-        <v>-15982.80990135187</v>
+        <v>-16255.02610711453</v>
       </c>
       <c r="O89">
-        <v>-1997.851237668983</v>
+        <v>-2031.878263389316</v>
       </c>
       <c r="P89">
-        <v>-13984.95866368288</v>
+        <v>-14223.14784372521</v>
       </c>
       <c r="Q89">
-        <v>-12319.95866368288</v>
+        <v>-12558.14784372521</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4417753035756063</v>
+        <v>0.4747732455402402</v>
       </c>
       <c r="T89">
-        <v>7.71829569513353</v>
+        <v>8.361487003061324</v>
       </c>
       <c r="U89">
         <v>0.2067366166625341</v>
       </c>
       <c r="V89">
-        <v>0.04064129231325116</v>
+        <v>0.04017945944605512</v>
       </c>
       <c r="W89">
-        <v>0.1983345733928995</v>
+        <v>0.1984300511573271</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3251303385060093</v>
+        <v>0.321435675568441</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2315912344832767</v>
+        <v>0.2332006006499021</v>
       </c>
       <c r="C90">
-        <v>-77022.17067759756</v>
+        <v>-78660.56652148812</v>
       </c>
       <c r="D90">
-        <v>37456.02697095662</v>
+        <v>37134.36064579964</v>
       </c>
       <c r="E90">
-        <v>86628.24577519715</v>
+        <v>87944.97529393072</v>
       </c>
       <c r="F90">
-        <v>115872.1976485542</v>
+        <v>117188.9271672878</v>
       </c>
       <c r="G90">
         <v>1394</v>
@@ -8673,37 +8673,37 @@
         <v>7700</v>
       </c>
       <c r="M90">
-        <v>23955.02610711453</v>
+        <v>24227.2423128772</v>
       </c>
       <c r="N90">
-        <v>-16255.02610711453</v>
+        <v>-16527.2423128772</v>
       </c>
       <c r="O90">
-        <v>-2031.878263389316</v>
+        <v>-2065.905289109649</v>
       </c>
       <c r="P90">
-        <v>-14223.14784372521</v>
+        <v>-14461.33702376755</v>
       </c>
       <c r="Q90">
-        <v>-12558.14784372521</v>
+        <v>-12796.33702376755</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4747732455402402</v>
+        <v>0.5137708133166258</v>
       </c>
       <c r="T90">
-        <v>8.361487003061324</v>
+        <v>9.121622185157811</v>
       </c>
       <c r="U90">
         <v>0.2067366166625341</v>
       </c>
       <c r="V90">
-        <v>0.04017945944605512</v>
+        <v>0.03972800484553765</v>
       </c>
       <c r="W90">
-        <v>0.1984300511573271</v>
+        <v>0.1985233833540149</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.321435675568441</v>
+        <v>0.3178240387643012</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2332006006499021</v>
+        <v>0.2348099668165274</v>
       </c>
       <c r="C91">
-        <v>-78660.56652148812</v>
+        <v>-80293.48457064255</v>
       </c>
       <c r="D91">
-        <v>37134.36064579964</v>
+        <v>36818.17211537879</v>
       </c>
       <c r="E91">
-        <v>87944.97529393072</v>
+        <v>89261.70481266431</v>
       </c>
       <c r="F91">
-        <v>117188.9271672878</v>
+        <v>118505.6566860213</v>
       </c>
       <c r="G91">
         <v>1394</v>
@@ -8755,37 +8755,37 @@
         <v>7700</v>
       </c>
       <c r="M91">
-        <v>24227.2423128772</v>
+        <v>24499.45851863986</v>
       </c>
       <c r="N91">
-        <v>-16527.2423128772</v>
+        <v>-16799.45851863986</v>
       </c>
       <c r="O91">
-        <v>-2065.905289109649</v>
+        <v>-2099.932314829983</v>
       </c>
       <c r="P91">
-        <v>-14461.33702376755</v>
+        <v>-14699.52620380988</v>
       </c>
       <c r="Q91">
-        <v>-12796.33702376755</v>
+        <v>-13034.52620380988</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5137708133166258</v>
+        <v>0.5605678946482883</v>
       </c>
       <c r="T91">
-        <v>9.121622185157811</v>
+        <v>10.03378440367359</v>
       </c>
       <c r="U91">
         <v>0.2067366166625341</v>
       </c>
       <c r="V91">
-        <v>0.03972800484553765</v>
+        <v>0.03928658256947612</v>
       </c>
       <c r="W91">
-        <v>0.1985233833540149</v>
+        <v>0.1986146415018873</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3178240387643012</v>
+        <v>0.314292660555809</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2348099668165274</v>
+        <v>0.2364193329831527</v>
       </c>
       <c r="C92">
-        <v>-80293.48457064255</v>
+        <v>-81921.06356929071</v>
       </c>
       <c r="D92">
-        <v>36818.17211537879</v>
+        <v>36507.3226354642</v>
       </c>
       <c r="E92">
-        <v>89261.70481266431</v>
+        <v>90578.43433139788</v>
       </c>
       <c r="F92">
-        <v>118505.6566860213</v>
+        <v>119822.3862047549</v>
       </c>
       <c r="G92">
         <v>1394</v>
@@ -8837,37 +8837,37 @@
         <v>7700</v>
       </c>
       <c r="M92">
-        <v>24499.45851863986</v>
+        <v>24771.67472440253</v>
       </c>
       <c r="N92">
-        <v>-16799.45851863986</v>
+        <v>-17071.67472440253</v>
       </c>
       <c r="O92">
-        <v>-2099.932314829983</v>
+        <v>-2133.959340550316</v>
       </c>
       <c r="P92">
-        <v>-14699.52620380988</v>
+        <v>-14937.71538385221</v>
       </c>
       <c r="Q92">
-        <v>-13034.52620380988</v>
+        <v>-13272.71538385221</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5605678946482883</v>
+        <v>0.6177643273869871</v>
       </c>
       <c r="T92">
-        <v>10.03378440367359</v>
+        <v>11.1486493374151</v>
       </c>
       <c r="U92">
         <v>0.2067366166625341</v>
       </c>
       <c r="V92">
-        <v>0.03928658256947612</v>
+        <v>0.03885486188189945</v>
       </c>
       <c r="W92">
-        <v>0.1986146415018873</v>
+        <v>0.1987038939761801</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.314292660555809</v>
+        <v>0.3108388950551957</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2364193329831527</v>
+        <v>0.2380286991497781</v>
       </c>
       <c r="C93">
-        <v>-81921.06356929071</v>
+        <v>-83543.4376153163</v>
       </c>
       <c r="D93">
-        <v>36507.3226354642</v>
+        <v>36201.67810817218</v>
       </c>
       <c r="E93">
-        <v>90578.43433139788</v>
+        <v>91895.16385013144</v>
       </c>
       <c r="F93">
-        <v>119822.3862047549</v>
+        <v>121139.1157234885</v>
       </c>
       <c r="G93">
         <v>1394</v>
@@ -8919,37 +8919,37 @@
         <v>7700</v>
       </c>
       <c r="M93">
-        <v>24771.67472440253</v>
+        <v>25043.89093016519</v>
       </c>
       <c r="N93">
-        <v>-17071.67472440253</v>
+        <v>-17343.89093016519</v>
       </c>
       <c r="O93">
-        <v>-2133.959340550316</v>
+        <v>-2167.986366270649</v>
       </c>
       <c r="P93">
-        <v>-14937.71538385221</v>
+        <v>-15175.90456389455</v>
       </c>
       <c r="Q93">
-        <v>-13272.71538385221</v>
+        <v>-13510.90456389455</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6177643273869871</v>
+        <v>0.6892598683103608</v>
       </c>
       <c r="T93">
-        <v>11.1486493374151</v>
+        <v>12.542230504592</v>
       </c>
       <c r="U93">
         <v>0.2067366166625341</v>
       </c>
       <c r="V93">
-        <v>0.03885486188189945</v>
+        <v>0.03843252642666142</v>
       </c>
       <c r="W93">
-        <v>0.1987038939761801</v>
+        <v>0.1987912061792927</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3108388950551957</v>
+        <v>0.3074602114132914</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2380286991497781</v>
+        <v>0.2396380653164034</v>
       </c>
       <c r="C94">
-        <v>-83543.4376153163</v>
+        <v>-85160.73635314133</v>
       </c>
       <c r="D94">
-        <v>36201.67810817218</v>
+        <v>35901.10888908072</v>
       </c>
       <c r="E94">
-        <v>91895.16385013144</v>
+        <v>93211.89336886501</v>
       </c>
       <c r="F94">
-        <v>121139.1157234885</v>
+        <v>122455.845242222</v>
       </c>
       <c r="G94">
         <v>1394</v>
@@ -9001,37 +9001,37 @@
         <v>7700</v>
       </c>
       <c r="M94">
-        <v>25043.89093016519</v>
+        <v>25316.10713592786</v>
       </c>
       <c r="N94">
-        <v>-17343.89093016519</v>
+        <v>-17616.10713592786</v>
       </c>
       <c r="O94">
-        <v>-2167.986366270649</v>
+        <v>-2202.013391990982</v>
       </c>
       <c r="P94">
-        <v>-15175.90456389455</v>
+        <v>-15414.09374393688</v>
       </c>
       <c r="Q94">
-        <v>-13510.90456389455</v>
+        <v>-13749.09374393688</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6892598683103608</v>
+        <v>0.7811827066404122</v>
       </c>
       <c r="T94">
-        <v>12.542230504592</v>
+        <v>14.33397771953371</v>
       </c>
       <c r="U94">
         <v>0.2067366166625341</v>
       </c>
       <c r="V94">
-        <v>0.03843252642666142</v>
+        <v>0.03801927345433172</v>
       </c>
       <c r="W94">
-        <v>0.1987912061792927</v>
+        <v>0.1988766407006179</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3074602114132914</v>
+        <v>0.3041541876346538</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2396380653164034</v>
+        <v>0.2412474314830288</v>
       </c>
       <c r="C95">
-        <v>-85160.73635314133</v>
+        <v>-86773.08515708119</v>
       </c>
       <c r="D95">
-        <v>35901.10888908072</v>
+        <v>35605.48960387441</v>
       </c>
       <c r="E95">
-        <v>93211.89336886501</v>
+        <v>94528.62288759858</v>
       </c>
       <c r="F95">
-        <v>122455.845242222</v>
+        <v>123772.5747609556</v>
       </c>
       <c r="G95">
         <v>1394</v>
@@ -9083,37 +9083,37 @@
         <v>7700</v>
       </c>
       <c r="M95">
-        <v>25316.10713592786</v>
+        <v>25588.32334169052</v>
       </c>
       <c r="N95">
-        <v>-17616.10713592786</v>
+        <v>-17888.32334169052</v>
       </c>
       <c r="O95">
-        <v>-2202.013391990982</v>
+        <v>-2236.040417711316</v>
       </c>
       <c r="P95">
-        <v>-15414.09374393688</v>
+        <v>-15652.28292397921</v>
       </c>
       <c r="Q95">
-        <v>-13749.09374393688</v>
+        <v>-13987.28292397921</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7811827066404122</v>
+        <v>0.903746491080481</v>
       </c>
       <c r="T95">
-        <v>14.33397771953371</v>
+        <v>16.72297400612266</v>
       </c>
       <c r="U95">
         <v>0.2067366166625341</v>
       </c>
       <c r="V95">
-        <v>0.03801927345433172</v>
+        <v>0.03761481309843458</v>
       </c>
       <c r="W95">
-        <v>0.1988766407006179</v>
+        <v>0.1989602574661702</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3041541876346538</v>
+        <v>0.3009185047874766</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2412474314830288</v>
+        <v>0.2428567976496541</v>
       </c>
       <c r="C96">
-        <v>-86773.08515708119</v>
+        <v>-88380.60530571469</v>
       </c>
       <c r="D96">
-        <v>35605.48960387441</v>
+        <v>35314.69897397449</v>
       </c>
       <c r="E96">
-        <v>94528.62288759858</v>
+        <v>95845.35240633215</v>
       </c>
       <c r="F96">
-        <v>123772.5747609556</v>
+        <v>125089.3042796892</v>
       </c>
       <c r="G96">
         <v>1394</v>
@@ -9165,37 +9165,37 @@
         <v>7700</v>
       </c>
       <c r="M96">
-        <v>25588.32334169052</v>
+        <v>25860.53954745319</v>
       </c>
       <c r="N96">
-        <v>-17888.32334169052</v>
+        <v>-18160.53954745319</v>
       </c>
       <c r="O96">
-        <v>-2236.040417711316</v>
+        <v>-2270.067443431648</v>
       </c>
       <c r="P96">
-        <v>-15652.28292397921</v>
+        <v>-15890.47210402154</v>
       </c>
       <c r="Q96">
-        <v>-13987.28292397921</v>
+        <v>-14225.47210402154</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.903746491080481</v>
+        <v>1.075335789296578</v>
       </c>
       <c r="T96">
-        <v>16.72297400612266</v>
+        <v>20.06756880734721</v>
       </c>
       <c r="U96">
         <v>0.2067366166625341</v>
       </c>
       <c r="V96">
-        <v>0.03761481309843458</v>
+        <v>0.03721886769739843</v>
       </c>
       <c r="W96">
-        <v>0.1989602574661702</v>
+        <v>0.1990421138787634</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3009185047874766</v>
+        <v>0.2977509415791875</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2428567976496541</v>
+        <v>0.2444661638162794</v>
       </c>
       <c r="C97">
-        <v>-88380.60530571469</v>
+        <v>-89983.414147779</v>
       </c>
       <c r="D97">
-        <v>35314.69897397449</v>
+        <v>35028.61965064376</v>
       </c>
       <c r="E97">
-        <v>95845.35240633215</v>
+        <v>97162.08192506572</v>
       </c>
       <c r="F97">
-        <v>125089.3042796892</v>
+        <v>126406.0337984228</v>
       </c>
       <c r="G97">
         <v>1394</v>
@@ -9247,37 +9247,37 @@
         <v>7700</v>
       </c>
       <c r="M97">
-        <v>25860.53954745319</v>
+        <v>26132.75575321585</v>
       </c>
       <c r="N97">
-        <v>-18160.53954745319</v>
+        <v>-18432.75575321585</v>
       </c>
       <c r="O97">
-        <v>-2270.067443431648</v>
+        <v>-2304.094469151982</v>
       </c>
       <c r="P97">
-        <v>-15890.47210402154</v>
+        <v>-16128.66128406387</v>
       </c>
       <c r="Q97">
-        <v>-14225.47210402154</v>
+        <v>-14463.66128406387</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.075335789296578</v>
+        <v>1.332719736620723</v>
       </c>
       <c r="T97">
-        <v>20.06756880734721</v>
+        <v>25.08446100918402</v>
       </c>
       <c r="U97">
         <v>0.2067366166625341</v>
       </c>
       <c r="V97">
-        <v>0.03721886769739843</v>
+        <v>0.03683117115888386</v>
       </c>
       <c r="W97">
-        <v>0.1990421138787634</v>
+        <v>0.1991222649494277</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2977509415791875</v>
+        <v>0.2946493692710709</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2444661638162794</v>
+        <v>0.2460755299829048</v>
       </c>
       <c r="C98">
-        <v>-89983.41414777897</v>
+        <v>-91581.62526006592</v>
       </c>
       <c r="D98">
-        <v>35028.61965064376</v>
+        <v>34747.13805709039</v>
       </c>
       <c r="E98">
-        <v>97162.08192506571</v>
+        <v>98478.81144379929</v>
       </c>
       <c r="F98">
-        <v>126406.0337984227</v>
+        <v>127722.7633171563</v>
       </c>
       <c r="G98">
         <v>1394</v>
@@ -9329,37 +9329,37 @@
         <v>7700</v>
       </c>
       <c r="M98">
-        <v>26132.75575321585</v>
+        <v>26404.97195897852</v>
       </c>
       <c r="N98">
-        <v>-18432.75575321585</v>
+        <v>-18704.97195897852</v>
       </c>
       <c r="O98">
-        <v>-2304.094469151981</v>
+        <v>-2338.121494872315</v>
       </c>
       <c r="P98">
-        <v>-16128.66128406387</v>
+        <v>-16366.8504641062</v>
       </c>
       <c r="Q98">
-        <v>-14463.66128406387</v>
+        <v>-14701.8504641062</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.33271973662072</v>
+        <v>1.761692982160959</v>
       </c>
       <c r="T98">
-        <v>25.08446100918395</v>
+        <v>33.44594801224527</v>
       </c>
       <c r="U98">
         <v>0.2067366166625341</v>
       </c>
       <c r="V98">
-        <v>0.03683117115888387</v>
+        <v>0.03645146836343145</v>
       </c>
       <c r="W98">
-        <v>0.1991222649494277</v>
+        <v>0.1992007634206969</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2946493692710709</v>
+        <v>0.2916117469074516</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2460755299829048</v>
+        <v>0.2476848961495302</v>
       </c>
       <c r="C99">
-        <v>-91581.62526006592</v>
+        <v>-93175.34859776615</v>
       </c>
       <c r="D99">
-        <v>34747.13805709039</v>
+        <v>34470.14423812374</v>
       </c>
       <c r="E99">
-        <v>98478.81144379929</v>
+        <v>99795.54096253286</v>
       </c>
       <c r="F99">
-        <v>127722.7633171563</v>
+        <v>129039.4928358899</v>
       </c>
       <c r="G99">
         <v>1394</v>
@@ -9411,37 +9411,37 @@
         <v>7700</v>
       </c>
       <c r="M99">
-        <v>26404.97195897852</v>
+        <v>26677.18816474118</v>
       </c>
       <c r="N99">
-        <v>-18704.97195897852</v>
+        <v>-18977.18816474118</v>
       </c>
       <c r="O99">
-        <v>-2338.121494872315</v>
+        <v>-2372.148520592648</v>
       </c>
       <c r="P99">
-        <v>-16366.8504641062</v>
+        <v>-16605.03964414854</v>
       </c>
       <c r="Q99">
-        <v>-14701.8504641062</v>
+        <v>-14940.03964414854</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.761692982160959</v>
+        <v>2.619639473241439</v>
       </c>
       <c r="T99">
-        <v>33.44594801224527</v>
+        <v>50.16892201836791</v>
       </c>
       <c r="U99">
         <v>0.2067366166625341</v>
       </c>
       <c r="V99">
-        <v>0.03645146836343145</v>
+        <v>0.03607951460462092</v>
       </c>
       <c r="W99">
-        <v>0.1992007634206969</v>
+        <v>0.1992776598823483</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2916117469074516</v>
+        <v>0.2886361168369674</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2476848961495302</v>
+        <v>0.2492942623161555</v>
       </c>
       <c r="C100">
-        <v>-93175.34859776615</v>
+        <v>-94764.69063767901</v>
       </c>
       <c r="D100">
-        <v>34470.14423812374</v>
+        <v>34197.53171694444</v>
       </c>
       <c r="E100">
-        <v>99795.54096253286</v>
+        <v>101112.2704812664</v>
       </c>
       <c r="F100">
-        <v>129039.4928358899</v>
+        <v>130356.2223546235</v>
       </c>
       <c r="G100">
         <v>1394</v>
@@ -9493,37 +9493,37 @@
         <v>7700</v>
       </c>
       <c r="M100">
-        <v>26677.18816474118</v>
+        <v>26949.40437050385</v>
       </c>
       <c r="N100">
-        <v>-18977.18816474118</v>
+        <v>-19249.40437050385</v>
       </c>
       <c r="O100">
-        <v>-2372.148520592648</v>
+        <v>-2406.175546312981</v>
       </c>
       <c r="P100">
-        <v>-16605.03964414854</v>
+        <v>-16843.22882419087</v>
       </c>
       <c r="Q100">
-        <v>-14940.03964414854</v>
+        <v>-15178.22882419087</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.619639473241439</v>
+        <v>5.193478946482879</v>
       </c>
       <c r="T100">
-        <v>50.16892201836791</v>
+        <v>100.3378440367358</v>
       </c>
       <c r="U100">
         <v>0.2067366166625341</v>
       </c>
       <c r="V100">
-        <v>0.03607951460462092</v>
+        <v>0.03571507506316011</v>
       </c>
       <c r="W100">
-        <v>0.1992776598823483</v>
+        <v>0.1993530028801279</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2886361168369674</v>
+        <v>0.2857206005052808</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2492942623161555</v>
-      </c>
-      <c r="C101">
-        <v>-94764.69063767901</v>
-      </c>
-      <c r="D101">
-        <v>34197.53171694444</v>
-      </c>
-      <c r="E101">
-        <v>101112.2704812664</v>
-      </c>
-      <c r="F101">
-        <v>130356.2223546235</v>
-      </c>
-      <c r="G101">
-        <v>1394</v>
-      </c>
-      <c r="H101">
-        <v>102429</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9365</v>
-      </c>
-      <c r="K101">
-        <v>1665</v>
-      </c>
-      <c r="L101">
-        <v>7700</v>
-      </c>
-      <c r="M101">
-        <v>26949.40437050385</v>
-      </c>
-      <c r="N101">
-        <v>-19249.40437050385</v>
-      </c>
-      <c r="O101">
-        <v>-2406.175546312981</v>
-      </c>
-      <c r="P101">
-        <v>-16843.22882419087</v>
-      </c>
-      <c r="Q101">
-        <v>-15178.22882419087</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.193478946482879</v>
-      </c>
-      <c r="T101">
-        <v>100.3378440367358</v>
-      </c>
-      <c r="U101">
-        <v>0.2067366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.03571507506316011</v>
-      </c>
-      <c r="W101">
-        <v>0.1993530028801279</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2857206005052808</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
